--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234B64BA-AC69-134D-ADA9-DE6164084FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC3F89A-01DC-D742-AE73-E34035428ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.6.1.1" sheetId="5" r:id="rId1"/>
     <sheet name="4.6.1.3" sheetId="1" r:id="rId2"/>
     <sheet name="4.6.1.5" sheetId="6" r:id="rId3"/>
-    <sheet name="Input Scenarios" sheetId="3" r:id="rId4"/>
-    <sheet name="Constants" sheetId="2" r:id="rId5"/>
+    <sheet name="4.6.1.7" sheetId="7" r:id="rId4"/>
+    <sheet name="Input Scenarios" sheetId="3" r:id="rId5"/>
+    <sheet name="Constants" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="138">
   <si>
     <t/>
   </si>
@@ -434,13 +435,31 @@
   <si>
     <t>MMSATMOS</t>
   </si>
+  <si>
+    <t>EFLeach</t>
+  </si>
+  <si>
+    <t>FracLEACHMS</t>
+  </si>
+  <si>
+    <t>FracWET</t>
+  </si>
+  <si>
+    <t>EN2O,leach</t>
+  </si>
+  <si>
+    <t>MNLeachjm=4</t>
+  </si>
+  <si>
+    <t>MNLeachjm=14</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="186" formatCode="0.000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -541,7 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,7 +1229,7 @@
         <v>0.15</v>
       </c>
       <c r="P11">
-        <f>IF(F11="", "",I11*(1-Q11)*(1-R11))</f>
+        <f t="shared" ref="P11:P30" si="0">IF(F11="", "",I11*(1-Q11)*(1-R11))</f>
         <v>1.4103999999999995E-2</v>
       </c>
       <c r="Q11">
@@ -1250,7 +1269,7 @@
         <v>1.1988399999999996E-3</v>
       </c>
       <c r="Z11">
-        <f>IF(F11="", "",SUM(Y11:Y13))</f>
+        <f t="shared" ref="Z11:Z30" si="1">IF(F11="", "",SUM(Y11:Y13))</f>
         <v>7.4045999999999973E-3</v>
       </c>
       <c r="AA11">
@@ -1262,7 +1281,7 @@
         <v>1.4693095871999993</v>
       </c>
       <c r="AC11">
-        <f>IF(F11="", "", SUM(W11:W14,AB11:AB15)/1000)</f>
+        <f t="shared" ref="AC11:AC30" si="2">IF(F11="", "", SUM(W11:W14,AB11:AB15)/1000)</f>
         <v>2.6820730559999995E-2</v>
       </c>
       <c r="AE11" s="12"/>
@@ -1325,7 +1344,7 @@
         <v>0.2</v>
       </c>
       <c r="P12" t="str">
-        <f>IF(F12="", "",I12*(1-Q12)*(1-R12))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q12" t="str">
@@ -1365,7 +1384,7 @@
         <v>2.8207999999999992E-3</v>
       </c>
       <c r="Z12" t="str">
-        <f>IF(F12="", "",SUM(Y12:Y14))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA12">
@@ -1373,11 +1392,11 @@
         <v>3.918158899199999E-6</v>
       </c>
       <c r="AB12">
-        <f t="shared" ref="AB12:AB15" si="0">$G$11*AA12*$H$11</f>
+        <f t="shared" ref="AB12:AB15" si="3">$G$11*AA12*$H$11</f>
         <v>0.97953972479999984</v>
       </c>
       <c r="AC12" t="str">
-        <f>IF(F12="", "", SUM(W12:W15,AB12:AB16)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1439,7 +1458,7 @@
         <v>0.25</v>
       </c>
       <c r="P13" t="str">
-        <f>IF(F13="", "",I13*(1-Q13)*(1-R13))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q13" t="str">
@@ -1479,7 +1498,7 @@
         <v>3.3849599999999989E-3</v>
       </c>
       <c r="Z13" t="str">
-        <f>IF(F13="", "",SUM(Y13:Y15))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA13">
@@ -1487,11 +1506,11 @@
         <v>4.8976986239999993E-5</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>12.244246559999999</v>
       </c>
       <c r="AC13" t="str">
-        <f>IF(F13="", "", SUM(W13:W16,AB13:AB17)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1553,7 +1572,7 @@
         <v>0.17</v>
       </c>
       <c r="P14" t="str">
-        <f>IF(F14="", "",I14*(1-Q14)*(1-R14))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q14" t="str">
@@ -1593,7 +1612,7 @@
         <v/>
       </c>
       <c r="Z14" t="str">
-        <f>IF(F14="", "",SUM(Y14:Y16))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA14">
@@ -1601,11 +1620,11 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14" t="str">
-        <f>IF(F14="", "", SUM(W14:W17,AB14:AB18)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1661,7 +1680,7 @@
         <v>0.23</v>
       </c>
       <c r="P15" s="11" t="str">
-        <f>IF(F15="", "",I15*(1-Q15)*(1-R15))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q15" s="11" t="str">
@@ -1697,7 +1716,7 @@
         <v/>
       </c>
       <c r="Z15" s="11" t="str">
-        <f>IF(F15="", "",SUM(Y15:Y17))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA15" s="11">
@@ -1705,11 +1724,11 @@
         <v>0</v>
       </c>
       <c r="AB15" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15" s="11" t="str">
-        <f>IF(F15="", "", SUM(W15:W18,AB15:AB19)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1771,7 +1790,7 @@
         <v>0.2</v>
       </c>
       <c r="P16">
-        <f>IF(F16="", "",I16*(1-Q16)*(1-R16))</f>
+        <f t="shared" si="0"/>
         <v>1.6891999999999997E-2</v>
       </c>
       <c r="Q16">
@@ -1811,7 +1830,7 @@
         <v>5.743279999999999E-3</v>
       </c>
       <c r="Z16">
-        <f>IF(F16="", "",SUM(Y16:Y18))</f>
+        <f t="shared" si="1"/>
         <v>1.3513599999999999E-2</v>
       </c>
       <c r="AA16">
@@ -1823,7 +1842,7 @@
         <v>3.7128886271999995</v>
       </c>
       <c r="AC16">
-        <f>IF(F16="", "", SUM(W16:W19,AB16:AB20)/1000)</f>
+        <f t="shared" si="2"/>
         <v>4.3742469139199998E-2</v>
       </c>
     </row>
@@ -1885,7 +1904,7 @@
         <v>0.25</v>
       </c>
       <c r="P17" t="str">
-        <f>IF(F17="", "",I17*(1-Q17)*(1-R17))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q17" t="str">
@@ -1925,7 +1944,7 @@
         <v>5.0675999999999994E-3</v>
       </c>
       <c r="Z17" t="str">
-        <f>IF(F17="", "",SUM(Y17:Y19))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA17">
@@ -1933,11 +1952,11 @@
         <v>8.2508636159999994E-6</v>
       </c>
       <c r="AB17">
-        <f t="shared" ref="AB17:AB20" si="1">$G$16*AA17*$H$16</f>
+        <f t="shared" ref="AB17:AB20" si="4">$G$16*AA17*$H$16</f>
         <v>2.3205553919999997</v>
       </c>
       <c r="AC17" t="str">
-        <f>IF(F17="", "", SUM(W17:W20,AB17:AB21)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1999,7 +2018,7 @@
         <v>0.2</v>
       </c>
       <c r="P18" t="str">
-        <f>IF(F18="", "",I18*(1-Q18)*(1-R18))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q18" t="str">
@@ -2039,7 +2058,7 @@
         <v>2.70272E-3</v>
       </c>
       <c r="Z18" t="str">
-        <f>IF(F18="", "",SUM(Y18:Y20))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA18">
@@ -2047,11 +2066,11 @@
         <v>6.6006908927999995E-5</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>18.564443135999998</v>
       </c>
       <c r="AC18" t="str">
-        <f>IF(F18="", "", SUM(W18:W21,AB18:AB22)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -2113,7 +2132,7 @@
         <v>0.25</v>
       </c>
       <c r="P19" t="str">
-        <f>IF(F19="", "",I19*(1-Q19)*(1-R19))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q19" t="str">
@@ -2153,7 +2172,7 @@
         <v/>
       </c>
       <c r="Z19" t="str">
-        <f>IF(F19="", "",SUM(Y19:Y21))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA19">
@@ -2161,11 +2180,11 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC19" t="str">
-        <f>IF(F19="", "", SUM(W19:W22,AB19:AB23)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -2221,7 +2240,7 @@
         <v>0.1</v>
       </c>
       <c r="P20" s="11" t="str">
-        <f>IF(F20="", "",I20*(1-Q20)*(1-R20))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q20" s="11" t="str">
@@ -2257,7 +2276,7 @@
         <v/>
       </c>
       <c r="Z20" s="11" t="str">
-        <f>IF(F20="", "",SUM(Y20:Y22))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA20" s="11">
@@ -2265,11 +2284,11 @@
         <v>0</v>
       </c>
       <c r="AB20" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC20" s="11" t="str">
-        <f>IF(F20="", "", SUM(W20:W23,AB20:AB24)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -2331,7 +2350,7 @@
         <v>0.34</v>
       </c>
       <c r="P21">
-        <f>IF(F21="", "",I21*(1-Q21)*(1-R21))</f>
+        <f t="shared" si="0"/>
         <v>1.5809999999999994E-2</v>
       </c>
       <c r="Q21">
@@ -2367,11 +2386,11 @@
         <v>0.15</v>
       </c>
       <c r="Y21">
-        <f>IF(OR(ISBLANK(L21), L21="pastureRangeAndPaddock"), "",$P$21*M21*(1-X21))</f>
+        <f t="shared" ref="Y21:Y30" si="5">IF(OR(ISBLANK(L21), L21="pastureRangeAndPaddock"), "",$P$21*M21*(1-X21))</f>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>IF(F21="", "",SUM(Y21:Y23))</f>
+        <f t="shared" si="1"/>
         <v>1.4228999999999995E-2</v>
       </c>
       <c r="AA21">
@@ -2383,7 +2402,7 @@
         <v>8.7423849268107237</v>
       </c>
       <c r="AC21">
-        <f>IF(F21="", "", SUM(W21:W24,AB21:AB25)/1000)</f>
+        <f t="shared" si="2"/>
         <v>3.3312486355102297E-2</v>
       </c>
     </row>
@@ -2445,7 +2464,7 @@
         <v>0.6</v>
       </c>
       <c r="P22" t="str">
-        <f>IF(F22="", "",I22*(1-Q22)*(1-R22))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q22" t="str">
@@ -2481,11 +2500,11 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <f>IF(OR(ISBLANK(L22), L22="pastureRangeAndPaddock"), "",$P$21*M22*(1-X22))</f>
+        <f t="shared" si="5"/>
         <v>1.4228999999999995E-2</v>
       </c>
       <c r="Z22" t="str">
-        <f>IF(F22="", "",SUM(Y22:Y24))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA22">
@@ -2493,11 +2512,11 @@
         <v>1.0425189887999997E-5</v>
       </c>
       <c r="AB22">
-        <f t="shared" ref="AB22:AB25" si="2">$G$21*AA22*$H$21</f>
+        <f t="shared" ref="AB22:AB25" si="6">$G$21*AA22*$H$21</f>
         <v>3.8569345265341428</v>
       </c>
       <c r="AC22" t="str">
-        <f>IF(F22="", "", SUM(W22:W25,AB22:AB26)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -2559,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="str">
-        <f>IF(F23="", "",I23*(1-Q23)*(1-R23))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q23" t="str">
@@ -2595,11 +2614,11 @@
         <v>0.2</v>
       </c>
       <c r="Y23">
-        <f>IF(OR(ISBLANK(L23), L23="pastureRangeAndPaddock"), "",$P$21*M23*(1-X23))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z23" t="str">
-        <f>IF(F23="", "",SUM(Y23:Y25))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA23">
@@ -2607,11 +2626,11 @@
         <v>0</v>
       </c>
       <c r="AB23">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" t="str">
-        <f>IF(F23="", "", SUM(W23:W26,AB23:AB27)/1000)</f>
         <v/>
       </c>
     </row>
@@ -2673,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="str">
-        <f>IF(F24="", "",I24*(1-Q24)*(1-R24))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q24" t="str">
@@ -2709,11 +2728,11 @@
         <v/>
       </c>
       <c r="Y24" t="str">
-        <f>IF(OR(ISBLANK(L24), L24="pastureRangeAndPaddock"), "",$P$21*M24*(1-X24))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Z24" t="str">
-        <f>IF(F24="", "",SUM(Y24:Y26))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA24">
@@ -2721,11 +2740,11 @@
         <v>0</v>
       </c>
       <c r="AB24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC24" t="str">
-        <f>IF(F24="", "", SUM(W24:W27,AB24:AB28)/1000)</f>
         <v/>
       </c>
     </row>
@@ -2781,7 +2800,7 @@
         <v>0.06</v>
       </c>
       <c r="P25" s="11" t="str">
-        <f>IF(F25="", "",I25*(1-Q25)*(1-R25))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q25" s="11" t="str">
@@ -2813,11 +2832,11 @@
         <v/>
       </c>
       <c r="Y25" s="11" t="str">
-        <f>IF(OR(ISBLANK(L25), L25="pastureRangeAndPaddock"), "",$P$21*M25*(1-X25))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Z25" s="11" t="str">
-        <f>IF(F25="", "",SUM(Y25:Y27))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA25" s="11">
@@ -2825,11 +2844,11 @@
         <v>0</v>
       </c>
       <c r="AB25" s="11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="11" t="str">
-        <f>IF(F25="", "", SUM(W25:W28,AB25:AB29)/1000)</f>
         <v/>
       </c>
     </row>
@@ -2891,7 +2910,7 @@
         <v>0.5</v>
       </c>
       <c r="P26">
-        <f>IF(F26="", "",I26*(1-Q26)*(1-R26))</f>
+        <f t="shared" si="0"/>
         <v>1.5809999999999994E-2</v>
       </c>
       <c r="Q26">
@@ -2927,11 +2946,11 @@
         <v>0.15</v>
       </c>
       <c r="Y26">
-        <f>IF(OR(ISBLANK(L26), L26="pastureRangeAndPaddock"), "",$P$21*M26*(1-X26))</f>
+        <f t="shared" si="5"/>
         <v>1.3438499999999995E-3</v>
       </c>
       <c r="Z26">
-        <f>IF(F26="", "",SUM(Y26:Y28))</f>
+        <f t="shared" si="1"/>
         <v>1.3438499999999995E-3</v>
       </c>
       <c r="AA26">
@@ -2943,7 +2962,7 @@
         <v>0.60749898186239981</v>
       </c>
       <c r="AC26">
-        <f>IF(F26="", "", SUM(W26:W29,AB26:AB30)/1000)</f>
+        <f t="shared" si="2"/>
         <v>2.2647204691487993E-2</v>
       </c>
     </row>
@@ -3005,7 +3024,7 @@
         <v>0.25</v>
       </c>
       <c r="P27" t="str">
-        <f>IF(F27="", "",I27*(1-Q27)*(1-R27))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q27" t="str">
@@ -3041,11 +3060,11 @@
         <v>0</v>
       </c>
       <c r="Y27">
-        <f>IF(OR(ISBLANK(L27), L27="pastureRangeAndPaddock"), "",$P$21*M27*(1-X27))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z27" t="str">
-        <f>IF(F27="", "",SUM(Y27:Y29))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA27">
@@ -3053,11 +3072,11 @@
         <v>8.2050105599999983E-7</v>
       </c>
       <c r="AB27">
-        <f t="shared" ref="AB27:AB30" si="3">$G$26*AA27*$H$26</f>
+        <f t="shared" ref="AB27:AB30" si="7">$G$26*AA27*$H$26</f>
         <v>0.15187474546559995</v>
       </c>
       <c r="AC27" t="str">
-        <f>IF(F27="", "", SUM(W27:W30,AB27:AB31)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3119,7 +3138,7 @@
         <v>0.25</v>
       </c>
       <c r="P28" t="str">
-        <f>IF(F28="", "",I28*(1-Q28)*(1-R28))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q28" t="str">
@@ -3155,11 +3174,11 @@
         <v>0.2</v>
       </c>
       <c r="Y28">
-        <f>IF(OR(ISBLANK(L28), L28="pastureRangeAndPaddock"), "",$P$21*M28*(1-X28))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z28" t="str">
-        <f>IF(F28="", "",SUM(Y28:Y30))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA28">
@@ -3167,11 +3186,11 @@
         <v>8.2050105599999979E-6</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.5187474546559996</v>
       </c>
       <c r="AC28" t="str">
-        <f>IF(F28="", "", SUM(W28:W31,AB28:AB32)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3233,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="str">
-        <f>IF(F29="", "",I29*(1-Q29)*(1-R29))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q29" t="str">
@@ -3269,11 +3288,11 @@
         <v/>
       </c>
       <c r="Y29" t="str">
-        <f>IF(OR(ISBLANK(L29), L29="pastureRangeAndPaddock"), "",$P$21*M29*(1-X29))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Z29" t="str">
-        <f>IF(F29="", "",SUM(Y29:Y31))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA29">
@@ -3281,11 +3300,11 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC29" t="str">
-        <f>IF(F29="", "", SUM(W29:W32,AB29:AB33)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3341,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="11" t="str">
-        <f>IF(F30="", "",I30*(1-Q30)*(1-R30))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q30" s="11" t="str">
@@ -3373,11 +3392,11 @@
         <v/>
       </c>
       <c r="Y30" s="11" t="str">
-        <f>IF(OR(ISBLANK(L30), L30="pastureRangeAndPaddock"), "",$P$21*M30*(1-X30))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Z30" s="11" t="str">
-        <f>IF(F30="", "",SUM(Y30:Y32))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA30" s="11">
@@ -3385,11 +3404,11 @@
         <v>0</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC30" s="11" t="str">
-        <f>IF(F30="", "", SUM(W30:W33,AB30:AB34)/1000)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3406,21 +3425,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AK30"/>
+  <dimension ref="A2:AI30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="27" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="12.1640625" customWidth="1"/>
-    <col min="36" max="37" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="12.1640625" customWidth="1"/>
+    <col min="34" max="35" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3473,7 +3492,7 @@
         <v>52</v>
       </c>
       <c r="S4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="T4" t="s">
         <v>52</v>
@@ -3482,10 +3501,10 @@
         <v>52</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="W4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="X4" t="s">
         <v>59</v>
@@ -3496,39 +3515,27 @@
       <c r="Z4" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="K5" t="s">
         <v>0</v>
       </c>
       <c r="Q5" t="s">
         <v>0</v>
       </c>
-      <c r="R5" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="Z5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AC6" t="s">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="AA6" t="s">
         <v>112</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AG6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -3580,14 +3587,8 @@
       <c r="Q8" t="s">
         <v>47</v>
       </c>
-      <c r="R8" t="s">
-        <v>51</v>
-      </c>
-      <c r="S8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -3638,67 +3639,61 @@
         <v>34</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH10" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="AG10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH10" s="10" t="s">
+        <v>114</v>
+      </c>
       <c r="AI10" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ10" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK10" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A8), "", 'Input Scenarios'!A8)</f>
         <v>NSW</v>
@@ -3764,87 +3759,79 @@
         <v>0.18</v>
       </c>
       <c r="R11">
-        <f>IF(F11="", "",_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.39</v>
-      </c>
-      <c r="S11">
-        <f>IF(F11="", "",I11*(1-P11)*(1-Q11))</f>
-        <v>1.4103999999999995E-2</v>
-      </c>
-      <c r="T11">
         <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U11">
+      <c r="S11">
         <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V11">
+      <c r="T11">
         <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W11">
+      <c r="U11">
         <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X11">
+      <c r="V11">
         <f>IF(F11="","",I11*J11/6.25)</f>
         <v>2.6144000000000002E-3</v>
       </c>
+      <c r="W11">
+        <f>IF(F11="", "", V11*(1-K11))</f>
+        <v>1.6993600000000002E-3</v>
+      </c>
+      <c r="X11">
+        <f>IF(F11="", "", G11*W11*H11)</f>
+        <v>424.84000000000003</v>
+      </c>
       <c r="Y11">
-        <f>IF(F11="", "", X11*(1-K11))</f>
-        <v>1.6993600000000002E-3</v>
+        <f>IF(ISBLANK(L11), "", $X$11*M11)</f>
+        <v>42.484000000000009</v>
       </c>
       <c r="Z11">
-        <f>IF(F11="", "", G11*Y11*H11)</f>
-        <v>424.84000000000003</v>
+        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <v>29.69631600000001</v>
       </c>
       <c r="AA11">
-        <f>IF(ISBLANK(L11), "", $Z$11*M11)</f>
-        <v>42.484000000000009</v>
+        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <v>186.67469600000001</v>
       </c>
       <c r="AB11">
-        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", AA11*(1-T11-U11))</f>
-        <v>29.69631600000001</v>
+        <f>IF(N11="directApplication", "", $AA$11*O11)</f>
+        <v>28.001204400000002</v>
       </c>
       <c r="AC11">
-        <f>IF(F11="", "",SUM(AB11:AB15))</f>
-        <v>186.67469600000001</v>
-      </c>
-      <c r="AD11">
-        <f>IF(N11="directApplication", "", $AC$11*O11)</f>
-        <v>28.001204400000002</v>
-      </c>
-      <c r="AE11">
         <f>IF(D11="", "", _xlfn.XLOOKUP('4.6.1.3'!D11, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="AF11">
+      <c r="AD11">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE11">
+        <f>IF(L11="", "", Y11*R11*AD11)</f>
+        <v>6.6760571428571433E-2</v>
+      </c>
+      <c r="AF11">
+        <f>IF(N11="directApplication", "", AB11*T11*AD11)</f>
+        <v>0.22000946314285716</v>
+      </c>
       <c r="AG11">
-        <f>IF(L11="", "", AA11*T11*AF11)</f>
-        <v>6.6760571428571433E-2</v>
+        <f>IF(F11="", "", Y14*AC11*Constants!$J$2/1000)</f>
+        <v>1.6022537142857147E-3</v>
       </c>
       <c r="AH11">
-        <f>IF(N11="directApplication", "", AD11*V11*AF11)</f>
-        <v>0.22000946314285716</v>
+        <f>IF(F11="","",SUM(AE11:AF15)/1000)</f>
+        <v>6.5481105077142866E-3</v>
       </c>
       <c r="AI11">
-        <f>IF(F11="", "", AA14*AE11*Constants!$J$2/1000)</f>
-        <v>1.6022537142857147E-3</v>
-      </c>
-      <c r="AJ11">
-        <f>IF(F11="","",SUM(AG11:AH15)/1000)</f>
-        <v>6.5481105077142866E-3</v>
-      </c>
-      <c r="AK11">
-        <f>IF(AI11="", "", AI11+AJ11)</f>
+        <f>IF(AG11="", "", AG11+AH11)</f>
         <v>8.1503642220000019E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A9), "", 'Input Scenarios'!A9)</f>
         <v/>
@@ -3909,88 +3896,80 @@
         <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R12" t="str">
-        <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <f>IF(F12="", "",I12*(1-P12)*(1-Q12))</f>
-        <v/>
-      </c>
-      <c r="T12">
+      <c r="R12">
         <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U12">
+      <c r="S12">
         <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V12">
+      <c r="T12">
         <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W12">
+      <c r="U12">
         <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V12" t="str">
+        <f>IF(F12="","",I12*J12/6.25)</f>
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <f>IF(F12="", "", V12*(1-K12))</f>
+        <v/>
+      </c>
       <c r="X12" t="str">
-        <f>IF(F12="","",I12*J12/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <f>IF(F12="", "", X12*(1-K12))</f>
-        <v/>
-      </c>
-      <c r="Z12" t="str">
-        <f t="shared" ref="Z12:Z30" si="0">IF(F12="", "", G12*Y12*H12)</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>IF(ISBLANK(L12), "", $Z$11*M12)</f>
+        <f>IF(F12="", "", G12*W12*H12)</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>IF(ISBLANK(L12), "", $X$11*M12)</f>
         <v>84.968000000000018</v>
       </c>
+      <c r="Z12">
+        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <v>80.634632000000011</v>
+      </c>
+      <c r="AA12" t="str">
+        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <v/>
+      </c>
       <c r="AB12">
-        <f t="shared" ref="AB12:AB30" si="1">IF(OR(L12="", L12="pastureRangeAndPaddock"), "", AA12*(1-T12-U12))</f>
-        <v>80.634632000000011</v>
+        <f>IF(N12="directApplication", "", $AA$11*O12)</f>
+        <v>37.334939200000001</v>
       </c>
       <c r="AC12" t="str">
-        <f>IF(F12="", "",SUM(AB12:AB16))</f>
+        <f>IF(D12="", "", _xlfn.XLOOKUP('4.6.1.3'!D12, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD12:AD15" si="2">IF(N12="directApplication", "", $AC$11*O12)</f>
-        <v>37.334939200000001</v>
-      </c>
-      <c r="AE12" t="str">
-        <f>IF(D12="", "", _xlfn.XLOOKUP('4.6.1.3'!D12, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF12">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG12">
-        <f t="shared" ref="AG12:AG30" si="3">IF(L12="", "", AA12*T12*AF12)</f>
+      <c r="AE12">
+        <f>IF(L12="", "", Y12*R12*AD12)</f>
         <v>0.13352114285714287</v>
       </c>
-      <c r="AH12">
-        <f t="shared" ref="AH12:AH30" si="4">IF(N12="directApplication", "", AD12*V12*AF12)</f>
+      <c r="AF12">
+        <f>IF(N12="directApplication", "", AB12*T12*AD12)</f>
         <v>0.58669190171428576</v>
       </c>
+      <c r="AG12" t="str">
+        <f>IF(F12="", "", Y15*AC12*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <f>IF(F12="","",SUM(AE12:AF16)/1000)</f>
+        <v/>
+      </c>
       <c r="AI12" t="str">
-        <f>IF(F12="", "", AA15*AE12*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ12" t="str">
-        <f t="shared" ref="AJ12:AJ30" si="5">IF(F12="","",SUM(AG12:AH16)/1000)</f>
-        <v/>
-      </c>
-      <c r="AK12" t="str">
-        <f t="shared" ref="AK12:AK30" si="6">IF(AI12="", "", AI12+AJ12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" ref="AI12:AI30" si="0">IF(AG12="", "", AG12+AH12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A10), "", 'Input Scenarios'!A10)</f>
         <v/>
@@ -4055,88 +4034,80 @@
         <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R13" t="str">
-        <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S13" t="str">
-        <f>IF(F13="", "",I13*(1-P13)*(1-Q13))</f>
-        <v/>
-      </c>
-      <c r="T13">
+      <c r="R13">
         <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U13">
+      <c r="S13">
         <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V13">
+      <c r="T13">
         <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W13">
+      <c r="U13">
         <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V13" t="str">
+        <f>IF(F13="","",I13*J13/6.25)</f>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f>IF(F13="", "", V13*(1-K13))</f>
+        <v/>
+      </c>
       <c r="X13" t="str">
-        <f>IF(F13="","",I13*J13/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <f>IF(F13="", "", X13*(1-K13))</f>
-        <v/>
-      </c>
-      <c r="Z13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>IF(ISBLANK(L13), "", $Z$11*M13)</f>
+        <f>IF(F13="", "", G13*W13*H13)</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>IF(ISBLANK(L13), "", $X$11*M13)</f>
         <v>127.452</v>
       </c>
+      <c r="Z13">
+        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <v>76.343747999999991</v>
+      </c>
+      <c r="AA13" t="str">
+        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <v/>
+      </c>
       <c r="AB13">
-        <f t="shared" si="1"/>
-        <v>76.343747999999991</v>
+        <f>IF(N13="directApplication", "", $AA$11*O13)</f>
+        <v>46.668674000000003</v>
       </c>
       <c r="AC13" t="str">
-        <f>IF(F13="", "",SUM(AB13:AB17))</f>
+        <f>IF(D13="", "", _xlfn.XLOOKUP('4.6.1.3'!D13, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
-        <v>46.668674000000003</v>
-      </c>
-      <c r="AE13" t="str">
-        <f>IF(D13="", "", _xlfn.XLOOKUP('4.6.1.3'!D13, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF13">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG13">
-        <f t="shared" si="3"/>
+      <c r="AE13">
+        <f>IF(L13="", "", Y13*R13*AD13)</f>
         <v>0.20028171428571429</v>
       </c>
-      <c r="AH13">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF13">
+        <f>IF(N13="directApplication", "", AB13*T13*AD13)</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" t="str">
+        <f>IF(F13="", "", Y16*AC13*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <f>IF(F13="","",SUM(AE13:AF17)/1000)</f>
+        <v/>
       </c>
       <c r="AI13" t="str">
-        <f>IF(F13="", "", AA16*AE13*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ13" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A11), "", 'Input Scenarios'!A11)</f>
         <v/>
@@ -4201,88 +4172,80 @@
         <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R14" t="str">
-        <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S14" t="str">
-        <f>IF(F14="", "",I14*(1-P14)*(1-Q14))</f>
-        <v/>
-      </c>
-      <c r="T14">
+      <c r="R14">
         <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U14" t="str">
+      <c r="S14" t="str">
         <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V14">
+      <c r="T14">
         <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W14">
+      <c r="U14">
         <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V14" t="str">
+        <f>IF(F14="","",I14*J14/6.25)</f>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f>IF(F14="", "", V14*(1-K14))</f>
+        <v/>
+      </c>
       <c r="X14" t="str">
-        <f>IF(F14="","",I14*J14/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <f>IF(F14="", "", X14*(1-K14))</f>
-        <v/>
+        <f>IF(F14="", "", G14*W14*H14)</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>IF(ISBLANK(L14), "", $X$11*M14)</f>
+        <v>169.93600000000004</v>
       </c>
       <c r="Z14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>IF(ISBLANK(L14), "", $Z$11*M14)</f>
-        <v>169.93600000000004</v>
-      </c>
-      <c r="AB14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>IF(N14="directApplication", "", $AA$11*O14)</f>
+        <v>31.734698320000003</v>
       </c>
       <c r="AC14" t="str">
-        <f>IF(F14="", "",SUM(AB14:AB18))</f>
+        <f>IF(D14="", "", _xlfn.XLOOKUP('4.6.1.3'!D14, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
-        <v>31.734698320000003</v>
-      </c>
-      <c r="AE14" t="str">
-        <f>IF(D14="", "", _xlfn.XLOOKUP('4.6.1.3'!D14, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF14">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG14">
-        <f>IF(L14="", "", AA14*T14*AF14)</f>
+      <c r="AE14">
+        <f>IF(L14="", "", Y14*R14*AD14)</f>
         <v>5.3408457142857158</v>
       </c>
-      <c r="AH14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF14">
+        <f>IF(N14="directApplication", "", AB14*T14*AD14)</f>
+        <v>0</v>
+      </c>
+      <c r="AG14" t="str">
+        <f>IF(F14="", "", Y17*AC14*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <f>IF(F14="","",SUM(AE14:AF18)/1000)</f>
+        <v/>
       </c>
       <c r="AI14" t="str">
-        <f>IF(F14="", "", AA17*AE14*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A12), "", 'Input Scenarios'!A12)</f>
         <v/>
@@ -4341,88 +4304,80 @@
         <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R15" s="11" t="str">
-        <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S15" s="11" t="str">
-        <f>IF(F15="", "",I15*(1-P15)*(1-Q15))</f>
+      <c r="R15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T15" t="str">
-        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V15" t="str">
         <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W15" t="str">
+      <c r="U15" t="str">
         <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X15" s="11" t="str">
+      <c r="V15" s="11" t="str">
         <f>IF(F15="","",I15*J15/6.25)</f>
         <v/>
       </c>
+      <c r="W15" s="11" t="str">
+        <f>IF(F15="", "", V15*(1-K15))</f>
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <f>IF(F15="", "", G15*W15*H15)</f>
+        <v/>
+      </c>
       <c r="Y15" s="11" t="str">
-        <f>IF(F15="", "", X15*(1-K15))</f>
+        <f>IF(ISBLANK(L15), "", $X$11*M15)</f>
         <v/>
       </c>
       <c r="Z15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
         <v/>
       </c>
       <c r="AA15" s="11" t="str">
-        <f>IF(ISBLANK(L15), "", $Z$11*M15)</f>
+        <f>IF(F15="", "",SUM(Z15:Z19))</f>
         <v/>
       </c>
       <c r="AB15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC15" s="11" t="str">
-        <f>IF(F15="", "",SUM(AB15:AB19))</f>
-        <v/>
-      </c>
-      <c r="AD15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AE15" t="str">
+        <f>IF(N15="directApplication", "", $AA$11*O15)</f>
+        <v/>
+      </c>
+      <c r="AC15" t="str">
         <f>IF(D15="", "", _xlfn.XLOOKUP('4.6.1.3'!D15, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
-      <c r="AF15">
+      <c r="AD15">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE15" t="str">
+        <f>IF(L15="", "", Y15*R15*AD15)</f>
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <f>IF(N15="directApplication", "", AB15*T15*AD15)</f>
+        <v/>
+      </c>
       <c r="AG15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(F15="", "", Y18*AC15*Constants!$J$2/1000)</f>
         <v/>
       </c>
       <c r="AH15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(F15="","",SUM(AE15:AF19)/1000)</f>
         <v/>
       </c>
       <c r="AI15" t="str">
-        <f>IF(F15="", "", AA18*AE15*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A13), "", 'Input Scenarios'!A13)</f>
         <v>QLD</v>
@@ -4488,87 +4443,79 @@
         <v>0.18</v>
       </c>
       <c r="R16">
-        <f>IF(F16="", "",_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S16">
-        <f>IF(F16="", "",I16*(1-P16)*(1-Q16))</f>
-        <v>1.6891999999999997E-2</v>
-      </c>
-      <c r="T16">
         <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U16">
+      <c r="S16">
         <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V16">
+      <c r="T16">
         <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W16">
+      <c r="U16">
         <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X16">
+      <c r="V16">
         <f>IF(F16="","",I16*J16/6.25)</f>
         <v>3.1312000000000002E-3</v>
       </c>
+      <c r="W16">
+        <f>IF(F16="", "", V16*(1-K16))</f>
+        <v>2.1292159999999997E-3</v>
+      </c>
+      <c r="X16">
+        <f>IF(F16="", "", G16*W16*H16)</f>
+        <v>598.84199999999987</v>
+      </c>
       <c r="Y16">
-        <f>IF(F16="", "", X16*(1-K16))</f>
-        <v>2.1292159999999997E-3</v>
+        <f>IF(ISBLANK(L16), "", $X$16*M16)</f>
+        <v>239.53679999999997</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="0"/>
-        <v>598.84199999999987</v>
+        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <v>167.4362232</v>
       </c>
       <c r="AA16">
-        <f>IF(ISBLANK(L16), "", $Z$16*M16)</f>
-        <v>239.53679999999997</v>
+        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <v>409.66781219999996</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="1"/>
-        <v>167.4362232</v>
+        <f>IF(N16="directApplication", "", $AA$16*O16)</f>
+        <v>81.933562440000003</v>
       </c>
       <c r="AC16">
-        <f>IF(F16="", "",SUM(AB16:AB20))</f>
-        <v>409.66781219999996</v>
-      </c>
-      <c r="AD16">
-        <f>IF(N16="directApplication", "", $AC$16*O16)</f>
-        <v>81.933562440000003</v>
-      </c>
-      <c r="AE16">
         <f>IF(D16="", "", _xlfn.XLOOKUP('4.6.1.3'!D16, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v>2E-3</v>
       </c>
-      <c r="AF16">
+      <c r="AD16">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE16">
+        <f>IF(L16="", "", Y16*R16*AD16)</f>
+        <v>0.37641497142857139</v>
+      </c>
+      <c r="AF16">
+        <f>IF(N16="directApplication", "", AB16*T16*AD16)</f>
+        <v>0.64376370488571433</v>
+      </c>
       <c r="AG16">
-        <f t="shared" si="3"/>
-        <v>0.37641497142857139</v>
+        <f>IF(F16="", "", Y19*AC16*Constants!$J$2/1000)</f>
+        <v>1.8820748571428568E-4</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="4"/>
-        <v>0.64376370488571433</v>
+        <f>IF(F16="","",SUM(AE16:AF20)/1000)</f>
+        <v>4.9821815099571429E-3</v>
       </c>
       <c r="AI16">
-        <f>IF(F16="", "", AA19*AE16*Constants!$J$2/1000)</f>
-        <v>1.8820748571428568E-4</v>
-      </c>
-      <c r="AJ16">
-        <f t="shared" si="5"/>
-        <v>4.9821815099571429E-3</v>
-      </c>
-      <c r="AK16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>5.1703889956714287E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A14), "", 'Input Scenarios'!A14)</f>
         <v/>
@@ -4633,88 +4580,80 @@
         <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R17" t="str">
-        <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <f>IF(F17="", "",I17*(1-P17)*(1-Q17))</f>
-        <v/>
-      </c>
-      <c r="T17">
+      <c r="R17">
         <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U17">
+      <c r="S17">
         <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V17">
+      <c r="T17">
         <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W17">
+      <c r="U17">
         <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V17" t="str">
+        <f>IF(F17="","",I17*J17/6.25)</f>
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <f>IF(F17="", "", V17*(1-K17))</f>
+        <v/>
+      </c>
       <c r="X17" t="str">
-        <f>IF(F17="","",I17*J17/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y17" t="str">
-        <f>IF(F17="", "", X17*(1-K17))</f>
-        <v/>
-      </c>
-      <c r="Z17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>IF(ISBLANK(L17), "", $Z$16*M17)</f>
+        <f>IF(F17="", "", G17*W17*H17)</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>IF(ISBLANK(L17), "", $X$16*M17)</f>
         <v>179.65259999999995</v>
       </c>
+      <c r="Z17">
+        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <v>170.49031739999995</v>
+      </c>
+      <c r="AA17" t="str">
+        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <v/>
+      </c>
       <c r="AB17">
-        <f t="shared" si="1"/>
-        <v>170.49031739999995</v>
+        <f>IF(N17="directApplication", "", $AA$16*O17)</f>
+        <v>102.41695304999999</v>
       </c>
       <c r="AC17" t="str">
-        <f>IF(F17="", "",SUM(AB17:AB21))</f>
+        <f>IF(D17="", "", _xlfn.XLOOKUP('4.6.1.3'!D17, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD17">
-        <f t="shared" ref="AD17:AD20" si="7">IF(N17="directApplication", "", $AC$16*O17)</f>
-        <v>102.41695304999999</v>
-      </c>
-      <c r="AE17" t="str">
-        <f>IF(D17="", "", _xlfn.XLOOKUP('4.6.1.3'!D17, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF17">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG17">
-        <f t="shared" si="3"/>
+      <c r="AE17">
+        <f>IF(L17="", "", Y17*R17*AD17)</f>
         <v>0.28231122857142849</v>
       </c>
-      <c r="AH17">
-        <f t="shared" si="4"/>
+      <c r="AF17">
+        <f>IF(N17="directApplication", "", AB17*T17*AD17)</f>
         <v>1.6094092622142855</v>
       </c>
+      <c r="AG17" t="str">
+        <f>IF(F17="", "", Y20*AC17*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <f>IF(F17="","",SUM(AE17:AF21)/1000)</f>
+        <v/>
+      </c>
       <c r="AI17" t="str">
-        <f>IF(F17="", "", AA20*AE17*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK17" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A15), "", 'Input Scenarios'!A15)</f>
         <v/>
@@ -4779,88 +4718,80 @@
         <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R18" t="str">
-        <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S18" t="str">
-        <f>IF(F18="", "",I18*(1-P18)*(1-Q18))</f>
-        <v/>
-      </c>
-      <c r="T18">
+      <c r="R18">
         <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U18">
+      <c r="S18">
         <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V18">
+      <c r="T18">
         <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W18">
+      <c r="U18">
         <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V18" t="str">
+        <f>IF(F18="","",I18*J18/6.25)</f>
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <f>IF(F18="", "", V18*(1-K18))</f>
+        <v/>
+      </c>
       <c r="X18" t="str">
-        <f>IF(F18="","",I18*J18/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y18" t="str">
-        <f>IF(F18="", "", X18*(1-K18))</f>
-        <v/>
-      </c>
-      <c r="Z18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>IF(ISBLANK(L18), "", $Z$16*M18)</f>
+        <f>IF(F18="", "", G18*W18*H18)</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>IF(ISBLANK(L18), "", $X$16*M18)</f>
         <v>119.76839999999999</v>
       </c>
+      <c r="Z18">
+        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <v>71.74127159999999</v>
+      </c>
+      <c r="AA18" t="str">
+        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <v/>
+      </c>
       <c r="AB18">
-        <f t="shared" si="1"/>
-        <v>71.74127159999999</v>
+        <f>IF(N18="directApplication", "", $AA$16*O18)</f>
+        <v>81.933562440000003</v>
       </c>
       <c r="AC18" t="str">
-        <f>IF(F18="", "",SUM(AB18:AB22))</f>
+        <f>IF(D18="", "", _xlfn.XLOOKUP('4.6.1.3'!D18, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD18">
-        <f t="shared" si="7"/>
-        <v>81.933562440000003</v>
-      </c>
-      <c r="AE18" t="str">
-        <f>IF(D18="", "", _xlfn.XLOOKUP('4.6.1.3'!D18, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF18">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG18">
-        <f t="shared" si="3"/>
+      <c r="AE18">
+        <f>IF(L18="", "", Y18*R18*AD18)</f>
         <v>0.18820748571428569</v>
       </c>
-      <c r="AH18">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF18">
+        <f>IF(N18="directApplication", "", AB18*T18*AD18)</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" t="str">
+        <f>IF(F18="", "", Y21*AC18*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <f>IF(F18="","",SUM(AE18:AF22)/1000)</f>
+        <v/>
       </c>
       <c r="AI18" t="str">
-        <f>IF(F18="", "", AA21*AE18*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ18" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A16), "", 'Input Scenarios'!A16)</f>
         <v/>
@@ -4925,88 +4856,80 @@
         <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R19" t="str">
-        <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <f>IF(F19="", "",I19*(1-P19)*(1-Q19))</f>
-        <v/>
-      </c>
-      <c r="T19">
+      <c r="R19">
         <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U19" t="str">
+      <c r="S19" t="str">
         <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V19">
+      <c r="T19">
         <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W19">
+      <c r="U19">
         <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V19" t="str">
+        <f>IF(F19="","",I19*J19/6.25)</f>
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <f>IF(F19="", "", V19*(1-K19))</f>
+        <v/>
+      </c>
       <c r="X19" t="str">
-        <f>IF(F19="","",I19*J19/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y19" t="str">
-        <f>IF(F19="", "", X19*(1-K19))</f>
-        <v/>
+        <f>IF(F19="", "", G19*W19*H19)</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>IF(ISBLANK(L19), "", $X$16*M19)</f>
+        <v>59.884199999999993</v>
       </c>
       <c r="Z19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>IF(ISBLANK(L19), "", $Z$16*M19)</f>
-        <v>59.884199999999993</v>
-      </c>
-      <c r="AB19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>IF(N19="directApplication", "", $AA$16*O19)</f>
+        <v>102.41695304999999</v>
       </c>
       <c r="AC19" t="str">
-        <f>IF(F19="", "",SUM(AB19:AB23))</f>
+        <f>IF(D19="", "", _xlfn.XLOOKUP('4.6.1.3'!D19, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD19">
-        <f t="shared" si="7"/>
-        <v>102.41695304999999</v>
-      </c>
-      <c r="AE19" t="str">
-        <f>IF(D19="", "", _xlfn.XLOOKUP('4.6.1.3'!D19, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF19">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG19">
-        <f t="shared" si="3"/>
+      <c r="AE19">
+        <f>IF(L19="", "", Y19*R19*AD19)</f>
         <v>1.8820748571428572</v>
       </c>
-      <c r="AH19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF19">
+        <f>IF(N19="directApplication", "", AB19*T19*AD19)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" t="str">
+        <f>IF(F19="", "", Y22*AC19*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <f>IF(F19="","",SUM(AE19:AF23)/1000)</f>
+        <v/>
       </c>
       <c r="AI19" t="str">
-        <f>IF(F19="", "", AA22*AE19*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ19" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK19" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A17), "", 'Input Scenarios'!A17)</f>
         <v/>
@@ -5065,88 +4988,80 @@
         <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R20" s="11" t="str">
-        <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S20" s="11" t="str">
-        <f>IF(F20="", "",I20*(1-P20)*(1-Q20))</f>
+      <c r="R20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T20" t="str">
-        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U20" t="str">
-        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V20" t="str">
         <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W20" t="str">
+      <c r="U20" t="str">
         <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X20" s="11" t="str">
+      <c r="V20" s="11" t="str">
         <f>IF(F20="","",I20*J20/6.25)</f>
         <v/>
       </c>
+      <c r="W20" s="11" t="str">
+        <f>IF(F20="", "", V20*(1-K20))</f>
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <f>IF(F20="", "", G20*W20*H20)</f>
+        <v/>
+      </c>
       <c r="Y20" s="11" t="str">
-        <f>IF(F20="", "", X20*(1-K20))</f>
+        <f>IF(ISBLANK(L20), "", $X$16*M20)</f>
         <v/>
       </c>
       <c r="Z20" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
         <v/>
       </c>
       <c r="AA20" s="11" t="str">
-        <f>IF(ISBLANK(L20), "", $Z$16*M20)</f>
+        <f>IF(F20="", "",SUM(Z20:Z24))</f>
         <v/>
       </c>
       <c r="AB20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC20" s="11" t="str">
-        <f>IF(F20="", "",SUM(AB20:AB24))</f>
-        <v/>
-      </c>
-      <c r="AD20" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AE20" t="str">
+        <f>IF(N20="directApplication", "", $AA$16*O20)</f>
+        <v/>
+      </c>
+      <c r="AC20" t="str">
         <f>IF(D20="", "", _xlfn.XLOOKUP('4.6.1.3'!D20, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
-      <c r="AF20">
+      <c r="AD20">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE20" t="str">
+        <f>IF(L20="", "", Y20*R20*AD20)</f>
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <f>IF(N20="directApplication", "", AB20*T20*AD20)</f>
+        <v/>
+      </c>
       <c r="AG20" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(F20="", "", Y23*AC20*Constants!$J$2/1000)</f>
         <v/>
       </c>
       <c r="AH20" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(F20="","",SUM(AE20:AF24)/1000)</f>
         <v/>
       </c>
       <c r="AI20" t="str">
-        <f>IF(F20="", "", AA23*AE20*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ20" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A18), "", 'Input Scenarios'!A18)</f>
         <v>TAS</v>
@@ -5212,87 +5127,79 @@
         <v>0.15</v>
       </c>
       <c r="R21">
-        <f>IF(F21="", "",_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S21">
-        <f>IF(F21="", "",I21*(1-P21)*(1-Q21))</f>
-        <v>1.5809999999999994E-2</v>
-      </c>
-      <c r="T21">
         <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U21">
+      <c r="S21">
         <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V21">
+      <c r="T21">
         <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W21">
+      <c r="U21">
         <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X21">
+      <c r="V21">
         <f>IF(F21="","",I21*J21/6.25)</f>
         <v>3.4223999999999999E-3</v>
       </c>
+      <c r="W21">
+        <f>IF(F21="", "", V21*(1-K21))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X21">
+        <f>IF(F21="", "", G21*W21*H21)</f>
+        <v>671.06552673600004</v>
+      </c>
       <c r="Y21">
-        <f>IF(F21="", "", X21*(1-K21))</f>
-        <v>1.813872E-3</v>
+        <f>IF(ISBLANK(L21), "", $X$21*M21)</f>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="0"/>
-        <v>671.06552673600004</v>
+        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <f>IF(ISBLANK(L21), "", $Z$21*M21)</f>
-        <v>0</v>
+        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <v>573.15706638521772</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(N21="directApplication", "", $AA$21*O21)</f>
+        <v>194.87340257097404</v>
       </c>
       <c r="AC21">
-        <f>IF(F21="", "",SUM(AB21:AB25))</f>
-        <v>573.15706638521772</v>
-      </c>
-      <c r="AD21">
-        <f>IF(N21="directApplication", "", $AC$21*O21)</f>
-        <v>194.87340257097404</v>
-      </c>
-      <c r="AE21">
         <f>IF(D21="", "", _xlfn.XLOOKUP('4.6.1.3'!D21, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="AF21">
+      <c r="AD21">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE21">
+        <f>IF(L21="", "", Y21*R21*AD21)</f>
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <f>IF(N21="directApplication", "", AB21*T21*AD21)</f>
+        <v>1.5311481630576531</v>
+      </c>
       <c r="AG21">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>IF(F21="", "", Y24*AC21*Constants!$J$2/1000)</f>
+        <v>6.327189252082286E-4</v>
       </c>
       <c r="AH21">
-        <f t="shared" si="4"/>
-        <v>1.5311481630576531</v>
+        <f>IF(F21="","",SUM(AE21:AF25)/1000)</f>
+        <v>9.9933419751009056E-3</v>
       </c>
       <c r="AI21">
-        <f>IF(F21="", "", AA24*AE21*Constants!$J$2/1000)</f>
-        <v>6.327189252082286E-4</v>
-      </c>
-      <c r="AJ21">
-        <f t="shared" si="5"/>
-        <v>9.9933419751009056E-3</v>
-      </c>
-      <c r="AK21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>1.0626060900309134E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A19), "", 'Input Scenarios'!A19)</f>
         <v/>
@@ -5357,88 +5264,80 @@
         <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R22" t="str">
-        <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <f>IF(F22="", "",I22*(1-P22)*(1-Q22))</f>
-        <v/>
-      </c>
-      <c r="T22">
+      <c r="R22">
         <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U22">
+      <c r="S22">
         <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V22">
+      <c r="T22">
         <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W22">
+      <c r="U22">
         <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V22" t="str">
+        <f>IF(F22="","",I22*J22/6.25)</f>
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <f>IF(F22="", "", V22*(1-K22))</f>
+        <v/>
+      </c>
       <c r="X22" t="str">
-        <f>IF(F22="","",I22*J22/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <f>IF(F22="", "", X22*(1-K22))</f>
-        <v/>
-      </c>
-      <c r="Z22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>IF(ISBLANK(L22), "", $Z$21*M22)</f>
+        <f>IF(F22="", "", G22*W22*H22)</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>IF(ISBLANK(L22), "", $X$21*M22)</f>
         <v>603.9589740624001</v>
       </c>
+      <c r="Z22">
+        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <v>573.15706638521772</v>
+      </c>
+      <c r="AA22" t="str">
+        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <v/>
+      </c>
       <c r="AB22">
-        <f t="shared" si="1"/>
-        <v>573.15706638521772</v>
+        <f>IF(N22="directApplication", "", $AA$21*O22)</f>
+        <v>343.89423983113062</v>
       </c>
       <c r="AC22" t="str">
-        <f>IF(F22="", "",SUM(AB22:AB26))</f>
+        <f>IF(D22="", "", _xlfn.XLOOKUP('4.6.1.3'!D22, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD22">
-        <f t="shared" ref="AD22:AD25" si="8">IF(N22="directApplication", "", $AC$21*O22)</f>
-        <v>343.89423983113062</v>
-      </c>
-      <c r="AE22" t="str">
-        <f>IF(D22="", "", _xlfn.XLOOKUP('4.6.1.3'!D22, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF22">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG22">
-        <f t="shared" si="3"/>
+      <c r="AE22">
+        <f>IF(L22="", "", Y22*R22*AD22)</f>
         <v>0.94907838781234299</v>
       </c>
-      <c r="AH22">
-        <f t="shared" si="4"/>
+      <c r="AF22">
+        <f>IF(N22="directApplication", "", AB22*T22*AD22)</f>
         <v>5.4040523402034806</v>
       </c>
+      <c r="AG22" t="str">
+        <f>IF(F22="", "", Y25*AC22*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <f>IF(F22="","",SUM(AE22:AF26)/1000)</f>
+        <v/>
+      </c>
       <c r="AI22" t="str">
-        <f>IF(F22="", "", AA25*AE22*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ22" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK22" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A20), "", 'Input Scenarios'!A20)</f>
         <v/>
@@ -5503,88 +5402,80 @@
         <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R23" t="str">
-        <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <f>IF(F23="", "",I23*(1-P23)*(1-Q23))</f>
-        <v/>
-      </c>
-      <c r="T23">
+      <c r="R23">
         <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U23">
+      <c r="S23">
         <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V23">
+      <c r="T23">
         <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W23">
+      <c r="U23">
         <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V23" t="str">
+        <f>IF(F23="","",I23*J23/6.25)</f>
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <f>IF(F23="", "", V23*(1-K23))</f>
+        <v/>
+      </c>
       <c r="X23" t="str">
-        <f>IF(F23="","",I23*J23/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <f>IF(F23="", "", X23*(1-K23))</f>
-        <v/>
-      </c>
-      <c r="Z23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>IF(ISBLANK(L23), "", $Z$21*M23)</f>
-        <v>0</v>
+        <f>IF(F23="", "", G23*W23*H23)</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>IF(ISBLANK(L23), "", $X$21*M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" t="str">
+        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <v/>
       </c>
       <c r="AB23">
-        <f t="shared" si="1"/>
+        <f>IF(N23="directApplication", "", $AA$21*O23)</f>
         <v>0</v>
       </c>
       <c r="AC23" t="str">
-        <f>IF(F23="", "",SUM(AB23:AB27))</f>
+        <f>IF(D23="", "", _xlfn.XLOOKUP('4.6.1.3'!D23, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD23">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" t="str">
-        <f>IF(D23="", "", _xlfn.XLOOKUP('4.6.1.3'!D23, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF23">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AE23">
+        <f>IF(L23="", "", Y23*R23*AD23)</f>
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <f>IF(N23="directApplication", "", AB23*T23*AD23)</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" t="str">
+        <f>IF(F23="", "", Y26*AC23*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <f>IF(F23="","",SUM(AE23:AF27)/1000)</f>
+        <v/>
       </c>
       <c r="AI23" t="str">
-        <f>IF(F23="", "", AA26*AE23*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ23" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK23" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A21), "", 'Input Scenarios'!A21)</f>
         <v/>
@@ -5649,88 +5540,80 @@
         <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R24" t="str">
-        <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <f>IF(F24="", "",I24*(1-P24)*(1-Q24))</f>
-        <v/>
-      </c>
-      <c r="T24">
+      <c r="R24">
         <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U24" t="str">
+      <c r="S24" t="str">
         <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V24">
+      <c r="T24">
         <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W24">
+      <c r="U24">
         <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V24" t="str">
+        <f>IF(F24="","",I24*J24/6.25)</f>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f>IF(F24="", "", V24*(1-K24))</f>
+        <v/>
+      </c>
       <c r="X24" t="str">
-        <f>IF(F24="","",I24*J24/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <f>IF(F24="", "", X24*(1-K24))</f>
-        <v/>
+        <f>IF(F24="", "", G24*W24*H24)</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>IF(ISBLANK(L24), "", $X$21*M24)</f>
+        <v>67.106552673600007</v>
       </c>
       <c r="Z24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>IF(ISBLANK(L24), "", $Z$21*M24)</f>
-        <v>67.106552673600007</v>
-      </c>
-      <c r="AB24" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <v/>
+      </c>
+      <c r="AA24" t="str">
+        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>IF(N24="directApplication", "", $AA$21*O24)</f>
+        <v>0</v>
       </c>
       <c r="AC24" t="str">
-        <f>IF(F24="", "",SUM(AB24:AB28))</f>
+        <f>IF(D24="", "", _xlfn.XLOOKUP('4.6.1.3'!D24, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD24">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AE24" t="str">
-        <f>IF(D24="", "", _xlfn.XLOOKUP('4.6.1.3'!D24, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF24">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG24">
-        <f t="shared" si="3"/>
+      <c r="AE24">
+        <f>IF(L24="", "", Y24*R24*AD24)</f>
         <v>2.1090630840274289</v>
       </c>
-      <c r="AH24">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF24">
+        <f>IF(N24="directApplication", "", AB24*T24*AD24)</f>
+        <v>0</v>
+      </c>
+      <c r="AG24" t="str">
+        <f>IF(F24="", "", Y27*AC24*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <f>IF(F24="","",SUM(AE24:AF28)/1000)</f>
+        <v/>
       </c>
       <c r="AI24" t="str">
-        <f>IF(F24="", "", AA27*AE24*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ24" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A22), "", 'Input Scenarios'!A22)</f>
         <v/>
@@ -5789,88 +5672,80 @@
         <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R25" s="11" t="str">
-        <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S25" s="11" t="str">
-        <f>IF(F25="", "",I25*(1-P25)*(1-Q25))</f>
+      <c r="R25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T25" t="str">
-        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U25" t="str">
-        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V25" t="str">
         <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W25" t="str">
+      <c r="U25" t="str">
         <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X25" s="11" t="str">
+      <c r="V25" s="11" t="str">
         <f>IF(F25="","",I25*J25/6.25)</f>
         <v/>
       </c>
+      <c r="W25" s="11" t="str">
+        <f>IF(F25="", "", V25*(1-K25))</f>
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <f>IF(F25="", "", G25*W25*H25)</f>
+        <v/>
+      </c>
       <c r="Y25" s="11" t="str">
-        <f>IF(F25="", "", X25*(1-K25))</f>
+        <f>IF(ISBLANK(L25), "", $X$21*M25)</f>
         <v/>
       </c>
       <c r="Z25" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
         <v/>
       </c>
       <c r="AA25" s="11" t="str">
-        <f>IF(ISBLANK(L25), "", $Z$21*M25)</f>
+        <f>IF(F25="", "",SUM(Z25:Z29))</f>
         <v/>
       </c>
       <c r="AB25" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC25" s="11" t="str">
-        <f>IF(F25="", "",SUM(AB25:AB29))</f>
-        <v/>
-      </c>
-      <c r="AD25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AE25" t="str">
+        <f>IF(N25="directApplication", "", $AA$21*O25)</f>
+        <v/>
+      </c>
+      <c r="AC25" t="str">
         <f>IF(D25="", "", _xlfn.XLOOKUP('4.6.1.3'!D25, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
-      <c r="AF25">
+      <c r="AD25">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE25" t="str">
+        <f>IF(L25="", "", Y25*R25*AD25)</f>
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <f>IF(N25="directApplication", "", AB25*T25*AD25)</f>
+        <v/>
+      </c>
       <c r="AG25" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(F25="", "", Y28*AC25*Constants!$J$2/1000)</f>
         <v/>
       </c>
       <c r="AH25" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(F25="","",SUM(AE25:AF29)/1000)</f>
         <v/>
       </c>
       <c r="AI25" t="str">
-        <f>IF(F25="", "", AA28*AE25*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ25" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK25" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A23), "", 'Input Scenarios'!A23)</f>
         <v>NT</v>
@@ -5936,87 +5811,79 @@
         <v>0.15</v>
       </c>
       <c r="R26">
-        <f>IF(F26="", "",_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S26">
-        <f>IF(F26="", "",I26*(1-P26)*(1-Q26))</f>
-        <v>1.5809999999999994E-2</v>
-      </c>
-      <c r="T26">
         <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U26">
+      <c r="S26">
         <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V26">
+      <c r="T26">
         <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W26">
+      <c r="U26">
         <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X26">
+      <c r="V26">
         <f>IF(F26="","",I26*J26/6.25)</f>
         <v>3.4223999999999999E-3</v>
       </c>
+      <c r="W26">
+        <f>IF(F26="", "", V26*(1-K26))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X26">
+        <f>IF(F26="", "", G26*W26*H26)</f>
+        <v>335.74770719999998</v>
+      </c>
       <c r="Y26">
-        <f>IF(F26="", "", X26*(1-K26))</f>
-        <v>1.813872E-3</v>
+        <f>IF(ISBLANK(L26), "", $X$26*M26)</f>
+        <v>33.574770719999997</v>
       </c>
       <c r="Z26">
-        <f t="shared" si="0"/>
-        <v>335.74770719999998</v>
+        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <v>23.46876473328</v>
       </c>
       <c r="AA26">
-        <f>IF(ISBLANK(L26), "", $Z$26*M26)</f>
-        <v>33.574770719999997</v>
+        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <v>23.46876473328</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="1"/>
-        <v>23.46876473328</v>
+        <f>IF(N26="directApplication", "", $AA$26*O26)</f>
+        <v>11.73438236664</v>
       </c>
       <c r="AC26">
-        <f>IF(F26="", "",SUM(AB26:AB30))</f>
-        <v>23.46876473328</v>
-      </c>
-      <c r="AD26">
-        <f>IF(N26="directApplication", "", $AC$26*O26)</f>
-        <v>11.73438236664</v>
-      </c>
-      <c r="AE26">
         <f>IF(D26="", "", _xlfn.XLOOKUP('4.6.1.3'!D26, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v>2E-3</v>
       </c>
-      <c r="AF26">
+      <c r="AD26">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE26">
+        <f>IF(L26="", "", Y26*R26*AD26)</f>
+        <v>5.2760353988571415E-2</v>
+      </c>
+      <c r="AF26">
+        <f>IF(N26="directApplication", "", AB26*T26*AD26)</f>
+        <v>9.2198718595028567E-2</v>
+      </c>
       <c r="AG26">
-        <f t="shared" si="3"/>
-        <v>5.2760353988571415E-2</v>
+        <f>IF(F26="", "", Y29*AC26*Constants!$J$2/1000)</f>
+        <v>9.4968637179428561E-4</v>
       </c>
       <c r="AH26">
-        <f t="shared" si="4"/>
-        <v>9.2198718595028567E-2</v>
+        <f>IF(F26="","",SUM(AE26:AF30)/1000)</f>
+        <v>9.7340215091214852E-3</v>
       </c>
       <c r="AI26">
-        <f>IF(F26="", "", AA29*AE26*Constants!$J$2/1000)</f>
-        <v>9.4968637179428561E-4</v>
-      </c>
-      <c r="AJ26">
-        <f t="shared" si="5"/>
-        <v>9.7340215091214852E-3</v>
-      </c>
-      <c r="AK26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>1.0683707880915772E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A24), "", 'Input Scenarios'!A24)</f>
         <v/>
@@ -6081,88 +5948,80 @@
         <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R27" t="str">
-        <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <f>IF(F27="", "",I27*(1-P27)*(1-Q27))</f>
-        <v/>
-      </c>
-      <c r="T27">
+      <c r="R27">
         <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U27">
+      <c r="S27">
         <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V27">
+      <c r="T27">
         <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W27">
+      <c r="U27">
         <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V27" t="str">
+        <f>IF(F27="","",I27*J27/6.25)</f>
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <f>IF(F27="", "", V27*(1-K27))</f>
+        <v/>
+      </c>
       <c r="X27" t="str">
-        <f>IF(F27="","",I27*J27/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <f>IF(F27="", "", X27*(1-K27))</f>
-        <v/>
-      </c>
-      <c r="Z27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>IF(ISBLANK(L27), "", $Z$26*M27)</f>
-        <v>0</v>
+        <f>IF(F27="", "", G27*W27*H27)</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>IF(ISBLANK(L27), "", $X$26*M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" t="str">
+        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <v/>
       </c>
       <c r="AB27">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(N27="directApplication", "", $AA$26*O27)</f>
+        <v>5.8671911833200001</v>
       </c>
       <c r="AC27" t="str">
-        <f>IF(F27="", "",SUM(AB27:AB31))</f>
+        <f>IF(D27="", "", _xlfn.XLOOKUP('4.6.1.3'!D27, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD27">
-        <f t="shared" ref="AD27:AD30" si="9">IF(N27="directApplication", "", $AC$26*O27)</f>
-        <v>5.8671911833200001</v>
-      </c>
-      <c r="AE27" t="str">
-        <f>IF(D27="", "", _xlfn.XLOOKUP('4.6.1.3'!D27, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF27">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG27">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <f t="shared" si="4"/>
+      <c r="AE27">
+        <f>IF(L27="", "", Y27*R27*AD27)</f>
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <f>IF(N27="directApplication", "", AB27*T27*AD27)</f>
         <v>9.2198718595028567E-2</v>
       </c>
+      <c r="AG27" t="str">
+        <f>IF(F27="", "", Y30*AC27*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH27" t="str">
+        <f>IF(F27="","",SUM(AE27:AF31)/1000)</f>
+        <v/>
+      </c>
       <c r="AI27" t="str">
-        <f>IF(F27="", "", AA30*AE27*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ27" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK27" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A25), "", 'Input Scenarios'!A25)</f>
         <v/>
@@ -6227,88 +6086,80 @@
         <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R28" t="str">
-        <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <f>IF(F28="", "",I28*(1-P28)*(1-Q28))</f>
-        <v/>
-      </c>
-      <c r="T28">
+      <c r="R28">
         <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U28">
+      <c r="S28">
         <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V28">
+      <c r="T28">
         <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W28">
+      <c r="U28">
         <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V28" t="str">
+        <f>IF(F28="","",I28*J28/6.25)</f>
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <f>IF(F28="", "", V28*(1-K28))</f>
+        <v/>
+      </c>
       <c r="X28" t="str">
-        <f>IF(F28="","",I28*J28/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y28" t="str">
-        <f>IF(F28="", "", X28*(1-K28))</f>
-        <v/>
-      </c>
-      <c r="Z28" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>IF(ISBLANK(L28), "", $Z$26*M28)</f>
-        <v>0</v>
+        <f>IF(F28="", "", G28*W28*H28)</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>IF(ISBLANK(L28), "", $X$26*M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" t="str">
+        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <v/>
       </c>
       <c r="AB28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(N28="directApplication", "", $AA$26*O28)</f>
+        <v>5.8671911833200001</v>
       </c>
       <c r="AC28" t="str">
-        <f>IF(F28="", "",SUM(AB28:AB32))</f>
+        <f>IF(D28="", "", _xlfn.XLOOKUP('4.6.1.3'!D28, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD28">
-        <f t="shared" si="9"/>
-        <v>5.8671911833200001</v>
-      </c>
-      <c r="AE28" t="str">
-        <f>IF(D28="", "", _xlfn.XLOOKUP('4.6.1.3'!D28, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF28">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AE28">
+        <f>IF(L28="", "", Y28*R28*AD28)</f>
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <f>IF(N28="directApplication", "", AB28*T28*AD28)</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" t="str">
+        <f>IF(F28="", "", Y31*AC28*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH28" t="str">
+        <f>IF(F28="","",SUM(AE28:AF32)/1000)</f>
+        <v/>
       </c>
       <c r="AI28" t="str">
-        <f>IF(F28="", "", AA31*AE28*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ28" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK28" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A26), "", 'Input Scenarios'!A26)</f>
         <v/>
@@ -6373,88 +6224,80 @@
         <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R29" t="str">
-        <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S29" t="str">
-        <f>IF(F29="", "",I29*(1-P29)*(1-Q29))</f>
-        <v/>
-      </c>
-      <c r="T29">
+      <c r="R29">
         <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U29" t="str">
+      <c r="S29" t="str">
         <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V29">
+      <c r="T29">
         <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W29">
+      <c r="U29">
         <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V29" t="str">
+        <f>IF(F29="","",I29*J29/6.25)</f>
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <f>IF(F29="", "", V29*(1-K29))</f>
+        <v/>
+      </c>
       <c r="X29" t="str">
-        <f>IF(F29="","",I29*J29/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <f>IF(F29="", "", X29*(1-K29))</f>
-        <v/>
+        <f>IF(F29="", "", G29*W29*H29)</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>IF(ISBLANK(L29), "", $X$26*M29)</f>
+        <v>302.17293647999998</v>
       </c>
       <c r="Z29" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>IF(ISBLANK(L29), "", $Z$26*M29)</f>
-        <v>302.17293647999998</v>
-      </c>
-      <c r="AB29" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>IF(N29="directApplication", "", $AA$26*O29)</f>
+        <v>0</v>
       </c>
       <c r="AC29" t="str">
-        <f>IF(F29="", "",SUM(AB29:AB33))</f>
+        <f>IF(D29="", "", _xlfn.XLOOKUP('4.6.1.3'!D29, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
       <c r="AD29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AE29" t="str">
-        <f>IF(D29="", "", _xlfn.XLOOKUP('4.6.1.3'!D29, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
-        <v/>
-      </c>
-      <c r="AF29">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AG29">
-        <f t="shared" si="3"/>
+      <c r="AE29">
+        <f>IF(L29="", "", Y29*R29*AD29)</f>
         <v>9.4968637179428566</v>
       </c>
-      <c r="AH29">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="AF29">
+        <f>IF(N29="directApplication", "", AB29*T29*AD29)</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" t="str">
+        <f>IF(F29="", "", Y32*AC29*Constants!$J$2/1000)</f>
+        <v/>
+      </c>
+      <c r="AH29" t="str">
+        <f>IF(F29="","",SUM(AE29:AF33)/1000)</f>
+        <v/>
       </c>
       <c r="AI29" t="str">
-        <f>IF(F29="", "", AA32*AE29*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ29" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK29" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A27), "", 'Input Scenarios'!A27)</f>
         <v/>
@@ -6513,110 +6356,102 @@
         <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R30" s="11" t="str">
-        <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S30" s="11" t="str">
-        <f>IF(F30="", "",I30*(1-P30)*(1-Q30))</f>
+      <c r="R30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T30" t="str">
-        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U30" t="str">
-        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V30" t="str">
         <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W30" t="str">
+      <c r="U30" t="str">
         <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X30" s="11" t="str">
+      <c r="V30" s="11" t="str">
         <f>IF(F30="","",I30*J30/6.25)</f>
         <v/>
       </c>
+      <c r="W30" s="11" t="str">
+        <f>IF(F30="", "", V30*(1-K30))</f>
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <f>IF(F30="", "", G30*W30*H30)</f>
+        <v/>
+      </c>
       <c r="Y30" s="11" t="str">
-        <f>IF(F30="", "", X30*(1-K30))</f>
+        <f>IF(ISBLANK(L30), "", $X$26*M30)</f>
         <v/>
       </c>
       <c r="Z30" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
         <v/>
       </c>
       <c r="AA30" s="11" t="str">
-        <f>IF(ISBLANK(L30), "", $Z$26*M30)</f>
+        <f>IF(F30="", "",SUM(Z30:Z34))</f>
         <v/>
       </c>
       <c r="AB30" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC30" s="11" t="str">
-        <f>IF(F30="", "",SUM(AB30:AB34))</f>
-        <v/>
-      </c>
-      <c r="AD30" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="AE30" t="str">
+        <f>IF(N30="directApplication", "", $AA$26*O30)</f>
+        <v/>
+      </c>
+      <c r="AC30" t="str">
         <f>IF(D30="", "", _xlfn.XLOOKUP('4.6.1.3'!D30, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
         <v/>
       </c>
-      <c r="AF30">
+      <c r="AD30">
         <f>Constants!$J$2</f>
         <v>1.5714285714285714</v>
       </c>
+      <c r="AE30" t="str">
+        <f>IF(L30="", "", Y30*R30*AD30)</f>
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <f>IF(N30="directApplication", "", AB30*T30*AD30)</f>
+        <v/>
+      </c>
       <c r="AG30" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(F30="", "", Y33*AC30*Constants!$J$2/1000)</f>
         <v/>
       </c>
       <c r="AH30" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(F30="","",SUM(AE30:AF34)/1000)</f>
         <v/>
       </c>
       <c r="AI30" t="str">
-        <f>IF(F30="", "", AA33*AE30*Constants!$J$2/1000)</f>
-        <v/>
-      </c>
-      <c r="AJ30" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK30" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="U11:U30" formula="1"/>
+    <ignoredError sqref="S11:S30" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62384FC7-4E95-334D-BAFB-568C04780500}">
-  <dimension ref="A2:AJ30"/>
+  <dimension ref="A2:AH30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="27" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -6669,7 +6504,7 @@
         <v>52</v>
       </c>
       <c r="S4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="T4" t="s">
         <v>52</v>
@@ -6678,10 +6513,10 @@
         <v>52</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="W4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="X4" t="s">
         <v>59</v>
@@ -6692,36 +6527,24 @@
       <c r="Z4" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="K5" t="s">
         <v>0</v>
       </c>
       <c r="Q5" t="s">
         <v>0</v>
       </c>
-      <c r="R5" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="Z5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="AC6" t="s">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AA6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -6773,14 +6596,8 @@
       <c r="Q8" t="s">
         <v>47</v>
       </c>
-      <c r="R8" t="s">
-        <v>51</v>
-      </c>
-      <c r="S8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -6831,64 +6648,58 @@
         <v>34</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AJ10" s="10" t="s">
+      <c r="AH10" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A8), "", 'Input Scenarios'!A8)</f>
         <v>NSW</v>
@@ -6954,83 +6765,75 @@
         <v>0.18</v>
       </c>
       <c r="R11">
-        <f>IF(F11="", "",_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.39</v>
-      </c>
-      <c r="S11">
-        <f>IF(F11="", "",I11*(1-P11)*(1-Q11))</f>
-        <v>1.4103999999999995E-2</v>
-      </c>
-      <c r="T11">
         <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U11">
+      <c r="S11">
         <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V11">
+      <c r="T11">
         <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W11">
+      <c r="U11">
         <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X11">
+      <c r="V11">
         <f>IF(F11="","",I11*J11/6.25)</f>
         <v>2.6144000000000002E-3</v>
       </c>
+      <c r="W11">
+        <f>IF(F11="", "", V11*(1-K11))</f>
+        <v>1.6993600000000002E-3</v>
+      </c>
+      <c r="X11">
+        <f>IF(F11="", "", G11*W11*H11)</f>
+        <v>424.84000000000003</v>
+      </c>
       <c r="Y11">
-        <f>IF(F11="", "", X11*(1-K11))</f>
-        <v>1.6993600000000002E-3</v>
+        <f>IF(ISBLANK(L11), "", $X$11*M11)</f>
+        <v>42.484000000000009</v>
       </c>
       <c r="Z11">
-        <f>IF(F11="", "", G11*Y11*H11)</f>
-        <v>424.84000000000003</v>
+        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <v>29.69631600000001</v>
       </c>
       <c r="AA11">
-        <f>IF(ISBLANK(L11), "", $Z$11*M11)</f>
-        <v>42.484000000000009</v>
+        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <v>186.67469600000001</v>
       </c>
       <c r="AB11">
-        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", AA11*(1-T11-U11))</f>
-        <v>29.69631600000001</v>
+        <f>IF(N11="directApplication", "", $AA$11*O11)</f>
+        <v>28.001204400000002</v>
       </c>
       <c r="AC11">
-        <f>IF(F11="", "",SUM(AB11:AB15))</f>
-        <v>186.67469600000001</v>
+        <f>IF(L11="", "",IF( L11="pastureRangeAndPaddock",Y11*Constants!$K$2, Y11*S11))</f>
+        <v>12.745200000000002</v>
       </c>
       <c r="AD11">
-        <f>IF(N11="directApplication", "", $AC$11*O11)</f>
-        <v>28.001204400000002</v>
+        <f>IF(OR(N11="", N11="directApplication"), "",AB11*U11)</f>
+        <v>5.6002408800000012</v>
       </c>
       <c r="AE11">
-        <f>IF(L11="", "",IF( L11="pastureRangeAndPaddock",AA11*Constants!$K$2, AA11*U11))</f>
-        <v>12.745200000000002</v>
+        <f>IF(F11="", "", SUM(AC11:AD15))</f>
+        <v>116.72818872000002</v>
       </c>
       <c r="AF11">
-        <f>IF(OR(N11="", N11="directApplication"), "",AD11*W11)</f>
-        <v>5.6002408800000012</v>
-      </c>
-      <c r="AG11">
-        <f>IF(F11="", "", SUM(AE11:AF15))</f>
-        <v>116.72818872000002</v>
-      </c>
-      <c r="AH11">
         <f>IF(C11="", "", _xlfn.XLOOKUP(C11,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
         <v>1.8E-3</v>
       </c>
-      <c r="AI11">
-        <f>IF(AG11="","",Constants!$J$2)</f>
+      <c r="AG11">
+        <f>IF(AE11="","",Constants!$J$2)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AJ11">
-        <f>IF(AG11="", "", (AG11*AH11*AI11)/1000)</f>
+      <c r="AH11">
+        <f>IF(AE11="", "", (AE11*AF11*AG11)/1000)</f>
         <v>3.3017401952228578E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A9), "", 'Input Scenarios'!A9)</f>
         <v/>
@@ -7095,84 +6898,76 @@
         <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R12" t="str">
-        <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <f>IF(F12="", "",I12*(1-P12)*(1-Q12))</f>
-        <v/>
-      </c>
-      <c r="T12">
+      <c r="R12">
         <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U12">
+      <c r="S12">
         <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V12">
+      <c r="T12">
         <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W12">
+      <c r="U12">
         <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V12" t="str">
+        <f>IF(F12="","",I12*J12/6.25)</f>
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <f>IF(F12="", "", V12*(1-K12))</f>
+        <v/>
+      </c>
       <c r="X12" t="str">
-        <f>IF(F12="","",I12*J12/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <f>IF(F12="", "", X12*(1-K12))</f>
-        <v/>
-      </c>
-      <c r="Z12" t="str">
-        <f t="shared" ref="Z12:Z30" si="0">IF(F12="", "", G12*Y12*H12)</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>IF(ISBLANK(L12), "", $Z$11*M12)</f>
+        <f>IF(F12="", "", G12*W12*H12)</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>IF(ISBLANK(L12), "", $X$11*M12)</f>
         <v>84.968000000000018</v>
       </c>
+      <c r="Z12">
+        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <v>80.634632000000011</v>
+      </c>
+      <c r="AA12" t="str">
+        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <v/>
+      </c>
       <c r="AB12">
-        <f t="shared" ref="AB12:AB30" si="1">IF(OR(L12="", L12="pastureRangeAndPaddock"), "", AA12*(1-T12-U12))</f>
-        <v>80.634632000000011</v>
-      </c>
-      <c r="AC12" t="str">
-        <f>IF(F12="", "",SUM(AB12:AB16))</f>
-        <v/>
+        <f>IF(N12="directApplication", "", $AA$11*O12)</f>
+        <v>37.334939200000001</v>
+      </c>
+      <c r="AC12">
+        <f>IF(L12="", "",IF( L12="pastureRangeAndPaddock",Y12*Constants!$K$2, Y12*S12))</f>
+        <v>4.2484000000000011</v>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD12:AD15" si="2">IF(N12="directApplication", "", $AC$11*O12)</f>
-        <v>37.334939200000001</v>
-      </c>
-      <c r="AE12">
-        <f>IF(L12="", "",IF( L12="pastureRangeAndPaddock",AA12*Constants!$K$2, AA12*U12))</f>
-        <v>4.2484000000000011</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" ref="AF12:AF30" si="3">IF(OR(N12="", N12="directApplication"), "",AD12*W12)</f>
+        <f>IF(OR(N12="", N12="directApplication"), "",AB12*U12)</f>
         <v>7.4669878400000007</v>
       </c>
+      <c r="AE12" t="str">
+        <f>IF(F12="", "", SUM(AC12:AD16))</f>
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <f>IF(C12="", "", _xlfn.XLOOKUP(C12,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
       <c r="AG12" t="str">
-        <f t="shared" ref="AG12:AG30" si="4">IF(F12="", "", SUM(AE12:AF16))</f>
+        <f>IF(AE12="","",Constants!$J$2)</f>
         <v/>
       </c>
       <c r="AH12" t="str">
-        <f>IF(C12="", "", _xlfn.XLOOKUP(C12,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI12" t="str">
-        <f>IF(AG12="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ12" t="str">
-        <f t="shared" ref="AJ12:AJ30" si="5">IF(AG12="", "", (AG12*AH12*AI12)/1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+        <f t="shared" ref="AH12:AH30" si="0">IF(AE12="", "", (AE12*AF12*AG12)/1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A10), "", 'Input Scenarios'!A10)</f>
         <v/>
@@ -7237,84 +7032,76 @@
         <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R13" t="str">
-        <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S13" t="str">
-        <f>IF(F13="", "",I13*(1-P13)*(1-Q13))</f>
-        <v/>
-      </c>
-      <c r="T13">
+      <c r="R13">
         <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U13">
+      <c r="S13">
         <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V13">
+      <c r="T13">
         <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W13">
+      <c r="U13">
         <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V13" t="str">
+        <f>IF(F13="","",I13*J13/6.25)</f>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f>IF(F13="", "", V13*(1-K13))</f>
+        <v/>
+      </c>
       <c r="X13" t="str">
-        <f>IF(F13="","",I13*J13/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <f>IF(F13="", "", X13*(1-K13))</f>
-        <v/>
-      </c>
-      <c r="Z13" t="str">
+        <f>IF(F13="", "", G13*W13*H13)</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>IF(ISBLANK(L13), "", $X$11*M13)</f>
+        <v>127.452</v>
+      </c>
+      <c r="Z13">
+        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <v>76.343747999999991</v>
+      </c>
+      <c r="AA13" t="str">
+        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>IF(N13="directApplication", "", $AA$11*O13)</f>
+        <v>46.668674000000003</v>
+      </c>
+      <c r="AC13">
+        <f>IF(L13="", "",IF( L13="pastureRangeAndPaddock",Y13*Constants!$K$2, Y13*S13))</f>
+        <v>50.980800000000002</v>
+      </c>
+      <c r="AD13">
+        <f>IF(OR(N13="", N13="directApplication"), "",AB13*U13)</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" t="str">
+        <f>IF(F13="", "", SUM(AC13:AD17))</f>
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <f>IF(C13="", "", _xlfn.XLOOKUP(C13,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <f>IF(AE13="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA13">
-        <f>IF(ISBLANK(L13), "", $Z$11*M13)</f>
-        <v>127.452</v>
-      </c>
-      <c r="AB13">
-        <f t="shared" si="1"/>
-        <v>76.343747999999991</v>
-      </c>
-      <c r="AC13" t="str">
-        <f>IF(F13="", "",SUM(AB13:AB17))</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f t="shared" si="2"/>
-        <v>46.668674000000003</v>
-      </c>
-      <c r="AE13">
-        <f>IF(L13="", "",IF( L13="pastureRangeAndPaddock",AA13*Constants!$K$2, AA13*U13))</f>
-        <v>50.980800000000002</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG13" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH13" t="str">
-        <f>IF(C13="", "", _xlfn.XLOOKUP(C13,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI13" t="str">
-        <f>IF(AG13="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ13" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A11), "", 'Input Scenarios'!A11)</f>
         <v/>
@@ -7379,84 +7166,76 @@
         <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R14" t="str">
-        <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S14" t="str">
-        <f>IF(F14="", "",I14*(1-P14)*(1-Q14))</f>
-        <v/>
-      </c>
-      <c r="T14">
+      <c r="R14">
         <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U14" t="str">
+      <c r="S14" t="str">
         <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V14">
+      <c r="T14">
         <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W14">
+      <c r="U14">
         <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V14" t="str">
+        <f>IF(F14="","",I14*J14/6.25)</f>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f>IF(F14="", "", V14*(1-K14))</f>
+        <v/>
+      </c>
       <c r="X14" t="str">
-        <f>IF(F14="","",I14*J14/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <f>IF(F14="", "", X14*(1-K14))</f>
-        <v/>
+        <f>IF(F14="", "", G14*W14*H14)</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>IF(ISBLANK(L14), "", $X$11*M14)</f>
+        <v>169.93600000000004</v>
       </c>
       <c r="Z14" t="str">
+        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>IF(N14="directApplication", "", $AA$11*O14)</f>
+        <v>31.734698320000003</v>
+      </c>
+      <c r="AC14">
+        <f>IF(L14="", "",IF( L14="pastureRangeAndPaddock",Y14*Constants!$K$2, Y14*S14))</f>
+        <v>35.686560000000007</v>
+      </c>
+      <c r="AD14">
+        <f>IF(OR(N14="", N14="directApplication"), "",AB14*U14)</f>
+        <v>0</v>
+      </c>
+      <c r="AE14" t="str">
+        <f>IF(F14="", "", SUM(AC14:AD18))</f>
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <f>IF(C14="", "", _xlfn.XLOOKUP(C14,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <f>IF(AE14="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA14">
-        <f>IF(ISBLANK(L14), "", $Z$11*M14)</f>
-        <v>169.93600000000004</v>
-      </c>
-      <c r="AB14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC14" t="str">
-        <f>IF(F14="", "",SUM(AB14:AB18))</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="2"/>
-        <v>31.734698320000003</v>
-      </c>
-      <c r="AE14">
-        <f>IF(L14="", "",IF( L14="pastureRangeAndPaddock",AA14*Constants!$K$2, AA14*U14))</f>
-        <v>35.686560000000007</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH14" t="str">
-        <f>IF(C14="", "", _xlfn.XLOOKUP(C14,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI14" t="str">
-        <f>IF(AG14="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A12), "", 'Input Scenarios'!A12)</f>
         <v/>
@@ -7515,84 +7294,76 @@
         <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R15" s="11" t="str">
-        <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S15" s="11" t="str">
-        <f>IF(F15="", "",I15*(1-P15)*(1-Q15))</f>
+      <c r="R15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T15" t="str">
-        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V15" t="str">
         <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W15" t="str">
+      <c r="U15" t="str">
         <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X15" s="11" t="str">
+      <c r="V15" s="11" t="str">
         <f>IF(F15="","",I15*J15/6.25)</f>
         <v/>
       </c>
+      <c r="W15" s="11" t="str">
+        <f>IF(F15="", "", V15*(1-K15))</f>
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <f>IF(F15="", "", G15*W15*H15)</f>
+        <v/>
+      </c>
       <c r="Y15" s="11" t="str">
-        <f>IF(F15="", "", X15*(1-K15))</f>
+        <f>IF(ISBLANK(L15), "", $X$11*M15)</f>
         <v/>
       </c>
       <c r="Z15" t="str">
+        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
+        <v/>
+      </c>
+      <c r="AA15" s="11" t="str">
+        <f>IF(F15="", "",SUM(Z15:Z19))</f>
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <f>IF(N15="directApplication", "", $AA$11*O15)</f>
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <f>IF(L15="", "",IF( L15="pastureRangeAndPaddock",Y15*Constants!$K$2, Y15*S15))</f>
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <f>IF(OR(N15="", N15="directApplication"), "",AB15*U15)</f>
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <f>IF(F15="", "", SUM(AC15:AD19))</f>
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <f>IF(C15="", "", _xlfn.XLOOKUP(C15,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <f>IF(AE15="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH15" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA15" s="11" t="str">
-        <f>IF(ISBLANK(L15), "", $Z$11*M15)</f>
-        <v/>
-      </c>
-      <c r="AB15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC15" s="11" t="str">
-        <f>IF(F15="", "",SUM(AB15:AB19))</f>
-        <v/>
-      </c>
-      <c r="AD15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AE15" t="str">
-        <f>IF(L15="", "",IF( L15="pastureRangeAndPaddock",AA15*Constants!$K$2, AA15*U15))</f>
-        <v/>
-      </c>
-      <c r="AF15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AG15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH15" t="str">
-        <f>IF(C15="", "", _xlfn.XLOOKUP(C15,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI15" t="str">
-        <f>IF(AG15="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A13), "", 'Input Scenarios'!A13)</f>
         <v>QLD</v>
@@ -7658,83 +7429,75 @@
         <v>0.18</v>
       </c>
       <c r="R16">
-        <f>IF(F16="", "",_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S16">
-        <f>IF(F16="", "",I16*(1-P16)*(1-Q16))</f>
-        <v>1.6891999999999997E-2</v>
-      </c>
-      <c r="T16">
         <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U16">
+      <c r="S16">
         <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V16">
+      <c r="T16">
         <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W16">
+      <c r="U16">
         <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X16">
+      <c r="V16">
         <f>IF(F16="","",I16*J16/6.25)</f>
         <v>3.1312000000000002E-3</v>
       </c>
+      <c r="W16">
+        <f>IF(F16="", "", V16*(1-K16))</f>
+        <v>2.1292159999999997E-3</v>
+      </c>
+      <c r="X16">
+        <f>IF(F16="", "", G16*W16*H16)</f>
+        <v>598.84199999999987</v>
+      </c>
       <c r="Y16">
-        <f>IF(F16="", "", X16*(1-K16))</f>
-        <v>2.1292159999999997E-3</v>
+        <f>IF(ISBLANK(L16), "", $X$16*M16)</f>
+        <v>239.53679999999997</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="0"/>
-        <v>598.84199999999987</v>
+        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <v>167.4362232</v>
       </c>
       <c r="AA16">
-        <f>IF(ISBLANK(L16), "", $Z$16*M16)</f>
-        <v>239.53679999999997</v>
+        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <v>409.66781219999996</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="1"/>
-        <v>167.4362232</v>
+        <f>IF(N16="directApplication", "", $AA$16*O16)</f>
+        <v>81.933562440000003</v>
       </c>
       <c r="AC16">
-        <f>IF(F16="", "",SUM(AB16:AB20))</f>
-        <v>409.66781219999996</v>
+        <f>IF(L16="", "",IF( L16="pastureRangeAndPaddock",Y16*Constants!$K$2, Y16*S16))</f>
+        <v>71.861039999999988</v>
       </c>
       <c r="AD16">
-        <f>IF(N16="directApplication", "", $AC$16*O16)</f>
-        <v>81.933562440000003</v>
+        <f>IF(OR(N16="", N16="directApplication"), "",AB16*U16)</f>
+        <v>16.386712488000001</v>
       </c>
       <c r="AE16">
-        <f>IF(L16="", "",IF( L16="pastureRangeAndPaddock",AA16*Constants!$K$2, AA16*U16))</f>
-        <v>71.861039999999988</v>
+        <f>IF(F16="", "", SUM(AC16:AD20))</f>
+        <v>178.19681509799997</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="3"/>
-        <v>16.386712488000001</v>
-      </c>
-      <c r="AG16">
-        <f t="shared" si="4"/>
-        <v>178.19681509799997</v>
-      </c>
-      <c r="AH16">
         <f>IF(C16="", "", _xlfn.XLOOKUP(C16,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AI16">
-        <f>IF(AG16="","",Constants!$J$2)</f>
+      <c r="AG16">
+        <f>IF(AE16="","",Constants!$J$2)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AJ16">
-        <f t="shared" si="5"/>
+      <c r="AH16">
+        <f t="shared" si="0"/>
         <v>1.9601649660779996E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A14), "", 'Input Scenarios'!A14)</f>
         <v/>
@@ -7799,84 +7562,76 @@
         <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R17" t="str">
-        <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <f>IF(F17="", "",I17*(1-P17)*(1-Q17))</f>
-        <v/>
-      </c>
-      <c r="T17">
+      <c r="R17">
         <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U17">
+      <c r="S17">
         <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V17">
+      <c r="T17">
         <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W17">
+      <c r="U17">
         <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V17" t="str">
+        <f>IF(F17="","",I17*J17/6.25)</f>
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <f>IF(F17="", "", V17*(1-K17))</f>
+        <v/>
+      </c>
       <c r="X17" t="str">
-        <f>IF(F17="","",I17*J17/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y17" t="str">
-        <f>IF(F17="", "", X17*(1-K17))</f>
-        <v/>
-      </c>
-      <c r="Z17" t="str">
+        <f>IF(F17="", "", G17*W17*H17)</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>IF(ISBLANK(L17), "", $X$16*M17)</f>
+        <v>179.65259999999995</v>
+      </c>
+      <c r="Z17">
+        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <v>170.49031739999995</v>
+      </c>
+      <c r="AA17" t="str">
+        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>IF(N17="directApplication", "", $AA$16*O17)</f>
+        <v>102.41695304999999</v>
+      </c>
+      <c r="AC17">
+        <f>IF(L17="", "",IF( L17="pastureRangeAndPaddock",Y17*Constants!$K$2, Y17*S17))</f>
+        <v>8.9826299999999986</v>
+      </c>
+      <c r="AD17">
+        <f>IF(OR(N17="", N17="directApplication"), "",AB17*U17)</f>
+        <v>20.483390610000001</v>
+      </c>
+      <c r="AE17" t="str">
+        <f>IF(F17="", "", SUM(AC17:AD21))</f>
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <f>IF(C17="", "", _xlfn.XLOOKUP(C17,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <f>IF(AE17="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA17">
-        <f>IF(ISBLANK(L17), "", $Z$16*M17)</f>
-        <v>179.65259999999995</v>
-      </c>
-      <c r="AB17">
-        <f t="shared" si="1"/>
-        <v>170.49031739999995</v>
-      </c>
-      <c r="AC17" t="str">
-        <f>IF(F17="", "",SUM(AB17:AB21))</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f t="shared" ref="AD17:AD20" si="6">IF(N17="directApplication", "", $AC$16*O17)</f>
-        <v>102.41695304999999</v>
-      </c>
-      <c r="AE17">
-        <f>IF(L17="", "",IF( L17="pastureRangeAndPaddock",AA17*Constants!$K$2, AA17*U17))</f>
-        <v>8.9826299999999986</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="3"/>
-        <v>20.483390610000001</v>
-      </c>
-      <c r="AG17" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH17" t="str">
-        <f>IF(C17="", "", _xlfn.XLOOKUP(C17,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI17" t="str">
-        <f>IF(AG17="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A15), "", 'Input Scenarios'!A15)</f>
         <v/>
@@ -7941,84 +7696,76 @@
         <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R18" t="str">
-        <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S18" t="str">
-        <f>IF(F18="", "",I18*(1-P18)*(1-Q18))</f>
-        <v/>
-      </c>
-      <c r="T18">
+      <c r="R18">
         <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U18">
+      <c r="S18">
         <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V18">
+      <c r="T18">
         <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W18">
+      <c r="U18">
         <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V18" t="str">
+        <f>IF(F18="","",I18*J18/6.25)</f>
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <f>IF(F18="", "", V18*(1-K18))</f>
+        <v/>
+      </c>
       <c r="X18" t="str">
-        <f>IF(F18="","",I18*J18/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y18" t="str">
-        <f>IF(F18="", "", X18*(1-K18))</f>
-        <v/>
-      </c>
-      <c r="Z18" t="str">
+        <f>IF(F18="", "", G18*W18*H18)</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>IF(ISBLANK(L18), "", $X$16*M18)</f>
+        <v>119.76839999999999</v>
+      </c>
+      <c r="Z18">
+        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <v>71.74127159999999</v>
+      </c>
+      <c r="AA18" t="str">
+        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>IF(N18="directApplication", "", $AA$16*O18)</f>
+        <v>81.933562440000003</v>
+      </c>
+      <c r="AC18">
+        <f>IF(L18="", "",IF( L18="pastureRangeAndPaddock",Y18*Constants!$K$2, Y18*S18))</f>
+        <v>47.907359999999997</v>
+      </c>
+      <c r="AD18">
+        <f>IF(OR(N18="", N18="directApplication"), "",AB18*U18)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" t="str">
+        <f>IF(F18="", "", SUM(AC18:AD22))</f>
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <f>IF(C18="", "", _xlfn.XLOOKUP(C18,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <f>IF(AE18="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA18">
-        <f>IF(ISBLANK(L18), "", $Z$16*M18)</f>
-        <v>119.76839999999999</v>
-      </c>
-      <c r="AB18">
-        <f t="shared" si="1"/>
-        <v>71.74127159999999</v>
-      </c>
-      <c r="AC18" t="str">
-        <f>IF(F18="", "",SUM(AB18:AB22))</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f t="shared" si="6"/>
-        <v>81.933562440000003</v>
-      </c>
-      <c r="AE18">
-        <f>IF(L18="", "",IF( L18="pastureRangeAndPaddock",AA18*Constants!$K$2, AA18*U18))</f>
-        <v>47.907359999999997</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH18" t="str">
-        <f>IF(C18="", "", _xlfn.XLOOKUP(C18,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI18" t="str">
-        <f>IF(AG18="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ18" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A16), "", 'Input Scenarios'!A16)</f>
         <v/>
@@ -8083,84 +7830,76 @@
         <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R19" t="str">
-        <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <f>IF(F19="", "",I19*(1-P19)*(1-Q19))</f>
-        <v/>
-      </c>
-      <c r="T19">
+      <c r="R19">
         <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U19" t="str">
+      <c r="S19" t="str">
         <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V19">
+      <c r="T19">
         <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W19">
+      <c r="U19">
         <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V19" t="str">
+        <f>IF(F19="","",I19*J19/6.25)</f>
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <f>IF(F19="", "", V19*(1-K19))</f>
+        <v/>
+      </c>
       <c r="X19" t="str">
-        <f>IF(F19="","",I19*J19/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y19" t="str">
-        <f>IF(F19="", "", X19*(1-K19))</f>
-        <v/>
+        <f>IF(F19="", "", G19*W19*H19)</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>IF(ISBLANK(L19), "", $X$16*M19)</f>
+        <v>59.884199999999993</v>
       </c>
       <c r="Z19" t="str">
+        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>IF(N19="directApplication", "", $AA$16*O19)</f>
+        <v>102.41695304999999</v>
+      </c>
+      <c r="AC19">
+        <f>IF(L19="", "",IF( L19="pastureRangeAndPaddock",Y19*Constants!$K$2, Y19*S19))</f>
+        <v>12.575681999999999</v>
+      </c>
+      <c r="AD19">
+        <f>IF(OR(N19="", N19="directApplication"), "",AB19*U19)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" t="str">
+        <f>IF(F19="", "", SUM(AC19:AD23))</f>
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <f>IF(C19="", "", _xlfn.XLOOKUP(C19,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <f>IF(AE19="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH19" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA19">
-        <f>IF(ISBLANK(L19), "", $Z$16*M19)</f>
-        <v>59.884199999999993</v>
-      </c>
-      <c r="AB19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC19" t="str">
-        <f>IF(F19="", "",SUM(AB19:AB23))</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f t="shared" si="6"/>
-        <v>102.41695304999999</v>
-      </c>
-      <c r="AE19">
-        <f>IF(L19="", "",IF( L19="pastureRangeAndPaddock",AA19*Constants!$K$2, AA19*U19))</f>
-        <v>12.575681999999999</v>
-      </c>
-      <c r="AF19">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH19" t="str">
-        <f>IF(C19="", "", _xlfn.XLOOKUP(C19,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI19" t="str">
-        <f>IF(AG19="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ19" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A17), "", 'Input Scenarios'!A17)</f>
         <v/>
@@ -8219,84 +7958,76 @@
         <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R20" s="11" t="str">
-        <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S20" s="11" t="str">
-        <f>IF(F20="", "",I20*(1-P20)*(1-Q20))</f>
+      <c r="R20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T20" t="str">
-        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U20" t="str">
-        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V20" t="str">
         <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W20" t="str">
+      <c r="U20" t="str">
         <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X20" s="11" t="str">
+      <c r="V20" s="11" t="str">
         <f>IF(F20="","",I20*J20/6.25)</f>
         <v/>
       </c>
+      <c r="W20" s="11" t="str">
+        <f>IF(F20="", "", V20*(1-K20))</f>
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <f>IF(F20="", "", G20*W20*H20)</f>
+        <v/>
+      </c>
       <c r="Y20" s="11" t="str">
-        <f>IF(F20="", "", X20*(1-K20))</f>
+        <f>IF(ISBLANK(L20), "", $X$16*M20)</f>
         <v/>
       </c>
       <c r="Z20" t="str">
+        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
+        <v/>
+      </c>
+      <c r="AA20" s="11" t="str">
+        <f>IF(F20="", "",SUM(Z20:Z24))</f>
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <f>IF(N20="directApplication", "", $AA$16*O20)</f>
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <f>IF(L20="", "",IF( L20="pastureRangeAndPaddock",Y20*Constants!$K$2, Y20*S20))</f>
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <f>IF(OR(N20="", N20="directApplication"), "",AB20*U20)</f>
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <f>IF(F20="", "", SUM(AC20:AD24))</f>
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <f>IF(C20="", "", _xlfn.XLOOKUP(C20,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <f>IF(AE20="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA20" s="11" t="str">
-        <f>IF(ISBLANK(L20), "", $Z$16*M20)</f>
-        <v/>
-      </c>
-      <c r="AB20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC20" s="11" t="str">
-        <f>IF(F20="", "",SUM(AB20:AB24))</f>
-        <v/>
-      </c>
-      <c r="AD20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AE20" t="str">
-        <f>IF(L20="", "",IF( L20="pastureRangeAndPaddock",AA20*Constants!$K$2, AA20*U20))</f>
-        <v/>
-      </c>
-      <c r="AF20" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AG20" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH20" t="str">
-        <f>IF(C20="", "", _xlfn.XLOOKUP(C20,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI20" t="str">
-        <f>IF(AG20="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ20" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A18), "", 'Input Scenarios'!A18)</f>
         <v>TAS</v>
@@ -8362,83 +8093,75 @@
         <v>0.15</v>
       </c>
       <c r="R21">
-        <f>IF(F21="", "",_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S21">
-        <f>IF(F21="", "",I21*(1-P21)*(1-Q21))</f>
-        <v>1.5809999999999994E-2</v>
-      </c>
-      <c r="T21">
         <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U21">
+      <c r="S21">
         <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V21">
+      <c r="T21">
         <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W21">
+      <c r="U21">
         <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X21">
+      <c r="V21">
         <f>IF(F21="","",I21*J21/6.25)</f>
         <v>3.4223999999999999E-3</v>
       </c>
+      <c r="W21">
+        <f>IF(F21="", "", V21*(1-K21))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X21">
+        <f>IF(F21="", "", G21*W21*H21)</f>
+        <v>671.06552673600004</v>
+      </c>
       <c r="Y21">
-        <f>IF(F21="", "", X21*(1-K21))</f>
-        <v>1.813872E-3</v>
+        <f>IF(ISBLANK(L21), "", $X$21*M21)</f>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="0"/>
-        <v>671.06552673600004</v>
+        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <f>IF(ISBLANK(L21), "", $Z$21*M21)</f>
-        <v>0</v>
+        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <v>573.15706638521772</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(N21="directApplication", "", $AA$21*O21)</f>
+        <v>194.87340257097404</v>
       </c>
       <c r="AC21">
-        <f>IF(F21="", "",SUM(AB21:AB25))</f>
-        <v>573.15706638521772</v>
+        <f>IF(L21="", "",IF( L21="pastureRangeAndPaddock",Y21*Constants!$K$2, Y21*S21))</f>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <f>IF(N21="directApplication", "", $AC$21*O21)</f>
-        <v>194.87340257097404</v>
+        <f>IF(OR(N21="", N21="directApplication"), "",AB21*U21)</f>
+        <v>38.974680514194809</v>
       </c>
       <c r="AE21">
-        <f>IF(L21="", "",IF( L21="pastureRangeAndPaddock",AA21*Constants!$K$2, AA21*U21))</f>
-        <v>0</v>
+        <f>IF(F21="", "", SUM(AC21:AD25))</f>
+        <v>152.04385324499694</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="3"/>
-        <v>38.974680514194809</v>
-      </c>
-      <c r="AG21">
-        <f t="shared" si="4"/>
-        <v>152.04385324499694</v>
-      </c>
-      <c r="AH21">
         <f>IF(C21="", "", _xlfn.XLOOKUP(C21,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="AI21">
-        <f>IF(AG21="","",Constants!$J$2)</f>
+      <c r="AG21">
+        <f>IF(AE21="","",Constants!$J$2)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AJ21">
-        <f t="shared" si="5"/>
+      <c r="AH21">
+        <f t="shared" si="0"/>
         <v>1.4096637250857571E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A19), "", 'Input Scenarios'!A19)</f>
         <v/>
@@ -8503,84 +8226,76 @@
         <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R22" t="str">
-        <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <f>IF(F22="", "",I22*(1-P22)*(1-Q22))</f>
-        <v/>
-      </c>
-      <c r="T22">
+      <c r="R22">
         <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U22">
+      <c r="S22">
         <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V22">
+      <c r="T22">
         <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W22">
+      <c r="U22">
         <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V22" t="str">
+        <f>IF(F22="","",I22*J22/6.25)</f>
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <f>IF(F22="", "", V22*(1-K22))</f>
+        <v/>
+      </c>
       <c r="X22" t="str">
-        <f>IF(F22="","",I22*J22/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <f>IF(F22="", "", X22*(1-K22))</f>
-        <v/>
-      </c>
-      <c r="Z22" t="str">
+        <f>IF(F22="", "", G22*W22*H22)</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>IF(ISBLANK(L22), "", $X$21*M22)</f>
+        <v>603.9589740624001</v>
+      </c>
+      <c r="Z22">
+        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <v>573.15706638521772</v>
+      </c>
+      <c r="AA22" t="str">
+        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>IF(N22="directApplication", "", $AA$21*O22)</f>
+        <v>343.89423983113062</v>
+      </c>
+      <c r="AC22">
+        <f>IF(L22="", "",IF( L22="pastureRangeAndPaddock",Y22*Constants!$K$2, Y22*S22))</f>
+        <v>30.197948703120005</v>
+      </c>
+      <c r="AD22">
+        <f>IF(OR(N22="", N22="directApplication"), "",AB22*U22)</f>
+        <v>68.778847966226124</v>
+      </c>
+      <c r="AE22" t="str">
+        <f>IF(F22="", "", SUM(AC22:AD26))</f>
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <f>IF(C22="", "", _xlfn.XLOOKUP(C22,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <f>IF(AE22="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA22">
-        <f>IF(ISBLANK(L22), "", $Z$21*M22)</f>
-        <v>603.9589740624001</v>
-      </c>
-      <c r="AB22">
-        <f t="shared" si="1"/>
-        <v>573.15706638521772</v>
-      </c>
-      <c r="AC22" t="str">
-        <f>IF(F22="", "",SUM(AB22:AB26))</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f t="shared" ref="AD22:AD25" si="7">IF(N22="directApplication", "", $AC$21*O22)</f>
-        <v>343.89423983113062</v>
-      </c>
-      <c r="AE22">
-        <f>IF(L22="", "",IF( L22="pastureRangeAndPaddock",AA22*Constants!$K$2, AA22*U22))</f>
-        <v>30.197948703120005</v>
-      </c>
-      <c r="AF22">
-        <f t="shared" si="3"/>
-        <v>68.778847966226124</v>
-      </c>
-      <c r="AG22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH22" t="str">
-        <f>IF(C22="", "", _xlfn.XLOOKUP(C22,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI22" t="str">
-        <f>IF(AG22="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ22" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A20), "", 'Input Scenarios'!A20)</f>
         <v/>
@@ -8645,84 +8360,76 @@
         <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R23" t="str">
-        <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <f>IF(F23="", "",I23*(1-P23)*(1-Q23))</f>
-        <v/>
-      </c>
-      <c r="T23">
+      <c r="R23">
         <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U23">
+      <c r="S23">
         <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V23">
+      <c r="T23">
         <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W23">
+      <c r="U23">
         <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V23" t="str">
+        <f>IF(F23="","",I23*J23/6.25)</f>
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <f>IF(F23="", "", V23*(1-K23))</f>
+        <v/>
+      </c>
       <c r="X23" t="str">
-        <f>IF(F23="","",I23*J23/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <f>IF(F23="", "", X23*(1-K23))</f>
-        <v/>
-      </c>
-      <c r="Z23" t="str">
+        <f>IF(F23="", "", G23*W23*H23)</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>IF(ISBLANK(L23), "", $X$21*M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" t="str">
+        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>IF(N23="directApplication", "", $AA$21*O23)</f>
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <f>IF(L23="", "",IF( L23="pastureRangeAndPaddock",Y23*Constants!$K$2, Y23*S23))</f>
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <f>IF(OR(N23="", N23="directApplication"), "",AB23*U23)</f>
+        <v>0</v>
+      </c>
+      <c r="AE23" t="str">
+        <f>IF(F23="", "", SUM(AC23:AD27))</f>
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <f>IF(C23="", "", _xlfn.XLOOKUP(C23,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <f>IF(AE23="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA23">
-        <f>IF(ISBLANK(L23), "", $Z$21*M23)</f>
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" t="str">
-        <f>IF(F23="", "",SUM(AB23:AB27))</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <f>IF(L23="", "",IF( L23="pastureRangeAndPaddock",AA23*Constants!$K$2, AA23*U23))</f>
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG23" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH23" t="str">
-        <f>IF(C23="", "", _xlfn.XLOOKUP(C23,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI23" t="str">
-        <f>IF(AG23="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ23" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A21), "", 'Input Scenarios'!A21)</f>
         <v/>
@@ -8787,84 +8494,76 @@
         <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R24" t="str">
-        <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <f>IF(F24="", "",I24*(1-P24)*(1-Q24))</f>
-        <v/>
-      </c>
-      <c r="T24">
+      <c r="R24">
         <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U24" t="str">
+      <c r="S24" t="str">
         <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V24">
+      <c r="T24">
         <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W24">
+      <c r="U24">
         <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V24" t="str">
+        <f>IF(F24="","",I24*J24/6.25)</f>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f>IF(F24="", "", V24*(1-K24))</f>
+        <v/>
+      </c>
       <c r="X24" t="str">
-        <f>IF(F24="","",I24*J24/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <f>IF(F24="", "", X24*(1-K24))</f>
-        <v/>
+        <f>IF(F24="", "", G24*W24*H24)</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>IF(ISBLANK(L24), "", $X$21*M24)</f>
+        <v>67.106552673600007</v>
       </c>
       <c r="Z24" t="str">
+        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <v/>
+      </c>
+      <c r="AA24" t="str">
+        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>IF(N24="directApplication", "", $AA$21*O24)</f>
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <f>IF(L24="", "",IF( L24="pastureRangeAndPaddock",Y24*Constants!$K$2, Y24*S24))</f>
+        <v>14.092376061456001</v>
+      </c>
+      <c r="AD24">
+        <f>IF(OR(N24="", N24="directApplication"), "",AB24*U24)</f>
+        <v>0</v>
+      </c>
+      <c r="AE24" t="str">
+        <f>IF(F24="", "", SUM(AC24:AD28))</f>
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <f>IF(C24="", "", _xlfn.XLOOKUP(C24,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <f>IF(AE24="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH24" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA24">
-        <f>IF(ISBLANK(L24), "", $Z$21*M24)</f>
-        <v>67.106552673600007</v>
-      </c>
-      <c r="AB24" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC24" t="str">
-        <f>IF(F24="", "",SUM(AB24:AB28))</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <f>IF(L24="", "",IF( L24="pastureRangeAndPaddock",AA24*Constants!$K$2, AA24*U24))</f>
-        <v>14.092376061456001</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH24" t="str">
-        <f>IF(C24="", "", _xlfn.XLOOKUP(C24,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI24" t="str">
-        <f>IF(AG24="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ24" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A22), "", 'Input Scenarios'!A22)</f>
         <v/>
@@ -8923,84 +8622,76 @@
         <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R25" s="11" t="str">
-        <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S25" s="11" t="str">
-        <f>IF(F25="", "",I25*(1-P25)*(1-Q25))</f>
+      <c r="R25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T25" t="str">
-        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U25" t="str">
-        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V25" t="str">
         <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W25" t="str">
+      <c r="U25" t="str">
         <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X25" s="11" t="str">
+      <c r="V25" s="11" t="str">
         <f>IF(F25="","",I25*J25/6.25)</f>
         <v/>
       </c>
+      <c r="W25" s="11" t="str">
+        <f>IF(F25="", "", V25*(1-K25))</f>
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <f>IF(F25="", "", G25*W25*H25)</f>
+        <v/>
+      </c>
       <c r="Y25" s="11" t="str">
-        <f>IF(F25="", "", X25*(1-K25))</f>
+        <f>IF(ISBLANK(L25), "", $X$21*M25)</f>
         <v/>
       </c>
       <c r="Z25" t="str">
+        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
+        <v/>
+      </c>
+      <c r="AA25" s="11" t="str">
+        <f>IF(F25="", "",SUM(Z25:Z29))</f>
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <f>IF(N25="directApplication", "", $AA$21*O25)</f>
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <f>IF(L25="", "",IF( L25="pastureRangeAndPaddock",Y25*Constants!$K$2, Y25*S25))</f>
+        <v/>
+      </c>
+      <c r="AD25" t="str">
+        <f>IF(OR(N25="", N25="directApplication"), "",AB25*U25)</f>
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <f>IF(F25="", "", SUM(AC25:AD29))</f>
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <f>IF(C25="", "", _xlfn.XLOOKUP(C25,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <f>IF(AE25="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA25" s="11" t="str">
-        <f>IF(ISBLANK(L25), "", $Z$21*M25)</f>
-        <v/>
-      </c>
-      <c r="AB25" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC25" s="11" t="str">
-        <f>IF(F25="", "",SUM(AB25:AB29))</f>
-        <v/>
-      </c>
-      <c r="AD25" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AE25" t="str">
-        <f>IF(L25="", "",IF( L25="pastureRangeAndPaddock",AA25*Constants!$K$2, AA25*U25))</f>
-        <v/>
-      </c>
-      <c r="AF25" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AG25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH25" t="str">
-        <f>IF(C25="", "", _xlfn.XLOOKUP(C25,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI25" t="str">
-        <f>IF(AG25="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ25" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A23), "", 'Input Scenarios'!A23)</f>
         <v>NT</v>
@@ -9066,83 +8757,75 @@
         <v>0.15</v>
       </c>
       <c r="R26">
-        <f>IF(F26="", "",_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v>0.36</v>
-      </c>
-      <c r="S26">
-        <f>IF(F26="", "",I26*(1-P26)*(1-Q26))</f>
-        <v>1.5809999999999994E-2</v>
-      </c>
-      <c r="T26">
         <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U26">
+      <c r="S26">
         <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.3</v>
       </c>
-      <c r="V26">
+      <c r="T26">
         <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="W26">
+      <c r="U26">
         <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
-      <c r="X26">
+      <c r="V26">
         <f>IF(F26="","",I26*J26/6.25)</f>
         <v>3.4223999999999999E-3</v>
       </c>
+      <c r="W26">
+        <f>IF(F26="", "", V26*(1-K26))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X26">
+        <f>IF(F26="", "", G26*W26*H26)</f>
+        <v>335.74770719999998</v>
+      </c>
       <c r="Y26">
-        <f>IF(F26="", "", X26*(1-K26))</f>
-        <v>1.813872E-3</v>
+        <f>IF(ISBLANK(L26), "", $X$26*M26)</f>
+        <v>33.574770719999997</v>
       </c>
       <c r="Z26">
-        <f t="shared" si="0"/>
-        <v>335.74770719999998</v>
+        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <v>23.46876473328</v>
       </c>
       <c r="AA26">
-        <f>IF(ISBLANK(L26), "", $Z$26*M26)</f>
-        <v>33.574770719999997</v>
+        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <v>23.46876473328</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="1"/>
-        <v>23.46876473328</v>
+        <f>IF(N26="directApplication", "", $AA$26*O26)</f>
+        <v>11.73438236664</v>
       </c>
       <c r="AC26">
-        <f>IF(F26="", "",SUM(AB26:AB30))</f>
-        <v>23.46876473328</v>
+        <f>IF(L26="", "",IF( L26="pastureRangeAndPaddock",Y26*Constants!$K$2, Y26*S26))</f>
+        <v>10.072431215999998</v>
       </c>
       <c r="AD26">
-        <f>IF(N26="directApplication", "", $AC$26*O26)</f>
-        <v>11.73438236664</v>
+        <f>IF(OR(N26="", N26="directApplication"), "",AB26*U26)</f>
+        <v>2.3468764733280003</v>
       </c>
       <c r="AE26">
-        <f>IF(L26="", "",IF( L26="pastureRangeAndPaddock",AA26*Constants!$K$2, AA26*U26))</f>
-        <v>10.072431215999998</v>
+        <f>IF(F26="", "", SUM(AC26:AD30))</f>
+        <v>77.04906258679199</v>
       </c>
       <c r="AF26">
-        <f t="shared" si="3"/>
-        <v>2.3468764733280003</v>
-      </c>
-      <c r="AG26">
-        <f t="shared" si="4"/>
-        <v>77.04906258679199</v>
-      </c>
-      <c r="AH26">
         <f>IF(C26="", "", _xlfn.XLOOKUP(C26,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AI26">
-        <f>IF(AG26="","",Constants!$J$2)</f>
+      <c r="AG26">
+        <f>IF(AE26="","",Constants!$J$2)</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AJ26">
-        <f t="shared" si="5"/>
+      <c r="AH26">
+        <f t="shared" si="0"/>
         <v>9.68616786805385E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A24), "", 'Input Scenarios'!A24)</f>
         <v/>
@@ -9207,84 +8890,76 @@
         <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R27" t="str">
-        <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <f>IF(F27="", "",I27*(1-P27)*(1-Q27))</f>
-        <v/>
-      </c>
-      <c r="T27">
+      <c r="R27">
         <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U27">
+      <c r="S27">
         <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.05</v>
       </c>
-      <c r="V27">
+      <c r="T27">
         <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.01</v>
       </c>
-      <c r="W27">
+      <c r="U27">
         <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.2</v>
       </c>
+      <c r="V27" t="str">
+        <f>IF(F27="","",I27*J27/6.25)</f>
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <f>IF(F27="", "", V27*(1-K27))</f>
+        <v/>
+      </c>
       <c r="X27" t="str">
-        <f>IF(F27="","",I27*J27/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <f>IF(F27="", "", X27*(1-K27))</f>
-        <v/>
-      </c>
-      <c r="Z27" t="str">
+        <f>IF(F27="", "", G27*W27*H27)</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>IF(ISBLANK(L27), "", $X$26*M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" t="str">
+        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>IF(N27="directApplication", "", $AA$26*O27)</f>
+        <v>5.8671911833200001</v>
+      </c>
+      <c r="AC27">
+        <f>IF(L27="", "",IF( L27="pastureRangeAndPaddock",Y27*Constants!$K$2, Y27*S27))</f>
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <f>IF(OR(N27="", N27="directApplication"), "",AB27*U27)</f>
+        <v>1.1734382366640002</v>
+      </c>
+      <c r="AE27" t="str">
+        <f>IF(F27="", "", SUM(AC27:AD31))</f>
+        <v/>
+      </c>
+      <c r="AF27" t="str">
+        <f>IF(C27="", "", _xlfn.XLOOKUP(C27,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG27" t="str">
+        <f>IF(AE27="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA27">
-        <f>IF(ISBLANK(L27), "", $Z$26*M27)</f>
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC27" t="str">
-        <f>IF(F27="", "",SUM(AB27:AB31))</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f t="shared" ref="AD27:AD30" si="8">IF(N27="directApplication", "", $AC$26*O27)</f>
-        <v>5.8671911833200001</v>
-      </c>
-      <c r="AE27">
-        <f>IF(L27="", "",IF( L27="pastureRangeAndPaddock",AA27*Constants!$K$2, AA27*U27))</f>
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="3"/>
-        <v>1.1734382366640002</v>
-      </c>
-      <c r="AG27" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH27" t="str">
-        <f>IF(C27="", "", _xlfn.XLOOKUP(C27,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI27" t="str">
-        <f>IF(AG27="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ27" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A25), "", 'Input Scenarios'!A25)</f>
         <v/>
@@ -9349,84 +9024,76 @@
         <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R28" t="str">
-        <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <f>IF(F28="", "",I28*(1-P28)*(1-Q28))</f>
-        <v/>
-      </c>
-      <c r="T28">
+      <c r="R28">
         <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>1E-3</v>
       </c>
-      <c r="U28">
+      <c r="S28">
         <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0.4</v>
       </c>
-      <c r="V28">
+      <c r="T28">
         <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W28">
+      <c r="U28">
         <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V28" t="str">
+        <f>IF(F28="","",I28*J28/6.25)</f>
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <f>IF(F28="", "", V28*(1-K28))</f>
+        <v/>
+      </c>
       <c r="X28" t="str">
-        <f>IF(F28="","",I28*J28/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y28" t="str">
-        <f>IF(F28="", "", X28*(1-K28))</f>
-        <v/>
-      </c>
-      <c r="Z28" t="str">
+        <f>IF(F28="", "", G28*W28*H28)</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>IF(ISBLANK(L28), "", $X$26*M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" t="str">
+        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>IF(N28="directApplication", "", $AA$26*O28)</f>
+        <v>5.8671911833200001</v>
+      </c>
+      <c r="AC28">
+        <f>IF(L28="", "",IF( L28="pastureRangeAndPaddock",Y28*Constants!$K$2, Y28*S28))</f>
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <f>IF(OR(N28="", N28="directApplication"), "",AB28*U28)</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" t="str">
+        <f>IF(F28="", "", SUM(AC28:AD32))</f>
+        <v/>
+      </c>
+      <c r="AF28" t="str">
+        <f>IF(C28="", "", _xlfn.XLOOKUP(C28,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG28" t="str">
+        <f>IF(AE28="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA28">
-        <f>IF(ISBLANK(L28), "", $Z$26*M28)</f>
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC28" t="str">
-        <f>IF(F28="", "",SUM(AB28:AB32))</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f t="shared" si="8"/>
-        <v>5.8671911833200001</v>
-      </c>
-      <c r="AE28">
-        <f>IF(L28="", "",IF( L28="pastureRangeAndPaddock",AA28*Constants!$K$2, AA28*U28))</f>
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH28" t="str">
-        <f>IF(C28="", "", _xlfn.XLOOKUP(C28,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI28" t="str">
-        <f>IF(AG28="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ28" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A26), "", 'Input Scenarios'!A26)</f>
         <v/>
@@ -9491,84 +9158,76 @@
         <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R29" t="str">
-        <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S29" t="str">
-        <f>IF(F29="", "",I29*(1-P29)*(1-Q29))</f>
-        <v/>
-      </c>
-      <c r="T29">
+      <c r="R29">
         <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0.02</v>
       </c>
-      <c r="U29" t="str">
+      <c r="S29" t="str">
         <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="V29">
+      <c r="T29">
         <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>0</v>
       </c>
-      <c r="W29">
+      <c r="U29">
         <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>0</v>
       </c>
+      <c r="V29" t="str">
+        <f>IF(F29="","",I29*J29/6.25)</f>
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <f>IF(F29="", "", V29*(1-K29))</f>
+        <v/>
+      </c>
       <c r="X29" t="str">
-        <f>IF(F29="","",I29*J29/6.25)</f>
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <f>IF(F29="", "", X29*(1-K29))</f>
-        <v/>
+        <f>IF(F29="", "", G29*W29*H29)</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>IF(ISBLANK(L29), "", $X$26*M29)</f>
+        <v>302.17293647999998</v>
       </c>
       <c r="Z29" t="str">
+        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>IF(N29="directApplication", "", $AA$26*O29)</f>
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <f>IF(L29="", "",IF( L29="pastureRangeAndPaddock",Y29*Constants!$K$2, Y29*S29))</f>
+        <v>63.456316660799992</v>
+      </c>
+      <c r="AD29">
+        <f>IF(OR(N29="", N29="directApplication"), "",AB29*U29)</f>
+        <v>0</v>
+      </c>
+      <c r="AE29" t="str">
+        <f>IF(F29="", "", SUM(AC29:AD33))</f>
+        <v/>
+      </c>
+      <c r="AF29" t="str">
+        <f>IF(C29="", "", _xlfn.XLOOKUP(C29,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG29" t="str">
+        <f>IF(AE29="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA29">
-        <f>IF(ISBLANK(L29), "", $Z$26*M29)</f>
-        <v>302.17293647999998</v>
-      </c>
-      <c r="AB29" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC29" t="str">
-        <f>IF(F29="", "",SUM(AB29:AB33))</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <f>IF(L29="", "",IF( L29="pastureRangeAndPaddock",AA29*Constants!$K$2, AA29*U29))</f>
-        <v>63.456316660799992</v>
-      </c>
-      <c r="AF29">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG29" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH29" t="str">
-        <f>IF(C29="", "", _xlfn.XLOOKUP(C29,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI29" t="str">
-        <f>IF(AG29="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ29" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>IF(ISBLANK('Input Scenarios'!A27), "", 'Input Scenarios'!A27)</f>
         <v/>
@@ -9627,80 +9286,72 @@
         <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
         <v/>
       </c>
-      <c r="R30" s="11" t="str">
-        <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!G$2:G$5))</f>
-        <v/>
-      </c>
-      <c r="S30" s="11" t="str">
-        <f>IF(F30="", "",I30*(1-P30)*(1-Q30))</f>
+      <c r="R30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v/>
       </c>
       <c r="T30" t="str">
-        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
-        <v/>
-      </c>
-      <c r="U30" t="str">
-        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
-        <v/>
-      </c>
-      <c r="V30" t="str">
         <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
         <v>N/A</v>
       </c>
-      <c r="W30" t="str">
+      <c r="U30" t="str">
         <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
         <v>N/A</v>
       </c>
-      <c r="X30" s="11" t="str">
+      <c r="V30" s="11" t="str">
         <f>IF(F30="","",I30*J30/6.25)</f>
         <v/>
       </c>
+      <c r="W30" s="11" t="str">
+        <f>IF(F30="", "", V30*(1-K30))</f>
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <f>IF(F30="", "", G30*W30*H30)</f>
+        <v/>
+      </c>
       <c r="Y30" s="11" t="str">
-        <f>IF(F30="", "", X30*(1-K30))</f>
+        <f>IF(ISBLANK(L30), "", $X$26*M30)</f>
         <v/>
       </c>
       <c r="Z30" t="str">
+        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
+        <v/>
+      </c>
+      <c r="AA30" s="11" t="str">
+        <f>IF(F30="", "",SUM(Z30:Z34))</f>
+        <v/>
+      </c>
+      <c r="AB30" t="str">
+        <f>IF(N30="directApplication", "", $AA$26*O30)</f>
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <f>IF(L30="", "",IF( L30="pastureRangeAndPaddock",Y30*Constants!$K$2, Y30*S30))</f>
+        <v/>
+      </c>
+      <c r="AD30" t="str">
+        <f>IF(OR(N30="", N30="directApplication"), "",AB30*U30)</f>
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <f>IF(F30="", "", SUM(AC30:AD34))</f>
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <f>IF(C30="", "", _xlfn.XLOOKUP(C30,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
+        <v/>
+      </c>
+      <c r="AG30" t="str">
+        <f>IF(AE30="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AH30" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA30" s="11" t="str">
-        <f>IF(ISBLANK(L30), "", $Z$26*M30)</f>
-        <v/>
-      </c>
-      <c r="AB30" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC30" s="11" t="str">
-        <f>IF(F30="", "",SUM(AB30:AB34))</f>
-        <v/>
-      </c>
-      <c r="AD30" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AE30" t="str">
-        <f>IF(L30="", "",IF( L30="pastureRangeAndPaddock",AA30*Constants!$K$2, AA30*U30))</f>
-        <v/>
-      </c>
-      <c r="AF30" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AG30" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AH30" t="str">
-        <f>IF(C30="", "", _xlfn.XLOOKUP(C30,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
-        <v/>
-      </c>
-      <c r="AI30" t="str">
-        <f>IF(AG30="","",Constants!$J$2)</f>
-        <v/>
-      </c>
-      <c r="AJ30" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -9710,6 +9361,3020 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73B6793-AC5B-024D-9741-D6649CB824BC}">
+  <dimension ref="A2:AI31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="25" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="12.1640625" customWidth="1"/>
+    <col min="35" max="35" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="AA6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI10" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A8), "", 'Input Scenarios'!A8)</f>
+        <v>NSW</v>
+      </c>
+      <c r="B11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B8), "", 'Input Scenarios'!B8)</f>
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C8), "", 'Input Scenarios'!C8)</f>
+        <v>Non-irrigated pasture</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D8), "", 'Input Scenarios'!D8)</f>
+        <v>wet</v>
+      </c>
+      <c r="E11" t="b">
+        <f>IF(ISBLANK('Input Scenarios'!E8), "", 'Input Scenarios'!E8)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F8), "", 'Input Scenarios'!F8)</f>
+        <v>layers</v>
+      </c>
+      <c r="G11">
+        <f>IF(ISBLANK('Input Scenarios'!G8), "", 'Input Scenarios'!G8)</f>
+        <v>5000</v>
+      </c>
+      <c r="H11">
+        <f>IF(ISBLANK('Input Scenarios'!H8), "", 'Input Scenarios'!H8)</f>
+        <v>50</v>
+      </c>
+      <c r="I11">
+        <f>IF(ISBLANK('Input Scenarios'!I8),_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I8)</f>
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="J11">
+        <f>IF(ISBLANK('Input Scenarios'!J8),_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J8)</f>
+        <v>0.19</v>
+      </c>
+      <c r="K11">
+        <f>IF(ISBLANK('Input Scenarios'!K8),_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K8)</f>
+        <v>0.35</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11">
+        <v>0.1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>0.15</v>
+      </c>
+      <c r="P11">
+        <f>IF(F11="", "",_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q11">
+        <f>IF(F11="", "",_xlfn.XLOOKUP(F11,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v>0.18</v>
+      </c>
+      <c r="R11">
+        <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S11">
+        <f>IF(L11="", "", _xlfn.XLOOKUP(L11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.3</v>
+      </c>
+      <c r="T11">
+        <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U11">
+        <f>IF(N11="", "", _xlfn.XLOOKUP(N11, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V11">
+        <f>IF(F11="","",I11*J11/6.25)</f>
+        <v>2.6144000000000002E-3</v>
+      </c>
+      <c r="W11">
+        <f>IF(F11="", "", V11*(1-K11))</f>
+        <v>1.6993600000000002E-3</v>
+      </c>
+      <c r="X11">
+        <f>IF(F11="", "", G11*W11*H11)</f>
+        <v>424.84000000000003</v>
+      </c>
+      <c r="Y11">
+        <f>IF(ISBLANK(L11), "", $X$11*M11)</f>
+        <v>42.484000000000009</v>
+      </c>
+      <c r="Z11">
+        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <v>29.69631600000001</v>
+      </c>
+      <c r="AA11">
+        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <v>186.67469600000001</v>
+      </c>
+      <c r="AB11">
+        <f>IF(N11="directApplication", "", $AA$11*O11)</f>
+        <v>28.001204400000002</v>
+      </c>
+      <c r="AC11">
+        <f>IF(E11="", "", IF(E11, 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <f>IF(E11="","",Constants!$M$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="AE11">
+        <f>IF(F11="","",Constants!$L$2)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AF11">
+        <f>IF(F11="","",Constants!$J$2)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="AG11">
+        <f>IF(N11="solidStorage", AB11*AC11*AD11, "")</f>
+        <v>0.56002408800000003</v>
+      </c>
+      <c r="AH11">
+        <f>IF(L14="pastureRangeAndPaddock", Y14*AD$11*AC$11, "")</f>
+        <v>3.3987200000000009</v>
+      </c>
+      <c r="AI11">
+        <f>IF(F11="", "", (AG11+AH11)*AE11*AF11/1000)</f>
+        <v>6.8429719235428584E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A9), "", 'Input Scenarios'!A9)</f>
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B9), "", 'Input Scenarios'!B9)</f>
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C9), "", 'Input Scenarios'!C9)</f>
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D9), "", 'Input Scenarios'!D9)</f>
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E9), "", 'Input Scenarios'!E9)</f>
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F9), "", 'Input Scenarios'!F9)</f>
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G9), "", 'Input Scenarios'!G9)</f>
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H9), "", 'Input Scenarios'!H9)</f>
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I9),_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I9)</f>
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J9),_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J9)</f>
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K9),_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K9)</f>
+        <v/>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <v>0.2</v>
+      </c>
+      <c r="N12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12">
+        <v>0.2</v>
+      </c>
+      <c r="P12" t="str">
+        <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <f>IF(F12="", "",_xlfn.XLOOKUP(F12,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R12">
+        <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S12">
+        <f>IF(L12="", "", _xlfn.XLOOKUP(L12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.05</v>
+      </c>
+      <c r="T12">
+        <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.01</v>
+      </c>
+      <c r="U12">
+        <f>IF(N12="", "", _xlfn.XLOOKUP(N12, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V12" t="str">
+        <f>IF(F12="","",I12*J12/6.25)</f>
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <f>IF(F12="", "", V12*(1-K12))</f>
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <f>IF(F12="", "", G12*W12*H12)</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>IF(ISBLANK(L12), "", $X$11*M12)</f>
+        <v>84.968000000000018</v>
+      </c>
+      <c r="Z12">
+        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <v>80.634632000000011</v>
+      </c>
+      <c r="AA12" t="str">
+        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>IF(N12="directApplication", "", $AA$11*O12)</f>
+        <v>37.334939200000001</v>
+      </c>
+      <c r="AC12" t="str">
+        <f t="shared" ref="AC12:AC30" si="0">IF(E12="", "", IF(E12, 1, 0))</f>
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <f>IF(E12="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <f>IF(F12="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <f>IF(F12="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG12" t="str">
+        <f t="shared" ref="AG12:AG30" si="1">IF(N12="solidStorage", AB12*AC12*AD12, "")</f>
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <f t="shared" ref="AH12:AH30" si="2">IF(L15="pastureRangeAndPaddock", Y15*AD$11*AC$11, "")</f>
+        <v/>
+      </c>
+      <c r="AI12" t="str">
+        <f t="shared" ref="AI12:AI31" si="3">IF(F12="", "", (AG12+AH12)*AE12*AF12/1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A10), "", 'Input Scenarios'!A10)</f>
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B10), "", 'Input Scenarios'!B10)</f>
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C10), "", 'Input Scenarios'!C10)</f>
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D10), "", 'Input Scenarios'!D10)</f>
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E10), "", 'Input Scenarios'!E10)</f>
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F10), "", 'Input Scenarios'!F10)</f>
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G10), "", 'Input Scenarios'!G10)</f>
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H10), "", 'Input Scenarios'!H10)</f>
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I10),_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I10)</f>
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J10),_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J10)</f>
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K10),_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K10)</f>
+        <v/>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13">
+        <v>0.3</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13">
+        <v>0.25</v>
+      </c>
+      <c r="P13" t="str">
+        <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <f>IF(F13="", "",_xlfn.XLOOKUP(F13,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S13">
+        <f>IF(L13="", "", _xlfn.XLOOKUP(L13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.4</v>
+      </c>
+      <c r="T13">
+        <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <f>IF(N13="", "", _xlfn.XLOOKUP(N13, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V13" t="str">
+        <f>IF(F13="","",I13*J13/6.25)</f>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f>IF(F13="", "", V13*(1-K13))</f>
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <f>IF(F13="", "", G13*W13*H13)</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>IF(ISBLANK(L13), "", $X$11*M13)</f>
+        <v>127.452</v>
+      </c>
+      <c r="Z13">
+        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <v>76.343747999999991</v>
+      </c>
+      <c r="AA13" t="str">
+        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>IF(N13="directApplication", "", $AA$11*O13)</f>
+        <v>46.668674000000003</v>
+      </c>
+      <c r="AC13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <f>IF(E13="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <f>IF(F13="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <f>IF(F13="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A11), "", 'Input Scenarios'!A11)</f>
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B11), "", 'Input Scenarios'!B11)</f>
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C11), "", 'Input Scenarios'!C11)</f>
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D11), "", 'Input Scenarios'!D11)</f>
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E11), "", 'Input Scenarios'!E11)</f>
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F11), "", 'Input Scenarios'!F11)</f>
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G11), "", 'Input Scenarios'!G11)</f>
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H11), "", 'Input Scenarios'!H11)</f>
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I11),_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I11)</f>
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J11),_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J11)</f>
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K11),_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K11)</f>
+        <v/>
+      </c>
+      <c r="L14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14">
+        <v>0.4</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14">
+        <v>0.17</v>
+      </c>
+      <c r="P14" t="str">
+        <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <f>IF(F14="", "",_xlfn.XLOOKUP(F14,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R14">
+        <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.02</v>
+      </c>
+      <c r="S14" t="str">
+        <f>IF(L14="", "", _xlfn.XLOOKUP(L14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="T14">
+        <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <f>IF(N14="", "", _xlfn.XLOOKUP(N14, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V14" t="str">
+        <f>IF(F14="","",I14*J14/6.25)</f>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f>IF(F14="", "", V14*(1-K14))</f>
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <f>IF(F14="", "", G14*W14*H14)</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>IF(ISBLANK(L14), "", $X$11*M14)</f>
+        <v>169.93600000000004</v>
+      </c>
+      <c r="Z14" t="str">
+        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>IF(N14="directApplication", "", $AA$11*O14)</f>
+        <v>31.734698320000003</v>
+      </c>
+      <c r="AC14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <f>IF(E14="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <f>IF(F14="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <f>IF(F14="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A12), "", 'Input Scenarios'!A12)</f>
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B12), "", 'Input Scenarios'!B12)</f>
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C12), "", 'Input Scenarios'!C12)</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D12), "", 'Input Scenarios'!D12)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E12), "", 'Input Scenarios'!E12)</f>
+        <v/>
+      </c>
+      <c r="F15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F12), "", 'Input Scenarios'!F12)</f>
+        <v/>
+      </c>
+      <c r="G15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G12), "", 'Input Scenarios'!G12)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H12), "", 'Input Scenarios'!H12)</f>
+        <v/>
+      </c>
+      <c r="I15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I12),_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I12)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J12),_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J12)</f>
+        <v/>
+      </c>
+      <c r="K15" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K12),_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K12)</f>
+        <v/>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="P15" s="11" t="str">
+        <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="11" t="str">
+        <f>IF(F15="", "",_xlfn.XLOOKUP(F15,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <f>IF(L15="", "", _xlfn.XLOOKUP(L15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="U15" t="str">
+        <f>IF(N15="", "", _xlfn.XLOOKUP(N15, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="V15" s="11" t="str">
+        <f>IF(F15="","",I15*J15/6.25)</f>
+        <v/>
+      </c>
+      <c r="W15" s="11" t="str">
+        <f>IF(F15="", "", V15*(1-K15))</f>
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <f>IF(F15="", "", G15*W15*H15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="11" t="str">
+        <f>IF(ISBLANK(L15), "", $X$11*M15)</f>
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
+        <v/>
+      </c>
+      <c r="AA15" s="11" t="str">
+        <f>IF(F15="", "",SUM(Z15:Z19))</f>
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <f>IF(N15="directApplication", "", $AA$11*O15)</f>
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <f>IF(E15="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <f>IF(F15="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <f>IF(F15="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A13), "", 'Input Scenarios'!A13)</f>
+        <v>QLD</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B13), "", 'Input Scenarios'!B13)</f>
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C13), "", 'Input Scenarios'!C13)</f>
+        <v>Irrigated crop</v>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D13), "", 'Input Scenarios'!D13)</f>
+        <v>dry</v>
+      </c>
+      <c r="E16" t="b">
+        <f>IF(ISBLANK('Input Scenarios'!E13), "", 'Input Scenarios'!E13)</f>
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F13), "", 'Input Scenarios'!F13)</f>
+        <v>meatChickenBreeder</v>
+      </c>
+      <c r="G16">
+        <f>IF(ISBLANK('Input Scenarios'!G13), "", 'Input Scenarios'!G13)</f>
+        <v>2250</v>
+      </c>
+      <c r="H16">
+        <f>IF(ISBLANK('Input Scenarios'!H13), "", 'Input Scenarios'!H13)</f>
+        <v>125</v>
+      </c>
+      <c r="I16">
+        <f>IF(ISBLANK('Input Scenarios'!I13),_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I13)</f>
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="J16">
+        <f>IF(ISBLANK('Input Scenarios'!J13),_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J13)</f>
+        <v>0.19</v>
+      </c>
+      <c r="K16">
+        <f>IF(ISBLANK('Input Scenarios'!K13),_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K13)</f>
+        <v>0.32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16">
+        <v>0.4</v>
+      </c>
+      <c r="N16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16">
+        <v>0.2</v>
+      </c>
+      <c r="P16">
+        <f>IF(F16="", "",_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q16">
+        <f>IF(F16="", "",_xlfn.XLOOKUP(F16,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v>0.18</v>
+      </c>
+      <c r="R16">
+        <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S16">
+        <f>IF(L16="", "", _xlfn.XLOOKUP(L16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.3</v>
+      </c>
+      <c r="T16">
+        <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U16">
+        <f>IF(N16="", "", _xlfn.XLOOKUP(N16, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V16">
+        <f>IF(F16="","",I16*J16/6.25)</f>
+        <v>3.1312000000000002E-3</v>
+      </c>
+      <c r="W16">
+        <f>IF(F16="", "", V16*(1-K16))</f>
+        <v>2.1292159999999997E-3</v>
+      </c>
+      <c r="X16">
+        <f>IF(F16="", "", G16*W16*H16)</f>
+        <v>598.84199999999987</v>
+      </c>
+      <c r="Y16">
+        <f>IF(ISBLANK(L16), "", $X$16*M16)</f>
+        <v>239.53679999999997</v>
+      </c>
+      <c r="Z16">
+        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <v>167.4362232</v>
+      </c>
+      <c r="AA16">
+        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <v>409.66781219999996</v>
+      </c>
+      <c r="AB16">
+        <f>IF(N16="directApplication", "", $AA$16*O16)</f>
+        <v>81.933562440000003</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <f>IF(E16="","",Constants!$M$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="AE16">
+        <f>IF(F16="","",Constants!$L$2)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AF16">
+        <f>IF(F16="","",Constants!$J$2)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="1"/>
+        <v>1.6386712488000001</v>
+      </c>
+      <c r="AH16">
+        <f>IF(L19="pastureRangeAndPaddock", Y19*AD$16*AC$16, "")</f>
+        <v>1.197684</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="3"/>
+        <v>4.9028426443542864E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A14), "", 'Input Scenarios'!A14)</f>
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B14), "", 'Input Scenarios'!B14)</f>
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C14), "", 'Input Scenarios'!C14)</f>
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D14), "", 'Input Scenarios'!D14)</f>
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E14), "", 'Input Scenarios'!E14)</f>
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F14), "", 'Input Scenarios'!F14)</f>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G14), "", 'Input Scenarios'!G14)</f>
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H14), "", 'Input Scenarios'!H14)</f>
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I14),_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I14)</f>
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J14),_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J14)</f>
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K14),_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K14)</f>
+        <v/>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17">
+        <v>0.3</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17">
+        <v>0.25</v>
+      </c>
+      <c r="P17" t="str">
+        <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <f>IF(F17="", "",_xlfn.XLOOKUP(F17,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R17">
+        <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S17">
+        <f>IF(L17="", "", _xlfn.XLOOKUP(L17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.05</v>
+      </c>
+      <c r="T17">
+        <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.01</v>
+      </c>
+      <c r="U17">
+        <f>IF(N17="", "", _xlfn.XLOOKUP(N17, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V17" t="str">
+        <f>IF(F17="","",I17*J17/6.25)</f>
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <f>IF(F17="", "", V17*(1-K17))</f>
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <f>IF(F17="", "", G17*W17*H17)</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>IF(ISBLANK(L17), "", $X$16*M17)</f>
+        <v>179.65259999999995</v>
+      </c>
+      <c r="Z17">
+        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <v>170.49031739999995</v>
+      </c>
+      <c r="AA17" t="str">
+        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>IF(N17="directApplication", "", $AA$16*O17)</f>
+        <v>102.41695304999999</v>
+      </c>
+      <c r="AC17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <f>IF(E17="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <f>IF(F17="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <f>IF(F17="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <f t="shared" ref="AH17:AH20" si="4">IF(L20="pastureRangeAndPaddock", Y20*AD$16*AC$16, "")</f>
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A15), "", 'Input Scenarios'!A15)</f>
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B15), "", 'Input Scenarios'!B15)</f>
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C15), "", 'Input Scenarios'!C15)</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D15), "", 'Input Scenarios'!D15)</f>
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E15), "", 'Input Scenarios'!E15)</f>
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F15), "", 'Input Scenarios'!F15)</f>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G15), "", 'Input Scenarios'!G15)</f>
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H15), "", 'Input Scenarios'!H15)</f>
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I15),_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I15)</f>
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J15),_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J15)</f>
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K15),_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K15)</f>
+        <v/>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18">
+        <v>0.2</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18">
+        <v>0.2</v>
+      </c>
+      <c r="P18" t="str">
+        <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <f>IF(F18="", "",_xlfn.XLOOKUP(F18,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S18">
+        <f>IF(L18="", "", _xlfn.XLOOKUP(L18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.4</v>
+      </c>
+      <c r="T18">
+        <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f>IF(N18="", "", _xlfn.XLOOKUP(N18, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V18" t="str">
+        <f>IF(F18="","",I18*J18/6.25)</f>
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <f>IF(F18="", "", V18*(1-K18))</f>
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <f>IF(F18="", "", G18*W18*H18)</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>IF(ISBLANK(L18), "", $X$16*M18)</f>
+        <v>119.76839999999999</v>
+      </c>
+      <c r="Z18">
+        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <v>71.74127159999999</v>
+      </c>
+      <c r="AA18" t="str">
+        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>IF(N18="directApplication", "", $AA$16*O18)</f>
+        <v>81.933562440000003</v>
+      </c>
+      <c r="AC18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <f>IF(E18="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <f>IF(F18="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <f>IF(F18="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A16), "", 'Input Scenarios'!A16)</f>
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B16), "", 'Input Scenarios'!B16)</f>
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C16), "", 'Input Scenarios'!C16)</f>
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D16), "", 'Input Scenarios'!D16)</f>
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E16), "", 'Input Scenarios'!E16)</f>
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F16), "", 'Input Scenarios'!F16)</f>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G16), "", 'Input Scenarios'!G16)</f>
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H16), "", 'Input Scenarios'!H16)</f>
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I16),_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I16)</f>
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J16),_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J16)</f>
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K16),_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K16)</f>
+        <v/>
+      </c>
+      <c r="L19" t="s">
+        <v>40</v>
+      </c>
+      <c r="M19">
+        <v>0.1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19">
+        <v>0.25</v>
+      </c>
+      <c r="P19" t="str">
+        <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <f>IF(F19="", "",_xlfn.XLOOKUP(F19,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.02</v>
+      </c>
+      <c r="S19" t="str">
+        <f>IF(L19="", "", _xlfn.XLOOKUP(L19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="T19">
+        <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <f>IF(N19="", "", _xlfn.XLOOKUP(N19, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V19" t="str">
+        <f>IF(F19="","",I19*J19/6.25)</f>
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <f>IF(F19="", "", V19*(1-K19))</f>
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <f>IF(F19="", "", G19*W19*H19)</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>IF(ISBLANK(L19), "", $X$16*M19)</f>
+        <v>59.884199999999993</v>
+      </c>
+      <c r="Z19" t="str">
+        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>IF(N19="directApplication", "", $AA$16*O19)</f>
+        <v>102.41695304999999</v>
+      </c>
+      <c r="AC19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <f>IF(E19="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <f>IF(F19="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <f>IF(F19="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A17), "", 'Input Scenarios'!A17)</f>
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B17), "", 'Input Scenarios'!B17)</f>
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C17), "", 'Input Scenarios'!C17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D17), "", 'Input Scenarios'!D17)</f>
+        <v/>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E17), "", 'Input Scenarios'!E17)</f>
+        <v/>
+      </c>
+      <c r="F20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F17), "", 'Input Scenarios'!F17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G17), "", 'Input Scenarios'!G17)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H17), "", 'Input Scenarios'!H17)</f>
+        <v/>
+      </c>
+      <c r="I20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I17),_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I17)</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J17),_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J17)</f>
+        <v/>
+      </c>
+      <c r="K20" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K17),_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K17)</f>
+        <v/>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O20" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="11" t="str">
+        <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="11" t="str">
+        <f>IF(F20="", "",_xlfn.XLOOKUP(F20,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <f>IF(L20="", "", _xlfn.XLOOKUP(L20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="U20" t="str">
+        <f>IF(N20="", "", _xlfn.XLOOKUP(N20, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="V20" s="11" t="str">
+        <f>IF(F20="","",I20*J20/6.25)</f>
+        <v/>
+      </c>
+      <c r="W20" s="11" t="str">
+        <f>IF(F20="", "", V20*(1-K20))</f>
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <f>IF(F20="", "", G20*W20*H20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="11" t="str">
+        <f>IF(ISBLANK(L20), "", $X$16*M20)</f>
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
+        <v/>
+      </c>
+      <c r="AA20" s="11" t="str">
+        <f>IF(F20="", "",SUM(Z20:Z24))</f>
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <f>IF(N20="directApplication", "", $AA$16*O20)</f>
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <f>IF(E20="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <f>IF(F20="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <f>IF(F20="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH20" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI20" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A18), "", 'Input Scenarios'!A18)</f>
+        <v>TAS</v>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B18), "", 'Input Scenarios'!B18)</f>
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C18), "", 'Input Scenarios'!C18)</f>
+        <v>Irrigated pasture</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D18), "", 'Input Scenarios'!D18)</f>
+        <v>wet</v>
+      </c>
+      <c r="E21" t="b">
+        <f>IF(ISBLANK('Input Scenarios'!E18), "", 'Input Scenarios'!E18)</f>
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F18), "", 'Input Scenarios'!F18)</f>
+        <v>meatChickenGrowers</v>
+      </c>
+      <c r="G21">
+        <f>IF(ISBLANK('Input Scenarios'!G18), "", 'Input Scenarios'!G18)</f>
+        <v>3333</v>
+      </c>
+      <c r="H21">
+        <f>IF(ISBLANK('Input Scenarios'!H18), "", 'Input Scenarios'!H18)</f>
+        <v>111</v>
+      </c>
+      <c r="I21">
+        <f>IF(ISBLANK('Input Scenarios'!I18),_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I18)</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J21">
+        <f>IF(ISBLANK('Input Scenarios'!J18),_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J18)</f>
+        <v>0.23</v>
+      </c>
+      <c r="K21">
+        <f>IF(ISBLANK('Input Scenarios'!K18),_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K18)</f>
+        <v>0.47</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21">
+        <v>0.34</v>
+      </c>
+      <c r="P21">
+        <f>IF(F21="", "",_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q21">
+        <f>IF(F21="", "",_xlfn.XLOOKUP(F21,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v>0.15</v>
+      </c>
+      <c r="R21">
+        <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S21">
+        <f>IF(L21="", "", _xlfn.XLOOKUP(L21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.3</v>
+      </c>
+      <c r="T21">
+        <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U21">
+        <f>IF(N21="", "", _xlfn.XLOOKUP(N21, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V21">
+        <f>IF(F21="","",I21*J21/6.25)</f>
+        <v>3.4223999999999999E-3</v>
+      </c>
+      <c r="W21">
+        <f>IF(F21="", "", V21*(1-K21))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X21">
+        <f>IF(F21="", "", G21*W21*H21)</f>
+        <v>671.06552673600004</v>
+      </c>
+      <c r="Y21">
+        <f>IF(ISBLANK(L21), "", $X$21*M21)</f>
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <v>573.15706638521772</v>
+      </c>
+      <c r="AB21">
+        <f>IF(N21="directApplication", "", $AA$21*O21)</f>
+        <v>194.87340257097404</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <f>IF(E21="","",Constants!$M$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="AE21">
+        <f>IF(F21="","",Constants!$L$2)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AF21">
+        <f>IF(F21="","",Constants!$J$2)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="1"/>
+        <v>3.8974680514194806</v>
+      </c>
+      <c r="AH21">
+        <f>IF(L24="pastureRangeAndPaddock", Y24*AD$21*AC$21, "")</f>
+        <v>1.3421310534720001</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="3"/>
+        <v>9.0570213098838429E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A19), "", 'Input Scenarios'!A19)</f>
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B19), "", 'Input Scenarios'!B19)</f>
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C19), "", 'Input Scenarios'!C19)</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D19), "", 'Input Scenarios'!D19)</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E19), "", 'Input Scenarios'!E19)</f>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F19), "", 'Input Scenarios'!F19)</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G19), "", 'Input Scenarios'!G19)</f>
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H19), "", 'Input Scenarios'!H19)</f>
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I19),_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I19)</f>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J19),_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J19)</f>
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K19),_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K19)</f>
+        <v/>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22">
+        <v>0.9</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22">
+        <v>0.6</v>
+      </c>
+      <c r="P22" t="str">
+        <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <f>IF(F22="", "",_xlfn.XLOOKUP(F22,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R22">
+        <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S22">
+        <f>IF(L22="", "", _xlfn.XLOOKUP(L22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.05</v>
+      </c>
+      <c r="T22">
+        <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.01</v>
+      </c>
+      <c r="U22">
+        <f>IF(N22="", "", _xlfn.XLOOKUP(N22, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V22" t="str">
+        <f>IF(F22="","",I22*J22/6.25)</f>
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <f>IF(F22="", "", V22*(1-K22))</f>
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <f>IF(F22="", "", G22*W22*H22)</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>IF(ISBLANK(L22), "", $X$21*M22)</f>
+        <v>603.9589740624001</v>
+      </c>
+      <c r="Z22">
+        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <v>573.15706638521772</v>
+      </c>
+      <c r="AA22" t="str">
+        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>IF(N22="directApplication", "", $AA$21*O22)</f>
+        <v>343.89423983113062</v>
+      </c>
+      <c r="AC22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <f>IF(E22="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <f>IF(F22="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <f>IF(F22="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <f t="shared" ref="AH22:AH30" si="5">IF(L25="pastureRangeAndPaddock", Y25*AD$21*AC$21, "")</f>
+        <v/>
+      </c>
+      <c r="AI22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A20), "", 'Input Scenarios'!A20)</f>
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B20), "", 'Input Scenarios'!B20)</f>
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C20), "", 'Input Scenarios'!C20)</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D20), "", 'Input Scenarios'!D20)</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E20), "", 'Input Scenarios'!E20)</f>
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F20), "", 'Input Scenarios'!F20)</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G20), "", 'Input Scenarios'!G20)</f>
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H20), "", 'Input Scenarios'!H20)</f>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I20),_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I20)</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J20),_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J20)</f>
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K20),_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K20)</f>
+        <v/>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23" t="str">
+        <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <f>IF(F23="", "",_xlfn.XLOOKUP(F23,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R23">
+        <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S23">
+        <f>IF(L23="", "", _xlfn.XLOOKUP(L23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.4</v>
+      </c>
+      <c r="T23">
+        <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <f>IF(N23="", "", _xlfn.XLOOKUP(N23, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V23" t="str">
+        <f>IF(F23="","",I23*J23/6.25)</f>
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <f>IF(F23="", "", V23*(1-K23))</f>
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <f>IF(F23="", "", G23*W23*H23)</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>IF(ISBLANK(L23), "", $X$21*M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" t="str">
+        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>IF(N23="directApplication", "", $AA$21*O23)</f>
+        <v>0</v>
+      </c>
+      <c r="AC23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <f>IF(E23="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <f>IF(F23="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <f>IF(F23="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A21), "", 'Input Scenarios'!A21)</f>
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B21), "", 'Input Scenarios'!B21)</f>
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C21), "", 'Input Scenarios'!C21)</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D21), "", 'Input Scenarios'!D21)</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E21), "", 'Input Scenarios'!E21)</f>
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F21), "", 'Input Scenarios'!F21)</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G21), "", 'Input Scenarios'!G21)</f>
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H21), "", 'Input Scenarios'!H21)</f>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I21),_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I21)</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J21),_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J21)</f>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K21),_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K21)</f>
+        <v/>
+      </c>
+      <c r="L24" t="s">
+        <v>40</v>
+      </c>
+      <c r="M24">
+        <v>0.1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" t="str">
+        <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <f>IF(F24="", "",_xlfn.XLOOKUP(F24,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R24">
+        <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.02</v>
+      </c>
+      <c r="S24" t="str">
+        <f>IF(L24="", "", _xlfn.XLOOKUP(L24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="T24">
+        <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <f>IF(N24="", "", _xlfn.XLOOKUP(N24, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V24" t="str">
+        <f>IF(F24="","",I24*J24/6.25)</f>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f>IF(F24="", "", V24*(1-K24))</f>
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <f>IF(F24="", "", G24*W24*H24)</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>IF(ISBLANK(L24), "", $X$21*M24)</f>
+        <v>67.106552673600007</v>
+      </c>
+      <c r="Z24" t="str">
+        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <v/>
+      </c>
+      <c r="AA24" t="str">
+        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>IF(N24="directApplication", "", $AA$21*O24)</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD24" t="str">
+        <f>IF(E24="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <f>IF(F24="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <f>IF(F24="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A22), "", 'Input Scenarios'!A22)</f>
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B22), "", 'Input Scenarios'!B22)</f>
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C22), "", 'Input Scenarios'!C22)</f>
+        <v/>
+      </c>
+      <c r="D25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D22), "", 'Input Scenarios'!D22)</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E22), "", 'Input Scenarios'!E22)</f>
+        <v/>
+      </c>
+      <c r="F25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F22), "", 'Input Scenarios'!F22)</f>
+        <v/>
+      </c>
+      <c r="G25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G22), "", 'Input Scenarios'!G22)</f>
+        <v/>
+      </c>
+      <c r="H25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H22), "", 'Input Scenarios'!H22)</f>
+        <v/>
+      </c>
+      <c r="I25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I22),_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I22)</f>
+        <v/>
+      </c>
+      <c r="J25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J22),_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J22)</f>
+        <v/>
+      </c>
+      <c r="K25" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K22),_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K22)</f>
+        <v/>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O25" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="P25" s="11" t="str">
+        <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="11" t="str">
+        <f>IF(F25="", "",_xlfn.XLOOKUP(F25,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <f>IF(L25="", "", _xlfn.XLOOKUP(L25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="U25" t="str">
+        <f>IF(N25="", "", _xlfn.XLOOKUP(N25, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="V25" s="11" t="str">
+        <f>IF(F25="","",I25*J25/6.25)</f>
+        <v/>
+      </c>
+      <c r="W25" s="11" t="str">
+        <f>IF(F25="", "", V25*(1-K25))</f>
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <f>IF(F25="", "", G25*W25*H25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="11" t="str">
+        <f>IF(ISBLANK(L25), "", $X$21*M25)</f>
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
+        <v/>
+      </c>
+      <c r="AA25" s="11" t="str">
+        <f>IF(F25="", "",SUM(Z25:Z29))</f>
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <f>IF(N25="directApplication", "", $AA$21*O25)</f>
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD25" t="str">
+        <f>IF(E25="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <f>IF(F25="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <f>IF(F25="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH25" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A23), "", 'Input Scenarios'!A23)</f>
+        <v>NT</v>
+      </c>
+      <c r="B26" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B23), "", 'Input Scenarios'!B23)</f>
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C23), "", 'Input Scenarios'!C23)</f>
+        <v>Non-irrigated crop (high rainfall)</v>
+      </c>
+      <c r="D26" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D23), "", 'Input Scenarios'!D23)</f>
+        <v>dry</v>
+      </c>
+      <c r="E26" t="b">
+        <f>IF(ISBLANK('Input Scenarios'!E23), "", 'Input Scenarios'!E23)</f>
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F23), "", 'Input Scenarios'!F23)</f>
+        <v>meatOther</v>
+      </c>
+      <c r="G26">
+        <f>IF(ISBLANK('Input Scenarios'!G23), "", 'Input Scenarios'!G23)</f>
+        <v>1234</v>
+      </c>
+      <c r="H26">
+        <f>IF(ISBLANK('Input Scenarios'!H23), "", 'Input Scenarios'!H23)</f>
+        <v>150</v>
+      </c>
+      <c r="I26">
+        <f>IF(ISBLANK('Input Scenarios'!I23),_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I23)</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J26">
+        <f>IF(ISBLANK('Input Scenarios'!J23),_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J23)</f>
+        <v>0.23</v>
+      </c>
+      <c r="K26">
+        <f>IF(ISBLANK('Input Scenarios'!K23),_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K23)</f>
+        <v>0.47</v>
+      </c>
+      <c r="L26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26">
+        <v>0.1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>19</v>
+      </c>
+      <c r="O26">
+        <v>0.5</v>
+      </c>
+      <c r="P26">
+        <f>IF(F26="", "",_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q26">
+        <f>IF(F26="", "",_xlfn.XLOOKUP(F26,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v>0.15</v>
+      </c>
+      <c r="R26">
+        <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S26">
+        <f>IF(L26="", "", _xlfn.XLOOKUP(L26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.3</v>
+      </c>
+      <c r="T26">
+        <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U26">
+        <f>IF(N26="", "", _xlfn.XLOOKUP(N26, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V26">
+        <f>IF(F26="","",I26*J26/6.25)</f>
+        <v>3.4223999999999999E-3</v>
+      </c>
+      <c r="W26">
+        <f>IF(F26="", "", V26*(1-K26))</f>
+        <v>1.813872E-3</v>
+      </c>
+      <c r="X26">
+        <f>IF(F26="", "", G26*W26*H26)</f>
+        <v>335.74770719999998</v>
+      </c>
+      <c r="Y26">
+        <f>IF(ISBLANK(L26), "", $X$26*M26)</f>
+        <v>33.574770719999997</v>
+      </c>
+      <c r="Z26">
+        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <v>23.46876473328</v>
+      </c>
+      <c r="AA26">
+        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <v>23.46876473328</v>
+      </c>
+      <c r="AB26">
+        <f>IF(N26="directApplication", "", $AA$26*O26)</f>
+        <v>11.73438236664</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD26">
+        <f>IF(E26="","",Constants!$M$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="AE26">
+        <f>IF(F26="","",Constants!$L$2)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AF26">
+        <f>IF(F26="","",Constants!$J$2)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="1"/>
+        <v>0.23468764733280001</v>
+      </c>
+      <c r="AH26">
+        <f>IF(L29="pastureRangeAndPaddock", Y29*AD$26*AC$26, "")</f>
+        <v>6.0434587295999993</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="3"/>
+        <v>1.0852224451555266E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A24), "", 'Input Scenarios'!A24)</f>
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B24), "", 'Input Scenarios'!B24)</f>
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C24), "", 'Input Scenarios'!C24)</f>
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D24), "", 'Input Scenarios'!D24)</f>
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E24), "", 'Input Scenarios'!E24)</f>
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F24), "", 'Input Scenarios'!F24)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G24), "", 'Input Scenarios'!G24)</f>
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H24), "", 'Input Scenarios'!H24)</f>
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I24),_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I24)</f>
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J24),_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J24)</f>
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K24),_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K24)</f>
+        <v/>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27">
+        <v>0.25</v>
+      </c>
+      <c r="P27" t="str">
+        <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <f>IF(F27="", "",_xlfn.XLOOKUP(F27,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R27">
+        <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S27">
+        <f>IF(L27="", "", _xlfn.XLOOKUP(L27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.05</v>
+      </c>
+      <c r="T27">
+        <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.01</v>
+      </c>
+      <c r="U27">
+        <f>IF(N27="", "", _xlfn.XLOOKUP(N27, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="V27" t="str">
+        <f>IF(F27="","",I27*J27/6.25)</f>
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <f>IF(F27="", "", V27*(1-K27))</f>
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <f>IF(F27="", "", G27*W27*H27)</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>IF(ISBLANK(L27), "", $X$26*M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" t="str">
+        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>IF(N27="directApplication", "", $AA$26*O27)</f>
+        <v>5.8671911833200001</v>
+      </c>
+      <c r="AC27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD27" t="str">
+        <f>IF(E27="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE27" t="str">
+        <f>IF(F27="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF27" t="str">
+        <f>IF(F27="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH27" t="str">
+        <f t="shared" ref="AH27:AH30" si="6">IF(L30="pastureRangeAndPaddock", Y30*AD$26*AC$26, "")</f>
+        <v/>
+      </c>
+      <c r="AI27" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A25), "", 'Input Scenarios'!A25)</f>
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B25), "", 'Input Scenarios'!B25)</f>
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C25), "", 'Input Scenarios'!C25)</f>
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D25), "", 'Input Scenarios'!D25)</f>
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E25), "", 'Input Scenarios'!E25)</f>
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F25), "", 'Input Scenarios'!F25)</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G25), "", 'Input Scenarios'!G25)</f>
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H25), "", 'Input Scenarios'!H25)</f>
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I25),_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I25)</f>
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J25),_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J25)</f>
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K25),_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K25)</f>
+        <v/>
+      </c>
+      <c r="L28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O28">
+        <v>0.25</v>
+      </c>
+      <c r="P28" t="str">
+        <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <f>IF(F28="", "",_xlfn.XLOOKUP(F28,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R28">
+        <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>1E-3</v>
+      </c>
+      <c r="S28">
+        <f>IF(L28="", "", _xlfn.XLOOKUP(L28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0.4</v>
+      </c>
+      <c r="T28">
+        <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <f>IF(N28="", "", _xlfn.XLOOKUP(N28, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V28" t="str">
+        <f>IF(F28="","",I28*J28/6.25)</f>
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <f>IF(F28="", "", V28*(1-K28))</f>
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <f>IF(F28="", "", G28*W28*H28)</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>IF(ISBLANK(L28), "", $X$26*M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" t="str">
+        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>IF(N28="directApplication", "", $AA$26*O28)</f>
+        <v>5.8671911833200001</v>
+      </c>
+      <c r="AC28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD28" t="str">
+        <f>IF(E28="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE28" t="str">
+        <f>IF(F28="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF28" t="str">
+        <f>IF(F28="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH28" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A26), "", 'Input Scenarios'!A26)</f>
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B26), "", 'Input Scenarios'!B26)</f>
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C26), "", 'Input Scenarios'!C26)</f>
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D26), "", 'Input Scenarios'!D26)</f>
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E26), "", 'Input Scenarios'!E26)</f>
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F26), "", 'Input Scenarios'!F26)</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G26), "", 'Input Scenarios'!G26)</f>
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H26), "", 'Input Scenarios'!H26)</f>
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I26),_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I26)</f>
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J26),_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J26)</f>
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K26),_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K26)</f>
+        <v/>
+      </c>
+      <c r="L29" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29">
+        <v>0.9</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="str">
+        <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <f>IF(F29="", "",_xlfn.XLOOKUP(F29,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R29">
+        <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0.02</v>
+      </c>
+      <c r="S29" t="str">
+        <f>IF(L29="", "", _xlfn.XLOOKUP(L29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="T29">
+        <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <f>IF(N29="", "", _xlfn.XLOOKUP(N29, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>0</v>
+      </c>
+      <c r="V29" t="str">
+        <f>IF(F29="","",I29*J29/6.25)</f>
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <f>IF(F29="", "", V29*(1-K29))</f>
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <f>IF(F29="", "", G29*W29*H29)</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>IF(ISBLANK(L29), "", $X$26*M29)</f>
+        <v>302.17293647999998</v>
+      </c>
+      <c r="Z29" t="str">
+        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>IF(N29="directApplication", "", $AA$26*O29)</f>
+        <v>0</v>
+      </c>
+      <c r="AC29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD29" t="str">
+        <f>IF(E29="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE29" t="str">
+        <f>IF(F29="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF29" t="str">
+        <f>IF(F29="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:35" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!A27), "", 'Input Scenarios'!A27)</f>
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!B27), "", 'Input Scenarios'!B27)</f>
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!C27), "", 'Input Scenarios'!C27)</f>
+        <v/>
+      </c>
+      <c r="D30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!D27), "", 'Input Scenarios'!D27)</f>
+        <v/>
+      </c>
+      <c r="E30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!E27), "", 'Input Scenarios'!E27)</f>
+        <v/>
+      </c>
+      <c r="F30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!F27), "", 'Input Scenarios'!F27)</f>
+        <v/>
+      </c>
+      <c r="G30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!G27), "", 'Input Scenarios'!G27)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!H27), "", 'Input Scenarios'!H27)</f>
+        <v/>
+      </c>
+      <c r="I30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!I27),_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!B$2:B$5), 'Input Scenarios'!I27)</f>
+        <v/>
+      </c>
+      <c r="J30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!J27),_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!D$2:D$5), 'Input Scenarios'!J27)</f>
+        <v/>
+      </c>
+      <c r="K30" s="11" t="str">
+        <f>IF(ISBLANK('Input Scenarios'!K27),_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!E$2:E$5), 'Input Scenarios'!K27)</f>
+        <v/>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O30" s="11">
+        <v>0</v>
+      </c>
+      <c r="P30" s="11" t="str">
+        <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!C$2:C$5))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="11" t="str">
+        <f>IF(F30="", "",_xlfn.XLOOKUP(F30,Constants!$A$2:$A$5,Constants!F$2:F$5))</f>
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <f>IF(L30="", "", _xlfn.XLOOKUP(L30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$D$9:$D$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="U30" t="str">
+        <f>IF(N30="", "", _xlfn.XLOOKUP(N30, Constants!$B$9:$B$17,Constants!$C$9:$C$17))</f>
+        <v>N/A</v>
+      </c>
+      <c r="V30" s="11" t="str">
+        <f>IF(F30="","",I30*J30/6.25)</f>
+        <v/>
+      </c>
+      <c r="W30" s="11" t="str">
+        <f>IF(F30="", "", V30*(1-K30))</f>
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <f>IF(F30="", "", G30*W30*H30)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="11" t="str">
+        <f>IF(ISBLANK(L30), "", $X$26*M30)</f>
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
+        <v/>
+      </c>
+      <c r="AA30" s="11" t="str">
+        <f>IF(F30="", "",SUM(Z30:Z34))</f>
+        <v/>
+      </c>
+      <c r="AB30" t="str">
+        <f>IF(N30="directApplication", "", $AA$26*O30)</f>
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD30" t="str">
+        <f>IF(E30="","",Constants!$M$2)</f>
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <f>IF(F30="","",Constants!$L$2)</f>
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <f>IF(F30="","",Constants!$J$2)</f>
+        <v/>
+      </c>
+      <c r="AG30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH30" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI30" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="AI31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F87875-5D60-8742-BBBA-69D98D824AF5}">
   <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10437,7 +13102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065437CD-FBA0-EB46-AB0B-6A14664DDC76}">
   <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10473,6 +13138,12 @@
       <c r="K1" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -10505,6 +13176,12 @@
       </c>
       <c r="K2">
         <v>0.21</v>
+      </c>
+      <c r="L2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="M2">
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">

--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC3F89A-01DC-D742-AE73-E34035428ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19870AA3-BF9B-9143-9193-C594C696099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19870AA3-BF9B-9143-9193-C594C696099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACA305F-99B4-AC45-BB86-63221D8D6F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3775,15 +3775,15 @@
         <v>0.2</v>
       </c>
       <c r="V11">
-        <f>IF(F11="","",I11*J11/6.25)</f>
+        <f t="shared" ref="V11:V30" si="0">IF(F11="","",I11*J11/6.25)</f>
         <v>2.6144000000000002E-3</v>
       </c>
       <c r="W11">
-        <f>IF(F11="", "", V11*(1-K11))</f>
+        <f t="shared" ref="W11:W30" si="1">IF(F11="", "", V11*(1-K11))</f>
         <v>1.6993600000000002E-3</v>
       </c>
       <c r="X11">
-        <f>IF(F11="", "", G11*W11*H11)</f>
+        <f t="shared" ref="X11:X30" si="2">IF(F11="", "", G11*W11*H11)</f>
         <v>424.84000000000003</v>
       </c>
       <c r="Y11">
@@ -3791,11 +3791,11 @@
         <v>42.484000000000009</v>
       </c>
       <c r="Z11">
-        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <f t="shared" ref="Z11:Z30" si="3">IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
         <v>29.69631600000001</v>
       </c>
       <c r="AA11">
-        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <f t="shared" ref="AA11:AA30" si="4">IF(F11="", "",SUM(Z11:Z15))</f>
         <v>186.67469600000001</v>
       </c>
       <c r="AB11">
@@ -3811,11 +3811,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE11">
-        <f>IF(L11="", "", Y11*R11*AD11)</f>
+        <f t="shared" ref="AE11:AE30" si="5">IF(L11="", "", Y11*R11*AD11)</f>
         <v>6.6760571428571433E-2</v>
       </c>
       <c r="AF11">
-        <f>IF(N11="directApplication", "", AB11*T11*AD11)</f>
+        <f t="shared" ref="AF11:AF30" si="6">IF(N11="directApplication", "", AB11*T11*AD11)</f>
         <v>0.22000946314285716</v>
       </c>
       <c r="AG11">
@@ -3823,7 +3823,7 @@
         <v>1.6022537142857147E-3</v>
       </c>
       <c r="AH11">
-        <f>IF(F11="","",SUM(AE11:AF15)/1000)</f>
+        <f t="shared" ref="AH11:AH30" si="7">IF(F11="","",SUM(AE11:AF15)/1000)</f>
         <v>6.5481105077142866E-3</v>
       </c>
       <c r="AI11">
@@ -3913,15 +3913,15 @@
         <v>0.2</v>
       </c>
       <c r="V12" t="str">
-        <f>IF(F12="","",I12*J12/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W12" t="str">
-        <f>IF(F12="", "", V12*(1-K12))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X12" t="str">
-        <f>IF(F12="", "", G12*W12*H12)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y12">
@@ -3929,11 +3929,11 @@
         <v>84.968000000000018</v>
       </c>
       <c r="Z12">
-        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <f t="shared" si="3"/>
         <v>80.634632000000011</v>
       </c>
       <c r="AA12" t="str">
-        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB12">
@@ -3949,11 +3949,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE12">
-        <f>IF(L12="", "", Y12*R12*AD12)</f>
+        <f t="shared" si="5"/>
         <v>0.13352114285714287</v>
       </c>
       <c r="AF12">
-        <f>IF(N12="directApplication", "", AB12*T12*AD12)</f>
+        <f t="shared" si="6"/>
         <v>0.58669190171428576</v>
       </c>
       <c r="AG12" t="str">
@@ -3961,11 +3961,11 @@
         <v/>
       </c>
       <c r="AH12" t="str">
-        <f>IF(F12="","",SUM(AE12:AF16)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI12" t="str">
-        <f t="shared" ref="AI12:AI30" si="0">IF(AG12="", "", AG12+AH12)</f>
+        <f t="shared" ref="AI12:AI30" si="8">IF(AG12="", "", AG12+AH12)</f>
         <v/>
       </c>
     </row>
@@ -4051,15 +4051,15 @@
         <v>0</v>
       </c>
       <c r="V13" t="str">
-        <f>IF(F13="","",I13*J13/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W13" t="str">
-        <f>IF(F13="", "", V13*(1-K13))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X13" t="str">
-        <f>IF(F13="", "", G13*W13*H13)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y13">
@@ -4067,11 +4067,11 @@
         <v>127.452</v>
       </c>
       <c r="Z13">
-        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <f t="shared" si="3"/>
         <v>76.343747999999991</v>
       </c>
       <c r="AA13" t="str">
-        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB13">
@@ -4087,11 +4087,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE13">
-        <f>IF(L13="", "", Y13*R13*AD13)</f>
+        <f t="shared" si="5"/>
         <v>0.20028171428571429</v>
       </c>
       <c r="AF13">
-        <f>IF(N13="directApplication", "", AB13*T13*AD13)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG13" t="str">
@@ -4099,11 +4099,11 @@
         <v/>
       </c>
       <c r="AH13" t="str">
-        <f>IF(F13="","",SUM(AE13:AF17)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -4189,15 +4189,15 @@
         <v>0</v>
       </c>
       <c r="V14" t="str">
-        <f>IF(F14="","",I14*J14/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W14" t="str">
-        <f>IF(F14="", "", V14*(1-K14))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X14" t="str">
-        <f>IF(F14="", "", G14*W14*H14)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y14">
@@ -4205,11 +4205,11 @@
         <v>169.93600000000004</v>
       </c>
       <c r="Z14" t="str">
-        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA14" t="str">
-        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB14">
@@ -4225,11 +4225,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE14">
-        <f>IF(L14="", "", Y14*R14*AD14)</f>
+        <f t="shared" si="5"/>
         <v>5.3408457142857158</v>
       </c>
       <c r="AF14">
-        <f>IF(N14="directApplication", "", AB14*T14*AD14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG14" t="str">
@@ -4237,11 +4237,11 @@
         <v/>
       </c>
       <c r="AH14" t="str">
-        <f>IF(F14="","",SUM(AE14:AF18)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -4321,15 +4321,15 @@
         <v>N/A</v>
       </c>
       <c r="V15" s="11" t="str">
-        <f>IF(F15="","",I15*J15/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W15" s="11" t="str">
-        <f>IF(F15="", "", V15*(1-K15))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X15" t="str">
-        <f>IF(F15="", "", G15*W15*H15)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y15" s="11" t="str">
@@ -4337,11 +4337,11 @@
         <v/>
       </c>
       <c r="Z15" t="str">
-        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA15" s="11" t="str">
-        <f>IF(F15="", "",SUM(Z15:Z19))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB15" t="str">
@@ -4357,11 +4357,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE15" t="str">
-        <f>IF(L15="", "", Y15*R15*AD15)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AF15" t="str">
-        <f>IF(N15="directApplication", "", AB15*T15*AD15)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AG15" t="str">
@@ -4369,11 +4369,11 @@
         <v/>
       </c>
       <c r="AH15" t="str">
-        <f>IF(F15="","",SUM(AE15:AF19)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -4459,15 +4459,15 @@
         <v>0.2</v>
       </c>
       <c r="V16">
-        <f>IF(F16="","",I16*J16/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.1312000000000002E-3</v>
       </c>
       <c r="W16">
-        <f>IF(F16="", "", V16*(1-K16))</f>
+        <f t="shared" si="1"/>
         <v>2.1292159999999997E-3</v>
       </c>
       <c r="X16">
-        <f>IF(F16="", "", G16*W16*H16)</f>
+        <f t="shared" si="2"/>
         <v>598.84199999999987</v>
       </c>
       <c r="Y16">
@@ -4475,11 +4475,11 @@
         <v>239.53679999999997</v>
       </c>
       <c r="Z16">
-        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <f t="shared" si="3"/>
         <v>167.4362232</v>
       </c>
       <c r="AA16">
-        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <f t="shared" si="4"/>
         <v>409.66781219999996</v>
       </c>
       <c r="AB16">
@@ -4495,11 +4495,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE16">
-        <f>IF(L16="", "", Y16*R16*AD16)</f>
+        <f t="shared" si="5"/>
         <v>0.37641497142857139</v>
       </c>
       <c r="AF16">
-        <f>IF(N16="directApplication", "", AB16*T16*AD16)</f>
+        <f t="shared" si="6"/>
         <v>0.64376370488571433</v>
       </c>
       <c r="AG16">
@@ -4507,11 +4507,11 @@
         <v>1.8820748571428568E-4</v>
       </c>
       <c r="AH16">
-        <f>IF(F16="","",SUM(AE16:AF20)/1000)</f>
+        <f t="shared" si="7"/>
         <v>4.9821815099571429E-3</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>5.1703889956714287E-3</v>
       </c>
     </row>
@@ -4597,15 +4597,15 @@
         <v>0.2</v>
       </c>
       <c r="V17" t="str">
-        <f>IF(F17="","",I17*J17/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W17" t="str">
-        <f>IF(F17="", "", V17*(1-K17))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X17" t="str">
-        <f>IF(F17="", "", G17*W17*H17)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y17">
@@ -4613,11 +4613,11 @@
         <v>179.65259999999995</v>
       </c>
       <c r="Z17">
-        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <f t="shared" si="3"/>
         <v>170.49031739999995</v>
       </c>
       <c r="AA17" t="str">
-        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB17">
@@ -4633,11 +4633,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE17">
-        <f>IF(L17="", "", Y17*R17*AD17)</f>
+        <f t="shared" si="5"/>
         <v>0.28231122857142849</v>
       </c>
       <c r="AF17">
-        <f>IF(N17="directApplication", "", AB17*T17*AD17)</f>
+        <f t="shared" si="6"/>
         <v>1.6094092622142855</v>
       </c>
       <c r="AG17" t="str">
@@ -4645,11 +4645,11 @@
         <v/>
       </c>
       <c r="AH17" t="str">
-        <f>IF(F17="","",SUM(AE17:AF21)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -4735,15 +4735,15 @@
         <v>0</v>
       </c>
       <c r="V18" t="str">
-        <f>IF(F18="","",I18*J18/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W18" t="str">
-        <f>IF(F18="", "", V18*(1-K18))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X18" t="str">
-        <f>IF(F18="", "", G18*W18*H18)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y18">
@@ -4751,11 +4751,11 @@
         <v>119.76839999999999</v>
       </c>
       <c r="Z18">
-        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <f t="shared" si="3"/>
         <v>71.74127159999999</v>
       </c>
       <c r="AA18" t="str">
-        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB18">
@@ -4771,11 +4771,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE18">
-        <f>IF(L18="", "", Y18*R18*AD18)</f>
+        <f t="shared" si="5"/>
         <v>0.18820748571428569</v>
       </c>
       <c r="AF18">
-        <f>IF(N18="directApplication", "", AB18*T18*AD18)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG18" t="str">
@@ -4783,11 +4783,11 @@
         <v/>
       </c>
       <c r="AH18" t="str">
-        <f>IF(F18="","",SUM(AE18:AF22)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -4873,15 +4873,15 @@
         <v>0</v>
       </c>
       <c r="V19" t="str">
-        <f>IF(F19="","",I19*J19/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W19" t="str">
-        <f>IF(F19="", "", V19*(1-K19))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f>IF(F19="", "", G19*W19*H19)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y19">
@@ -4889,11 +4889,11 @@
         <v>59.884199999999993</v>
       </c>
       <c r="Z19" t="str">
-        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA19" t="str">
-        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB19">
@@ -4909,11 +4909,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE19">
-        <f>IF(L19="", "", Y19*R19*AD19)</f>
+        <f t="shared" si="5"/>
         <v>1.8820748571428572</v>
       </c>
       <c r="AF19">
-        <f>IF(N19="directApplication", "", AB19*T19*AD19)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG19" t="str">
@@ -4921,11 +4921,11 @@
         <v/>
       </c>
       <c r="AH19" t="str">
-        <f>IF(F19="","",SUM(AE19:AF23)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5005,15 +5005,15 @@
         <v>N/A</v>
       </c>
       <c r="V20" s="11" t="str">
-        <f>IF(F20="","",I20*J20/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W20" s="11" t="str">
-        <f>IF(F20="", "", V20*(1-K20))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X20" t="str">
-        <f>IF(F20="", "", G20*W20*H20)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y20" s="11" t="str">
@@ -5021,11 +5021,11 @@
         <v/>
       </c>
       <c r="Z20" t="str">
-        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA20" s="11" t="str">
-        <f>IF(F20="", "",SUM(Z20:Z24))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB20" t="str">
@@ -5041,11 +5041,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE20" t="str">
-        <f>IF(L20="", "", Y20*R20*AD20)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AF20" t="str">
-        <f>IF(N20="directApplication", "", AB20*T20*AD20)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AG20" t="str">
@@ -5053,11 +5053,11 @@
         <v/>
       </c>
       <c r="AH20" t="str">
-        <f>IF(F20="","",SUM(AE20:AF24)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5143,15 +5143,15 @@
         <v>0.2</v>
       </c>
       <c r="V21">
-        <f>IF(F21="","",I21*J21/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W21">
-        <f>IF(F21="", "", V21*(1-K21))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X21">
-        <f>IF(F21="", "", G21*W21*H21)</f>
+        <f t="shared" si="2"/>
         <v>671.06552673600004</v>
       </c>
       <c r="Y21">
@@ -5159,11 +5159,11 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA21">
-        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <f t="shared" si="4"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AB21">
@@ -5179,11 +5179,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE21">
-        <f>IF(L21="", "", Y21*R21*AD21)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF21">
-        <f>IF(N21="directApplication", "", AB21*T21*AD21)</f>
+        <f t="shared" si="6"/>
         <v>1.5311481630576531</v>
       </c>
       <c r="AG21">
@@ -5191,11 +5191,11 @@
         <v>6.327189252082286E-4</v>
       </c>
       <c r="AH21">
-        <f>IF(F21="","",SUM(AE21:AF25)/1000)</f>
+        <f t="shared" si="7"/>
         <v>9.9933419751009056E-3</v>
       </c>
       <c r="AI21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>1.0626060900309134E-2</v>
       </c>
     </row>
@@ -5281,15 +5281,15 @@
         <v>0.2</v>
       </c>
       <c r="V22" t="str">
-        <f>IF(F22="","",I22*J22/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W22" t="str">
-        <f>IF(F22="", "", V22*(1-K22))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X22" t="str">
-        <f>IF(F22="", "", G22*W22*H22)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y22">
@@ -5297,11 +5297,11 @@
         <v>603.9589740624001</v>
       </c>
       <c r="Z22">
-        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <f t="shared" si="3"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AA22" t="str">
-        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB22">
@@ -5317,11 +5317,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE22">
-        <f>IF(L22="", "", Y22*R22*AD22)</f>
+        <f t="shared" si="5"/>
         <v>0.94907838781234299</v>
       </c>
       <c r="AF22">
-        <f>IF(N22="directApplication", "", AB22*T22*AD22)</f>
+        <f t="shared" si="6"/>
         <v>5.4040523402034806</v>
       </c>
       <c r="AG22" t="str">
@@ -5329,11 +5329,11 @@
         <v/>
       </c>
       <c r="AH22" t="str">
-        <f>IF(F22="","",SUM(AE22:AF26)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5419,15 +5419,15 @@
         <v>0</v>
       </c>
       <c r="V23" t="str">
-        <f>IF(F23="","",I23*J23/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W23" t="str">
-        <f>IF(F23="", "", V23*(1-K23))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X23" t="str">
-        <f>IF(F23="", "", G23*W23*H23)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y23">
@@ -5435,11 +5435,11 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA23" t="str">
-        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB23">
@@ -5455,11 +5455,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE23">
-        <f>IF(L23="", "", Y23*R23*AD23)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF23">
-        <f>IF(N23="directApplication", "", AB23*T23*AD23)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG23" t="str">
@@ -5467,11 +5467,11 @@
         <v/>
       </c>
       <c r="AH23" t="str">
-        <f>IF(F23="","",SUM(AE23:AF27)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5557,15 +5557,15 @@
         <v>0</v>
       </c>
       <c r="V24" t="str">
-        <f>IF(F24="","",I24*J24/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W24" t="str">
-        <f>IF(F24="", "", V24*(1-K24))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X24" t="str">
-        <f>IF(F24="", "", G24*W24*H24)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y24">
@@ -5573,11 +5573,11 @@
         <v>67.106552673600007</v>
       </c>
       <c r="Z24" t="str">
-        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA24" t="str">
-        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB24">
@@ -5593,11 +5593,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE24">
-        <f>IF(L24="", "", Y24*R24*AD24)</f>
+        <f t="shared" si="5"/>
         <v>2.1090630840274289</v>
       </c>
       <c r="AF24">
-        <f>IF(N24="directApplication", "", AB24*T24*AD24)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG24" t="str">
@@ -5605,11 +5605,11 @@
         <v/>
       </c>
       <c r="AH24" t="str">
-        <f>IF(F24="","",SUM(AE24:AF28)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5689,15 +5689,15 @@
         <v>N/A</v>
       </c>
       <c r="V25" s="11" t="str">
-        <f>IF(F25="","",I25*J25/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W25" s="11" t="str">
-        <f>IF(F25="", "", V25*(1-K25))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X25" t="str">
-        <f>IF(F25="", "", G25*W25*H25)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y25" s="11" t="str">
@@ -5705,11 +5705,11 @@
         <v/>
       </c>
       <c r="Z25" t="str">
-        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA25" s="11" t="str">
-        <f>IF(F25="", "",SUM(Z25:Z29))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB25" t="str">
@@ -5725,11 +5725,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE25" t="str">
-        <f>IF(L25="", "", Y25*R25*AD25)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AF25" t="str">
-        <f>IF(N25="directApplication", "", AB25*T25*AD25)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AG25" t="str">
@@ -5737,11 +5737,11 @@
         <v/>
       </c>
       <c r="AH25" t="str">
-        <f>IF(F25="","",SUM(AE25:AF29)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5827,15 +5827,15 @@
         <v>0.2</v>
       </c>
       <c r="V26">
-        <f>IF(F26="","",I26*J26/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W26">
-        <f>IF(F26="", "", V26*(1-K26))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X26">
-        <f>IF(F26="", "", G26*W26*H26)</f>
+        <f t="shared" si="2"/>
         <v>335.74770719999998</v>
       </c>
       <c r="Y26">
@@ -5843,11 +5843,11 @@
         <v>33.574770719999997</v>
       </c>
       <c r="Z26">
-        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <f t="shared" si="3"/>
         <v>23.46876473328</v>
       </c>
       <c r="AA26">
-        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <f t="shared" si="4"/>
         <v>23.46876473328</v>
       </c>
       <c r="AB26">
@@ -5863,11 +5863,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE26">
-        <f>IF(L26="", "", Y26*R26*AD26)</f>
+        <f t="shared" si="5"/>
         <v>5.2760353988571415E-2</v>
       </c>
       <c r="AF26">
-        <f>IF(N26="directApplication", "", AB26*T26*AD26)</f>
+        <f t="shared" si="6"/>
         <v>9.2198718595028567E-2</v>
       </c>
       <c r="AG26">
@@ -5875,11 +5875,11 @@
         <v>9.4968637179428561E-4</v>
       </c>
       <c r="AH26">
-        <f>IF(F26="","",SUM(AE26:AF30)/1000)</f>
+        <f t="shared" si="7"/>
         <v>9.7340215091214852E-3</v>
       </c>
       <c r="AI26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>1.0683707880915772E-2</v>
       </c>
     </row>
@@ -5965,15 +5965,15 @@
         <v>0.2</v>
       </c>
       <c r="V27" t="str">
-        <f>IF(F27="","",I27*J27/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W27" t="str">
-        <f>IF(F27="", "", V27*(1-K27))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X27" t="str">
-        <f>IF(F27="", "", G27*W27*H27)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y27">
@@ -5981,11 +5981,11 @@
         <v>0</v>
       </c>
       <c r="Z27">
-        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA27" t="str">
-        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB27">
@@ -6001,11 +6001,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE27">
-        <f>IF(L27="", "", Y27*R27*AD27)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF27">
-        <f>IF(N27="directApplication", "", AB27*T27*AD27)</f>
+        <f t="shared" si="6"/>
         <v>9.2198718595028567E-2</v>
       </c>
       <c r="AG27" t="str">
@@ -6013,11 +6013,11 @@
         <v/>
       </c>
       <c r="AH27" t="str">
-        <f>IF(F27="","",SUM(AE27:AF31)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -6103,15 +6103,15 @@
         <v>0</v>
       </c>
       <c r="V28" t="str">
-        <f>IF(F28="","",I28*J28/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W28" t="str">
-        <f>IF(F28="", "", V28*(1-K28))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X28" t="str">
-        <f>IF(F28="", "", G28*W28*H28)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y28">
@@ -6119,11 +6119,11 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA28" t="str">
-        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB28">
@@ -6139,11 +6139,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE28">
-        <f>IF(L28="", "", Y28*R28*AD28)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF28">
-        <f>IF(N28="directApplication", "", AB28*T28*AD28)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG28" t="str">
@@ -6151,11 +6151,11 @@
         <v/>
       </c>
       <c r="AH28" t="str">
-        <f>IF(F28="","",SUM(AE28:AF32)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -6241,15 +6241,15 @@
         <v>0</v>
       </c>
       <c r="V29" t="str">
-        <f>IF(F29="","",I29*J29/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W29" t="str">
-        <f>IF(F29="", "", V29*(1-K29))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X29" t="str">
-        <f>IF(F29="", "", G29*W29*H29)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y29">
@@ -6257,11 +6257,11 @@
         <v>302.17293647999998</v>
       </c>
       <c r="Z29" t="str">
-        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA29" t="str">
-        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB29">
@@ -6277,11 +6277,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE29">
-        <f>IF(L29="", "", Y29*R29*AD29)</f>
+        <f t="shared" si="5"/>
         <v>9.4968637179428566</v>
       </c>
       <c r="AF29">
-        <f>IF(N29="directApplication", "", AB29*T29*AD29)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG29" t="str">
@@ -6289,11 +6289,11 @@
         <v/>
       </c>
       <c r="AH29" t="str">
-        <f>IF(F29="","",SUM(AE29:AF33)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -6373,15 +6373,15 @@
         <v>N/A</v>
       </c>
       <c r="V30" s="11" t="str">
-        <f>IF(F30="","",I30*J30/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W30" s="11" t="str">
-        <f>IF(F30="", "", V30*(1-K30))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X30" t="str">
-        <f>IF(F30="", "", G30*W30*H30)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y30" s="11" t="str">
@@ -6389,11 +6389,11 @@
         <v/>
       </c>
       <c r="Z30" t="str">
-        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA30" s="11" t="str">
-        <f>IF(F30="", "",SUM(Z30:Z34))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB30" t="str">
@@ -6409,11 +6409,11 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AE30" t="str">
-        <f>IF(L30="", "", Y30*R30*AD30)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AF30" t="str">
-        <f>IF(N30="directApplication", "", AB30*T30*AD30)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AG30" t="str">
@@ -6421,11 +6421,11 @@
         <v/>
       </c>
       <c r="AH30" t="str">
-        <f>IF(F30="","",SUM(AE30:AF34)/1000)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -6781,15 +6781,15 @@
         <v>0.2</v>
       </c>
       <c r="V11">
-        <f>IF(F11="","",I11*J11/6.25)</f>
+        <f t="shared" ref="V11:V30" si="0">IF(F11="","",I11*J11/6.25)</f>
         <v>2.6144000000000002E-3</v>
       </c>
       <c r="W11">
-        <f>IF(F11="", "", V11*(1-K11))</f>
+        <f t="shared" ref="W11:W30" si="1">IF(F11="", "", V11*(1-K11))</f>
         <v>1.6993600000000002E-3</v>
       </c>
       <c r="X11">
-        <f>IF(F11="", "", G11*W11*H11)</f>
+        <f t="shared" ref="X11:X30" si="2">IF(F11="", "", G11*W11*H11)</f>
         <v>424.84000000000003</v>
       </c>
       <c r="Y11">
@@ -6797,11 +6797,11 @@
         <v>42.484000000000009</v>
       </c>
       <c r="Z11">
-        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <f t="shared" ref="Z11:Z30" si="3">IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
         <v>29.69631600000001</v>
       </c>
       <c r="AA11">
-        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <f t="shared" ref="AA11:AA30" si="4">IF(F11="", "",SUM(Z11:Z15))</f>
         <v>186.67469600000001</v>
       </c>
       <c r="AB11">
@@ -6813,11 +6813,11 @@
         <v>12.745200000000002</v>
       </c>
       <c r="AD11">
-        <f>IF(OR(N11="", N11="directApplication"), "",AB11*U11)</f>
+        <f t="shared" ref="AD11:AD30" si="5">IF(OR(N11="", N11="directApplication"), "",AB11*U11)</f>
         <v>5.6002408800000012</v>
       </c>
       <c r="AE11">
-        <f>IF(F11="", "", SUM(AC11:AD15))</f>
+        <f t="shared" ref="AE11:AE30" si="6">IF(F11="", "", SUM(AC11:AD15))</f>
         <v>116.72818872000002</v>
       </c>
       <c r="AF11">
@@ -6915,15 +6915,15 @@
         <v>0.2</v>
       </c>
       <c r="V12" t="str">
-        <f>IF(F12="","",I12*J12/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W12" t="str">
-        <f>IF(F12="", "", V12*(1-K12))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X12" t="str">
-        <f>IF(F12="", "", G12*W12*H12)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y12">
@@ -6931,11 +6931,11 @@
         <v>84.968000000000018</v>
       </c>
       <c r="Z12">
-        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <f t="shared" si="3"/>
         <v>80.634632000000011</v>
       </c>
       <c r="AA12" t="str">
-        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB12">
@@ -6947,11 +6947,11 @@
         <v>4.2484000000000011</v>
       </c>
       <c r="AD12">
-        <f>IF(OR(N12="", N12="directApplication"), "",AB12*U12)</f>
+        <f t="shared" si="5"/>
         <v>7.4669878400000007</v>
       </c>
       <c r="AE12" t="str">
-        <f>IF(F12="", "", SUM(AC12:AD16))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF12" t="str">
@@ -6963,7 +6963,7 @@
         <v/>
       </c>
       <c r="AH12" t="str">
-        <f t="shared" ref="AH12:AH30" si="0">IF(AE12="", "", (AE12*AF12*AG12)/1000)</f>
+        <f t="shared" ref="AH12:AH30" si="7">IF(AE12="", "", (AE12*AF12*AG12)/1000)</f>
         <v/>
       </c>
     </row>
@@ -7049,15 +7049,15 @@
         <v>0</v>
       </c>
       <c r="V13" t="str">
-        <f>IF(F13="","",I13*J13/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W13" t="str">
-        <f>IF(F13="", "", V13*(1-K13))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X13" t="str">
-        <f>IF(F13="", "", G13*W13*H13)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y13">
@@ -7065,11 +7065,11 @@
         <v>127.452</v>
       </c>
       <c r="Z13">
-        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <f t="shared" si="3"/>
         <v>76.343747999999991</v>
       </c>
       <c r="AA13" t="str">
-        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB13">
@@ -7081,11 +7081,11 @@
         <v>50.980800000000002</v>
       </c>
       <c r="AD13">
-        <f>IF(OR(N13="", N13="directApplication"), "",AB13*U13)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE13" t="str">
-        <f>IF(F13="", "", SUM(AC13:AD17))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF13" t="str">
@@ -7097,7 +7097,7 @@
         <v/>
       </c>
       <c r="AH13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7183,15 +7183,15 @@
         <v>0</v>
       </c>
       <c r="V14" t="str">
-        <f>IF(F14="","",I14*J14/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W14" t="str">
-        <f>IF(F14="", "", V14*(1-K14))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X14" t="str">
-        <f>IF(F14="", "", G14*W14*H14)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y14">
@@ -7199,11 +7199,11 @@
         <v>169.93600000000004</v>
       </c>
       <c r="Z14" t="str">
-        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA14" t="str">
-        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB14">
@@ -7215,11 +7215,11 @@
         <v>35.686560000000007</v>
       </c>
       <c r="AD14">
-        <f>IF(OR(N14="", N14="directApplication"), "",AB14*U14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE14" t="str">
-        <f>IF(F14="", "", SUM(AC14:AD18))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF14" t="str">
@@ -7231,7 +7231,7 @@
         <v/>
       </c>
       <c r="AH14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7311,15 +7311,15 @@
         <v>N/A</v>
       </c>
       <c r="V15" s="11" t="str">
-        <f>IF(F15="","",I15*J15/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W15" s="11" t="str">
-        <f>IF(F15="", "", V15*(1-K15))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X15" t="str">
-        <f>IF(F15="", "", G15*W15*H15)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y15" s="11" t="str">
@@ -7327,11 +7327,11 @@
         <v/>
       </c>
       <c r="Z15" t="str">
-        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA15" s="11" t="str">
-        <f>IF(F15="", "",SUM(Z15:Z19))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB15" t="str">
@@ -7343,11 +7343,11 @@
         <v/>
       </c>
       <c r="AD15" t="str">
-        <f>IF(OR(N15="", N15="directApplication"), "",AB15*U15)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AE15" t="str">
-        <f>IF(F15="", "", SUM(AC15:AD19))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF15" t="str">
@@ -7359,7 +7359,7 @@
         <v/>
       </c>
       <c r="AH15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7445,15 +7445,15 @@
         <v>0.2</v>
       </c>
       <c r="V16">
-        <f>IF(F16="","",I16*J16/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.1312000000000002E-3</v>
       </c>
       <c r="W16">
-        <f>IF(F16="", "", V16*(1-K16))</f>
+        <f t="shared" si="1"/>
         <v>2.1292159999999997E-3</v>
       </c>
       <c r="X16">
-        <f>IF(F16="", "", G16*W16*H16)</f>
+        <f t="shared" si="2"/>
         <v>598.84199999999987</v>
       </c>
       <c r="Y16">
@@ -7461,11 +7461,11 @@
         <v>239.53679999999997</v>
       </c>
       <c r="Z16">
-        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <f t="shared" si="3"/>
         <v>167.4362232</v>
       </c>
       <c r="AA16">
-        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <f t="shared" si="4"/>
         <v>409.66781219999996</v>
       </c>
       <c r="AB16">
@@ -7477,11 +7477,11 @@
         <v>71.861039999999988</v>
       </c>
       <c r="AD16">
-        <f>IF(OR(N16="", N16="directApplication"), "",AB16*U16)</f>
+        <f t="shared" si="5"/>
         <v>16.386712488000001</v>
       </c>
       <c r="AE16">
-        <f>IF(F16="", "", SUM(AC16:AD20))</f>
+        <f t="shared" si="6"/>
         <v>178.19681509799997</v>
       </c>
       <c r="AF16">
@@ -7493,7 +7493,7 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1.9601649660779996E-3</v>
       </c>
     </row>
@@ -7579,15 +7579,15 @@
         <v>0.2</v>
       </c>
       <c r="V17" t="str">
-        <f>IF(F17="","",I17*J17/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W17" t="str">
-        <f>IF(F17="", "", V17*(1-K17))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X17" t="str">
-        <f>IF(F17="", "", G17*W17*H17)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y17">
@@ -7595,11 +7595,11 @@
         <v>179.65259999999995</v>
       </c>
       <c r="Z17">
-        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <f t="shared" si="3"/>
         <v>170.49031739999995</v>
       </c>
       <c r="AA17" t="str">
-        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB17">
@@ -7611,11 +7611,11 @@
         <v>8.9826299999999986</v>
       </c>
       <c r="AD17">
-        <f>IF(OR(N17="", N17="directApplication"), "",AB17*U17)</f>
+        <f t="shared" si="5"/>
         <v>20.483390610000001</v>
       </c>
       <c r="AE17" t="str">
-        <f>IF(F17="", "", SUM(AC17:AD21))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF17" t="str">
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="AH17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7713,15 +7713,15 @@
         <v>0</v>
       </c>
       <c r="V18" t="str">
-        <f>IF(F18="","",I18*J18/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W18" t="str">
-        <f>IF(F18="", "", V18*(1-K18))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X18" t="str">
-        <f>IF(F18="", "", G18*W18*H18)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y18">
@@ -7729,11 +7729,11 @@
         <v>119.76839999999999</v>
       </c>
       <c r="Z18">
-        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <f t="shared" si="3"/>
         <v>71.74127159999999</v>
       </c>
       <c r="AA18" t="str">
-        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB18">
@@ -7745,11 +7745,11 @@
         <v>47.907359999999997</v>
       </c>
       <c r="AD18">
-        <f>IF(OR(N18="", N18="directApplication"), "",AB18*U18)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE18" t="str">
-        <f>IF(F18="", "", SUM(AC18:AD22))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF18" t="str">
@@ -7761,7 +7761,7 @@
         <v/>
       </c>
       <c r="AH18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7847,15 +7847,15 @@
         <v>0</v>
       </c>
       <c r="V19" t="str">
-        <f>IF(F19="","",I19*J19/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W19" t="str">
-        <f>IF(F19="", "", V19*(1-K19))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f>IF(F19="", "", G19*W19*H19)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y19">
@@ -7863,11 +7863,11 @@
         <v>59.884199999999993</v>
       </c>
       <c r="Z19" t="str">
-        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA19" t="str">
-        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB19">
@@ -7879,11 +7879,11 @@
         <v>12.575681999999999</v>
       </c>
       <c r="AD19">
-        <f>IF(OR(N19="", N19="directApplication"), "",AB19*U19)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE19" t="str">
-        <f>IF(F19="", "", SUM(AC19:AD23))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF19" t="str">
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
       <c r="AH19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7975,15 +7975,15 @@
         <v>N/A</v>
       </c>
       <c r="V20" s="11" t="str">
-        <f>IF(F20="","",I20*J20/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W20" s="11" t="str">
-        <f>IF(F20="", "", V20*(1-K20))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X20" t="str">
-        <f>IF(F20="", "", G20*W20*H20)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y20" s="11" t="str">
@@ -7991,11 +7991,11 @@
         <v/>
       </c>
       <c r="Z20" t="str">
-        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA20" s="11" t="str">
-        <f>IF(F20="", "",SUM(Z20:Z24))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB20" t="str">
@@ -8007,11 +8007,11 @@
         <v/>
       </c>
       <c r="AD20" t="str">
-        <f>IF(OR(N20="", N20="directApplication"), "",AB20*U20)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AE20" t="str">
-        <f>IF(F20="", "", SUM(AC20:AD24))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF20" t="str">
@@ -8023,7 +8023,7 @@
         <v/>
       </c>
       <c r="AH20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8109,15 +8109,15 @@
         <v>0.2</v>
       </c>
       <c r="V21">
-        <f>IF(F21="","",I21*J21/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W21">
-        <f>IF(F21="", "", V21*(1-K21))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X21">
-        <f>IF(F21="", "", G21*W21*H21)</f>
+        <f t="shared" si="2"/>
         <v>671.06552673600004</v>
       </c>
       <c r="Y21">
@@ -8125,11 +8125,11 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA21">
-        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <f t="shared" si="4"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AB21">
@@ -8141,11 +8141,11 @@
         <v>0</v>
       </c>
       <c r="AD21">
-        <f>IF(OR(N21="", N21="directApplication"), "",AB21*U21)</f>
+        <f t="shared" si="5"/>
         <v>38.974680514194809</v>
       </c>
       <c r="AE21">
-        <f>IF(F21="", "", SUM(AC21:AD25))</f>
+        <f t="shared" si="6"/>
         <v>152.04385324499694</v>
       </c>
       <c r="AF21">
@@ -8157,7 +8157,7 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AH21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1.4096637250857571E-3</v>
       </c>
     </row>
@@ -8243,15 +8243,15 @@
         <v>0.2</v>
       </c>
       <c r="V22" t="str">
-        <f>IF(F22="","",I22*J22/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W22" t="str">
-        <f>IF(F22="", "", V22*(1-K22))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X22" t="str">
-        <f>IF(F22="", "", G22*W22*H22)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y22">
@@ -8259,11 +8259,11 @@
         <v>603.9589740624001</v>
       </c>
       <c r="Z22">
-        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <f t="shared" si="3"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AA22" t="str">
-        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB22">
@@ -8275,11 +8275,11 @@
         <v>30.197948703120005</v>
       </c>
       <c r="AD22">
-        <f>IF(OR(N22="", N22="directApplication"), "",AB22*U22)</f>
+        <f t="shared" si="5"/>
         <v>68.778847966226124</v>
       </c>
       <c r="AE22" t="str">
-        <f>IF(F22="", "", SUM(AC22:AD26))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF22" t="str">
@@ -8291,7 +8291,7 @@
         <v/>
       </c>
       <c r="AH22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8377,15 +8377,15 @@
         <v>0</v>
       </c>
       <c r="V23" t="str">
-        <f>IF(F23="","",I23*J23/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W23" t="str">
-        <f>IF(F23="", "", V23*(1-K23))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X23" t="str">
-        <f>IF(F23="", "", G23*W23*H23)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y23">
@@ -8393,11 +8393,11 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA23" t="str">
-        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB23">
@@ -8409,11 +8409,11 @@
         <v>0</v>
       </c>
       <c r="AD23">
-        <f>IF(OR(N23="", N23="directApplication"), "",AB23*U23)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE23" t="str">
-        <f>IF(F23="", "", SUM(AC23:AD27))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF23" t="str">
@@ -8425,7 +8425,7 @@
         <v/>
       </c>
       <c r="AH23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8511,15 +8511,15 @@
         <v>0</v>
       </c>
       <c r="V24" t="str">
-        <f>IF(F24="","",I24*J24/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W24" t="str">
-        <f>IF(F24="", "", V24*(1-K24))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X24" t="str">
-        <f>IF(F24="", "", G24*W24*H24)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y24">
@@ -8527,11 +8527,11 @@
         <v>67.106552673600007</v>
       </c>
       <c r="Z24" t="str">
-        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA24" t="str">
-        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB24">
@@ -8543,11 +8543,11 @@
         <v>14.092376061456001</v>
       </c>
       <c r="AD24">
-        <f>IF(OR(N24="", N24="directApplication"), "",AB24*U24)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE24" t="str">
-        <f>IF(F24="", "", SUM(AC24:AD28))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF24" t="str">
@@ -8559,7 +8559,7 @@
         <v/>
       </c>
       <c r="AH24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8639,15 +8639,15 @@
         <v>N/A</v>
       </c>
       <c r="V25" s="11" t="str">
-        <f>IF(F25="","",I25*J25/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W25" s="11" t="str">
-        <f>IF(F25="", "", V25*(1-K25))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X25" t="str">
-        <f>IF(F25="", "", G25*W25*H25)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y25" s="11" t="str">
@@ -8655,11 +8655,11 @@
         <v/>
       </c>
       <c r="Z25" t="str">
-        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA25" s="11" t="str">
-        <f>IF(F25="", "",SUM(Z25:Z29))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB25" t="str">
@@ -8671,11 +8671,11 @@
         <v/>
       </c>
       <c r="AD25" t="str">
-        <f>IF(OR(N25="", N25="directApplication"), "",AB25*U25)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AE25" t="str">
-        <f>IF(F25="", "", SUM(AC25:AD29))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF25" t="str">
@@ -8687,7 +8687,7 @@
         <v/>
       </c>
       <c r="AH25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8773,15 +8773,15 @@
         <v>0.2</v>
       </c>
       <c r="V26">
-        <f>IF(F26="","",I26*J26/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W26">
-        <f>IF(F26="", "", V26*(1-K26))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X26">
-        <f>IF(F26="", "", G26*W26*H26)</f>
+        <f t="shared" si="2"/>
         <v>335.74770719999998</v>
       </c>
       <c r="Y26">
@@ -8789,11 +8789,11 @@
         <v>33.574770719999997</v>
       </c>
       <c r="Z26">
-        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <f t="shared" si="3"/>
         <v>23.46876473328</v>
       </c>
       <c r="AA26">
-        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <f t="shared" si="4"/>
         <v>23.46876473328</v>
       </c>
       <c r="AB26">
@@ -8805,11 +8805,11 @@
         <v>10.072431215999998</v>
       </c>
       <c r="AD26">
-        <f>IF(OR(N26="", N26="directApplication"), "",AB26*U26)</f>
+        <f t="shared" si="5"/>
         <v>2.3468764733280003</v>
       </c>
       <c r="AE26">
-        <f>IF(F26="", "", SUM(AC26:AD30))</f>
+        <f t="shared" si="6"/>
         <v>77.04906258679199</v>
       </c>
       <c r="AF26">
@@ -8821,7 +8821,7 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AH26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>9.68616786805385E-4</v>
       </c>
     </row>
@@ -8907,15 +8907,15 @@
         <v>0.2</v>
       </c>
       <c r="V27" t="str">
-        <f>IF(F27="","",I27*J27/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W27" t="str">
-        <f>IF(F27="", "", V27*(1-K27))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X27" t="str">
-        <f>IF(F27="", "", G27*W27*H27)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y27">
@@ -8923,11 +8923,11 @@
         <v>0</v>
       </c>
       <c r="Z27">
-        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA27" t="str">
-        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB27">
@@ -8939,11 +8939,11 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <f>IF(OR(N27="", N27="directApplication"), "",AB27*U27)</f>
+        <f t="shared" si="5"/>
         <v>1.1734382366640002</v>
       </c>
       <c r="AE27" t="str">
-        <f>IF(F27="", "", SUM(AC27:AD31))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF27" t="str">
@@ -8955,7 +8955,7 @@
         <v/>
       </c>
       <c r="AH27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9041,15 +9041,15 @@
         <v>0</v>
       </c>
       <c r="V28" t="str">
-        <f>IF(F28="","",I28*J28/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W28" t="str">
-        <f>IF(F28="", "", V28*(1-K28))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X28" t="str">
-        <f>IF(F28="", "", G28*W28*H28)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y28">
@@ -9057,11 +9057,11 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA28" t="str">
-        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB28">
@@ -9073,11 +9073,11 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <f>IF(OR(N28="", N28="directApplication"), "",AB28*U28)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE28" t="str">
-        <f>IF(F28="", "", SUM(AC28:AD32))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF28" t="str">
@@ -9089,7 +9089,7 @@
         <v/>
       </c>
       <c r="AH28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9175,15 +9175,15 @@
         <v>0</v>
       </c>
       <c r="V29" t="str">
-        <f>IF(F29="","",I29*J29/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W29" t="str">
-        <f>IF(F29="", "", V29*(1-K29))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X29" t="str">
-        <f>IF(F29="", "", G29*W29*H29)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y29">
@@ -9191,11 +9191,11 @@
         <v>302.17293647999998</v>
       </c>
       <c r="Z29" t="str">
-        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA29" t="str">
-        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB29">
@@ -9207,11 +9207,11 @@
         <v>63.456316660799992</v>
       </c>
       <c r="AD29">
-        <f>IF(OR(N29="", N29="directApplication"), "",AB29*U29)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE29" t="str">
-        <f>IF(F29="", "", SUM(AC29:AD33))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF29" t="str">
@@ -9223,7 +9223,7 @@
         <v/>
       </c>
       <c r="AH29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9303,15 +9303,15 @@
         <v>N/A</v>
       </c>
       <c r="V30" s="11" t="str">
-        <f>IF(F30="","",I30*J30/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W30" s="11" t="str">
-        <f>IF(F30="", "", V30*(1-K30))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X30" t="str">
-        <f>IF(F30="", "", G30*W30*H30)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y30" s="11" t="str">
@@ -9319,11 +9319,11 @@
         <v/>
       </c>
       <c r="Z30" t="str">
-        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA30" s="11" t="str">
-        <f>IF(F30="", "",SUM(Z30:Z34))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB30" t="str">
@@ -9335,11 +9335,11 @@
         <v/>
       </c>
       <c r="AD30" t="str">
-        <f>IF(OR(N30="", N30="directApplication"), "",AB30*U30)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AE30" t="str">
-        <f>IF(F30="", "", SUM(AC30:AD34))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF30" t="str">
@@ -9351,7 +9351,7 @@
         <v/>
       </c>
       <c r="AH30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9709,15 +9709,15 @@
         <v>0.2</v>
       </c>
       <c r="V11">
-        <f>IF(F11="","",I11*J11/6.25)</f>
+        <f t="shared" ref="V11:V30" si="0">IF(F11="","",I11*J11/6.25)</f>
         <v>2.6144000000000002E-3</v>
       </c>
       <c r="W11">
-        <f>IF(F11="", "", V11*(1-K11))</f>
+        <f t="shared" ref="W11:W30" si="1">IF(F11="", "", V11*(1-K11))</f>
         <v>1.6993600000000002E-3</v>
       </c>
       <c r="X11">
-        <f>IF(F11="", "", G11*W11*H11)</f>
+        <f t="shared" ref="X11:X30" si="2">IF(F11="", "", G11*W11*H11)</f>
         <v>424.84000000000003</v>
       </c>
       <c r="Y11">
@@ -9725,11 +9725,11 @@
         <v>42.484000000000009</v>
       </c>
       <c r="Z11">
-        <f>IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
+        <f t="shared" ref="Z11:Z30" si="3">IF(OR(L11="", L11="pastureRangeAndPaddock"), "", Y11*(1-R11-S11))</f>
         <v>29.69631600000001</v>
       </c>
       <c r="AA11">
-        <f>IF(F11="", "",SUM(Z11:Z15))</f>
+        <f t="shared" ref="AA11:AA30" si="4">IF(F11="", "",SUM(Z11:Z15))</f>
         <v>186.67469600000001</v>
       </c>
       <c r="AB11">
@@ -9847,15 +9847,15 @@
         <v>0.2</v>
       </c>
       <c r="V12" t="str">
-        <f>IF(F12="","",I12*J12/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W12" t="str">
-        <f>IF(F12="", "", V12*(1-K12))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X12" t="str">
-        <f>IF(F12="", "", G12*W12*H12)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y12">
@@ -9863,11 +9863,11 @@
         <v>84.968000000000018</v>
       </c>
       <c r="Z12">
-        <f>IF(OR(L12="", L12="pastureRangeAndPaddock"), "", Y12*(1-R12-S12))</f>
+        <f t="shared" si="3"/>
         <v>80.634632000000011</v>
       </c>
       <c r="AA12" t="str">
-        <f>IF(F12="", "",SUM(Z12:Z16))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB12">
@@ -9875,7 +9875,7 @@
         <v>37.334939200000001</v>
       </c>
       <c r="AC12" t="str">
-        <f t="shared" ref="AC12:AC30" si="0">IF(E12="", "", IF(E12, 1, 0))</f>
+        <f t="shared" ref="AC12:AC30" si="5">IF(E12="", "", IF(E12, 1, 0))</f>
         <v/>
       </c>
       <c r="AD12" t="str">
@@ -9891,15 +9891,15 @@
         <v/>
       </c>
       <c r="AG12" t="str">
-        <f t="shared" ref="AG12:AG30" si="1">IF(N12="solidStorage", AB12*AC12*AD12, "")</f>
+        <f t="shared" ref="AG12:AG30" si="6">IF(N12="solidStorage", AB12*AC12*AD12, "")</f>
         <v/>
       </c>
       <c r="AH12" t="str">
-        <f t="shared" ref="AH12:AH30" si="2">IF(L15="pastureRangeAndPaddock", Y15*AD$11*AC$11, "")</f>
+        <f t="shared" ref="AH12:AH15" si="7">IF(L15="pastureRangeAndPaddock", Y15*AD$11*AC$11, "")</f>
         <v/>
       </c>
       <c r="AI12" t="str">
-        <f t="shared" ref="AI12:AI31" si="3">IF(F12="", "", (AG12+AH12)*AE12*AF12/1000)</f>
+        <f t="shared" ref="AI12:AI31" si="8">IF(F12="", "", (AG12+AH12)*AE12*AF12/1000)</f>
         <v/>
       </c>
     </row>
@@ -9985,15 +9985,15 @@
         <v>0</v>
       </c>
       <c r="V13" t="str">
-        <f>IF(F13="","",I13*J13/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W13" t="str">
-        <f>IF(F13="", "", V13*(1-K13))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X13" t="str">
-        <f>IF(F13="", "", G13*W13*H13)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y13">
@@ -10001,11 +10001,11 @@
         <v>127.452</v>
       </c>
       <c r="Z13">
-        <f>IF(OR(L13="", L13="pastureRangeAndPaddock"), "", Y13*(1-R13-S13))</f>
+        <f t="shared" si="3"/>
         <v>76.343747999999991</v>
       </c>
       <c r="AA13" t="str">
-        <f>IF(F13="", "",SUM(Z13:Z17))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB13">
@@ -10013,7 +10013,7 @@
         <v>46.668674000000003</v>
       </c>
       <c r="AC13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD13" t="str">
@@ -10029,15 +10029,15 @@
         <v/>
       </c>
       <c r="AG13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10123,15 +10123,15 @@
         <v>0</v>
       </c>
       <c r="V14" t="str">
-        <f>IF(F14="","",I14*J14/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W14" t="str">
-        <f>IF(F14="", "", V14*(1-K14))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X14" t="str">
-        <f>IF(F14="", "", G14*W14*H14)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y14">
@@ -10139,11 +10139,11 @@
         <v>169.93600000000004</v>
       </c>
       <c r="Z14" t="str">
-        <f>IF(OR(L14="", L14="pastureRangeAndPaddock"), "", Y14*(1-R14-S14))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA14" t="str">
-        <f>IF(F14="", "",SUM(Z14:Z18))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB14">
@@ -10151,7 +10151,7 @@
         <v>31.734698320000003</v>
       </c>
       <c r="AC14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD14" t="str">
@@ -10167,15 +10167,15 @@
         <v/>
       </c>
       <c r="AG14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10255,15 +10255,15 @@
         <v>N/A</v>
       </c>
       <c r="V15" s="11" t="str">
-        <f>IF(F15="","",I15*J15/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W15" s="11" t="str">
-        <f>IF(F15="", "", V15*(1-K15))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X15" t="str">
-        <f>IF(F15="", "", G15*W15*H15)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y15" s="11" t="str">
@@ -10271,11 +10271,11 @@
         <v/>
       </c>
       <c r="Z15" t="str">
-        <f>IF(OR(L15="", L15="pastureRangeAndPaddock"), "", Y15*(1-R15-S15))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA15" s="11" t="str">
-        <f>IF(F15="", "",SUM(Z15:Z19))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB15" t="str">
@@ -10283,7 +10283,7 @@
         <v/>
       </c>
       <c r="AC15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD15" t="str">
@@ -10299,15 +10299,15 @@
         <v/>
       </c>
       <c r="AG15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AI15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10329,8 +10329,7 @@
         <v>dry</v>
       </c>
       <c r="E16" t="b">
-        <f>IF(ISBLANK('Input Scenarios'!E13), "", 'Input Scenarios'!E13)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="str">
         <f>IF(ISBLANK('Input Scenarios'!F13), "", 'Input Scenarios'!F13)</f>
@@ -10393,15 +10392,15 @@
         <v>0.2</v>
       </c>
       <c r="V16">
-        <f>IF(F16="","",I16*J16/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.1312000000000002E-3</v>
       </c>
       <c r="W16">
-        <f>IF(F16="", "", V16*(1-K16))</f>
+        <f t="shared" si="1"/>
         <v>2.1292159999999997E-3</v>
       </c>
       <c r="X16">
-        <f>IF(F16="", "", G16*W16*H16)</f>
+        <f t="shared" si="2"/>
         <v>598.84199999999987</v>
       </c>
       <c r="Y16">
@@ -10409,11 +10408,11 @@
         <v>239.53679999999997</v>
       </c>
       <c r="Z16">
-        <f>IF(OR(L16="", L16="pastureRangeAndPaddock"), "", Y16*(1-R16-S16))</f>
+        <f t="shared" si="3"/>
         <v>167.4362232</v>
       </c>
       <c r="AA16">
-        <f>IF(F16="", "",SUM(Z16:Z20))</f>
+        <f t="shared" si="4"/>
         <v>409.66781219999996</v>
       </c>
       <c r="AB16">
@@ -10421,8 +10420,8 @@
         <v>81.933562440000003</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AD16">
         <f>IF(E16="","",Constants!$M$2)</f>
@@ -10437,16 +10436,16 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="1"/>
-        <v>1.6386712488000001</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AH16">
         <f>IF(L19="pastureRangeAndPaddock", Y19*AD$16*AC$16, "")</f>
-        <v>1.197684</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="3"/>
-        <v>4.9028426443542864E-5</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
@@ -10531,15 +10530,15 @@
         <v>0.2</v>
       </c>
       <c r="V17" t="str">
-        <f>IF(F17="","",I17*J17/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W17" t="str">
-        <f>IF(F17="", "", V17*(1-K17))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X17" t="str">
-        <f>IF(F17="", "", G17*W17*H17)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y17">
@@ -10547,11 +10546,11 @@
         <v>179.65259999999995</v>
       </c>
       <c r="Z17">
-        <f>IF(OR(L17="", L17="pastureRangeAndPaddock"), "", Y17*(1-R17-S17))</f>
+        <f t="shared" si="3"/>
         <v>170.49031739999995</v>
       </c>
       <c r="AA17" t="str">
-        <f>IF(F17="", "",SUM(Z17:Z21))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB17">
@@ -10559,7 +10558,7 @@
         <v>102.41695304999999</v>
       </c>
       <c r="AC17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD17" t="str">
@@ -10575,15 +10574,15 @@
         <v/>
       </c>
       <c r="AG17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH17" t="str">
-        <f t="shared" ref="AH17:AH20" si="4">IF(L20="pastureRangeAndPaddock", Y20*AD$16*AC$16, "")</f>
+        <f t="shared" ref="AH17:AH20" si="9">IF(L20="pastureRangeAndPaddock", Y20*AD$16*AC$16, "")</f>
         <v/>
       </c>
       <c r="AI17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10669,15 +10668,15 @@
         <v>0</v>
       </c>
       <c r="V18" t="str">
-        <f>IF(F18="","",I18*J18/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W18" t="str">
-        <f>IF(F18="", "", V18*(1-K18))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X18" t="str">
-        <f>IF(F18="", "", G18*W18*H18)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y18">
@@ -10685,11 +10684,11 @@
         <v>119.76839999999999</v>
       </c>
       <c r="Z18">
-        <f>IF(OR(L18="", L18="pastureRangeAndPaddock"), "", Y18*(1-R18-S18))</f>
+        <f t="shared" si="3"/>
         <v>71.74127159999999</v>
       </c>
       <c r="AA18" t="str">
-        <f>IF(F18="", "",SUM(Z18:Z22))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB18">
@@ -10697,7 +10696,7 @@
         <v>81.933562440000003</v>
       </c>
       <c r="AC18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD18" t="str">
@@ -10713,15 +10712,15 @@
         <v/>
       </c>
       <c r="AG18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AI18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10807,15 +10806,15 @@
         <v>0</v>
       </c>
       <c r="V19" t="str">
-        <f>IF(F19="","",I19*J19/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W19" t="str">
-        <f>IF(F19="", "", V19*(1-K19))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f>IF(F19="", "", G19*W19*H19)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y19">
@@ -10823,11 +10822,11 @@
         <v>59.884199999999993</v>
       </c>
       <c r="Z19" t="str">
-        <f>IF(OR(L19="", L19="pastureRangeAndPaddock"), "", Y19*(1-R19-S19))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA19" t="str">
-        <f>IF(F19="", "",SUM(Z19:Z23))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB19">
@@ -10835,7 +10834,7 @@
         <v>102.41695304999999</v>
       </c>
       <c r="AC19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD19" t="str">
@@ -10851,15 +10850,15 @@
         <v/>
       </c>
       <c r="AG19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AI19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -10939,15 +10938,15 @@
         <v>N/A</v>
       </c>
       <c r="V20" s="11" t="str">
-        <f>IF(F20="","",I20*J20/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W20" s="11" t="str">
-        <f>IF(F20="", "", V20*(1-K20))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X20" t="str">
-        <f>IF(F20="", "", G20*W20*H20)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y20" s="11" t="str">
@@ -10955,11 +10954,11 @@
         <v/>
       </c>
       <c r="Z20" t="str">
-        <f>IF(OR(L20="", L20="pastureRangeAndPaddock"), "", Y20*(1-R20-S20))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA20" s="11" t="str">
-        <f>IF(F20="", "",SUM(Z20:Z24))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB20" t="str">
@@ -10967,7 +10966,7 @@
         <v/>
       </c>
       <c r="AC20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD20" t="str">
@@ -10983,15 +10982,15 @@
         <v/>
       </c>
       <c r="AG20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AI20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11077,15 +11076,15 @@
         <v>0.2</v>
       </c>
       <c r="V21">
-        <f>IF(F21="","",I21*J21/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W21">
-        <f>IF(F21="", "", V21*(1-K21))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X21">
-        <f>IF(F21="", "", G21*W21*H21)</f>
+        <f t="shared" si="2"/>
         <v>671.06552673600004</v>
       </c>
       <c r="Y21">
@@ -11093,11 +11092,11 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>IF(OR(L21="", L21="pastureRangeAndPaddock"), "", Y21*(1-R21-S21))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA21">
-        <f>IF(F21="", "",SUM(Z21:Z25))</f>
+        <f t="shared" si="4"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AB21">
@@ -11105,7 +11104,7 @@
         <v>194.87340257097404</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AD21">
@@ -11121,7 +11120,7 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AG21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8974680514194806</v>
       </c>
       <c r="AH21">
@@ -11129,7 +11128,7 @@
         <v>1.3421310534720001</v>
       </c>
       <c r="AI21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>9.0570213098838429E-5</v>
       </c>
     </row>
@@ -11215,15 +11214,15 @@
         <v>0.2</v>
       </c>
       <c r="V22" t="str">
-        <f>IF(F22="","",I22*J22/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W22" t="str">
-        <f>IF(F22="", "", V22*(1-K22))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X22" t="str">
-        <f>IF(F22="", "", G22*W22*H22)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y22">
@@ -11231,11 +11230,11 @@
         <v>603.9589740624001</v>
       </c>
       <c r="Z22">
-        <f>IF(OR(L22="", L22="pastureRangeAndPaddock"), "", Y22*(1-R22-S22))</f>
+        <f t="shared" si="3"/>
         <v>573.15706638521772</v>
       </c>
       <c r="AA22" t="str">
-        <f>IF(F22="", "",SUM(Z22:Z26))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB22">
@@ -11243,7 +11242,7 @@
         <v>343.89423983113062</v>
       </c>
       <c r="AC22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD22" t="str">
@@ -11259,15 +11258,15 @@
         <v/>
       </c>
       <c r="AG22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH22" t="str">
-        <f t="shared" ref="AH22:AH30" si="5">IF(L25="pastureRangeAndPaddock", Y25*AD$21*AC$21, "")</f>
+        <f t="shared" ref="AH22:AH25" si="10">IF(L25="pastureRangeAndPaddock", Y25*AD$21*AC$21, "")</f>
         <v/>
       </c>
       <c r="AI22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11353,15 +11352,15 @@
         <v>0</v>
       </c>
       <c r="V23" t="str">
-        <f>IF(F23="","",I23*J23/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W23" t="str">
-        <f>IF(F23="", "", V23*(1-K23))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X23" t="str">
-        <f>IF(F23="", "", G23*W23*H23)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y23">
@@ -11369,11 +11368,11 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>IF(OR(L23="", L23="pastureRangeAndPaddock"), "", Y23*(1-R23-S23))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA23" t="str">
-        <f>IF(F23="", "",SUM(Z23:Z27))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB23">
@@ -11381,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="AC23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD23" t="str">
@@ -11397,15 +11396,15 @@
         <v/>
       </c>
       <c r="AG23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AI23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11491,15 +11490,15 @@
         <v>0</v>
       </c>
       <c r="V24" t="str">
-        <f>IF(F24="","",I24*J24/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W24" t="str">
-        <f>IF(F24="", "", V24*(1-K24))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X24" t="str">
-        <f>IF(F24="", "", G24*W24*H24)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y24">
@@ -11507,11 +11506,11 @@
         <v>67.106552673600007</v>
       </c>
       <c r="Z24" t="str">
-        <f>IF(OR(L24="", L24="pastureRangeAndPaddock"), "", Y24*(1-R24-S24))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA24" t="str">
-        <f>IF(F24="", "",SUM(Z24:Z28))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB24">
@@ -11519,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="AC24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD24" t="str">
@@ -11535,15 +11534,15 @@
         <v/>
       </c>
       <c r="AG24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AI24" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11623,15 +11622,15 @@
         <v>N/A</v>
       </c>
       <c r="V25" s="11" t="str">
-        <f>IF(F25="","",I25*J25/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W25" s="11" t="str">
-        <f>IF(F25="", "", V25*(1-K25))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X25" t="str">
-        <f>IF(F25="", "", G25*W25*H25)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y25" s="11" t="str">
@@ -11639,11 +11638,11 @@
         <v/>
       </c>
       <c r="Z25" t="str">
-        <f>IF(OR(L25="", L25="pastureRangeAndPaddock"), "", Y25*(1-R25-S25))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA25" s="11" t="str">
-        <f>IF(F25="", "",SUM(Z25:Z29))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB25" t="str">
@@ -11651,7 +11650,7 @@
         <v/>
       </c>
       <c r="AC25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD25" t="str">
@@ -11667,15 +11666,15 @@
         <v/>
       </c>
       <c r="AG25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AI25" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11761,15 +11760,15 @@
         <v>0.2</v>
       </c>
       <c r="V26">
-        <f>IF(F26="","",I26*J26/6.25)</f>
+        <f t="shared" si="0"/>
         <v>3.4223999999999999E-3</v>
       </c>
       <c r="W26">
-        <f>IF(F26="", "", V26*(1-K26))</f>
+        <f t="shared" si="1"/>
         <v>1.813872E-3</v>
       </c>
       <c r="X26">
-        <f>IF(F26="", "", G26*W26*H26)</f>
+        <f t="shared" si="2"/>
         <v>335.74770719999998</v>
       </c>
       <c r="Y26">
@@ -11777,11 +11776,11 @@
         <v>33.574770719999997</v>
       </c>
       <c r="Z26">
-        <f>IF(OR(L26="", L26="pastureRangeAndPaddock"), "", Y26*(1-R26-S26))</f>
+        <f t="shared" si="3"/>
         <v>23.46876473328</v>
       </c>
       <c r="AA26">
-        <f>IF(F26="", "",SUM(Z26:Z30))</f>
+        <f t="shared" si="4"/>
         <v>23.46876473328</v>
       </c>
       <c r="AB26">
@@ -11789,7 +11788,7 @@
         <v>11.73438236664</v>
       </c>
       <c r="AC26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AD26">
@@ -11805,7 +11804,7 @@
         <v>1.5714285714285714</v>
       </c>
       <c r="AG26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.23468764733280001</v>
       </c>
       <c r="AH26">
@@ -11813,7 +11812,7 @@
         <v>6.0434587295999993</v>
       </c>
       <c r="AI26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.0852224451555266E-4</v>
       </c>
     </row>
@@ -11899,15 +11898,15 @@
         <v>0.2</v>
       </c>
       <c r="V27" t="str">
-        <f>IF(F27="","",I27*J27/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W27" t="str">
-        <f>IF(F27="", "", V27*(1-K27))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X27" t="str">
-        <f>IF(F27="", "", G27*W27*H27)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y27">
@@ -11915,11 +11914,11 @@
         <v>0</v>
       </c>
       <c r="Z27">
-        <f>IF(OR(L27="", L27="pastureRangeAndPaddock"), "", Y27*(1-R27-S27))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA27" t="str">
-        <f>IF(F27="", "",SUM(Z27:Z31))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB27">
@@ -11927,7 +11926,7 @@
         <v>5.8671911833200001</v>
       </c>
       <c r="AC27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD27" t="str">
@@ -11943,15 +11942,15 @@
         <v/>
       </c>
       <c r="AG27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH27" t="str">
-        <f t="shared" ref="AH27:AH30" si="6">IF(L30="pastureRangeAndPaddock", Y30*AD$26*AC$26, "")</f>
+        <f t="shared" ref="AH27:AH30" si="11">IF(L30="pastureRangeAndPaddock", Y30*AD$26*AC$26, "")</f>
         <v/>
       </c>
       <c r="AI27" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -12037,15 +12036,15 @@
         <v>0</v>
       </c>
       <c r="V28" t="str">
-        <f>IF(F28="","",I28*J28/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W28" t="str">
-        <f>IF(F28="", "", V28*(1-K28))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X28" t="str">
-        <f>IF(F28="", "", G28*W28*H28)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y28">
@@ -12053,11 +12052,11 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <f>IF(OR(L28="", L28="pastureRangeAndPaddock"), "", Y28*(1-R28-S28))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA28" t="str">
-        <f>IF(F28="", "",SUM(Z28:Z32))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB28">
@@ -12065,7 +12064,7 @@
         <v>5.8671911833200001</v>
       </c>
       <c r="AC28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD28" t="str">
@@ -12081,15 +12080,15 @@
         <v/>
       </c>
       <c r="AG28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AI28" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -12175,15 +12174,15 @@
         <v>0</v>
       </c>
       <c r="V29" t="str">
-        <f>IF(F29="","",I29*J29/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W29" t="str">
-        <f>IF(F29="", "", V29*(1-K29))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X29" t="str">
-        <f>IF(F29="", "", G29*W29*H29)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y29">
@@ -12191,11 +12190,11 @@
         <v>302.17293647999998</v>
       </c>
       <c r="Z29" t="str">
-        <f>IF(OR(L29="", L29="pastureRangeAndPaddock"), "", Y29*(1-R29-S29))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA29" t="str">
-        <f>IF(F29="", "",SUM(Z29:Z33))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB29">
@@ -12203,7 +12202,7 @@
         <v>0</v>
       </c>
       <c r="AC29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD29" t="str">
@@ -12219,15 +12218,15 @@
         <v/>
       </c>
       <c r="AG29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH29" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AI29" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -12307,15 +12306,15 @@
         <v>N/A</v>
       </c>
       <c r="V30" s="11" t="str">
-        <f>IF(F30="","",I30*J30/6.25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W30" s="11" t="str">
-        <f>IF(F30="", "", V30*(1-K30))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X30" t="str">
-        <f>IF(F30="", "", G30*W30*H30)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y30" s="11" t="str">
@@ -12323,11 +12322,11 @@
         <v/>
       </c>
       <c r="Z30" t="str">
-        <f>IF(OR(L30="", L30="pastureRangeAndPaddock"), "", Y30*(1-R30-S30))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AA30" s="11" t="str">
-        <f>IF(F30="", "",SUM(Z30:Z34))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AB30" t="str">
@@ -12335,7 +12334,7 @@
         <v/>
       </c>
       <c r="AC30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="AD30" t="str">
@@ -12351,21 +12350,21 @@
         <v/>
       </c>
       <c r="AG30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AH30" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AI30" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="AI31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>

--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9D7B04-2C32-654C-8AC6-66D76C6D2E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E67F5B8-FC51-954F-8452-B5E9FE41C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6820" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.6.1.1" sheetId="5" r:id="rId1"/>
@@ -8050,7 +8050,7 @@
       <c r="BQ10" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BR10" s="14" t="s">
+      <c r="BR10" s="15" t="s">
         <v>85</v>
       </c>
       <c r="BS10" s="15" t="s">
@@ -9490,7 +9490,7 @@
         <v>6.9011177039999989</v>
       </c>
       <c r="BS15" s="12">
-        <f t="shared" si="9"/>
+        <f>AU15+BR15</f>
         <v>12.941883863999998</v>
       </c>
       <c r="BT15">
